--- a/scripts/property_list.xlsx
+++ b/scripts/property_list.xlsx
@@ -8,8 +8,7 @@
     <sheet name="property list portsmouth" sheetId="3" r:id="rId3"/>
     <sheet name="ooPropTest" sheetId="4" r:id="rId4"/>
     <sheet name="property count" sheetId="5" r:id="rId5"/>
-    <sheet name="props manchester" sheetId="6" r:id="rId6"/>
-    <sheet name="property list 2" sheetId="7" r:id="rId7"/>
+    <sheet name="property list 2" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'property list'!$C$1:$C$29</definedName>
@@ -5497,6 +5496,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:P106"/>
   </ignoredErrors>
@@ -6876,6 +6876,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
   </ignoredErrors>
@@ -7833,6 +7834,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:P20"/>
   </ignoredErrors>
@@ -16854,6 +16856,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E530"/>
   </ignoredErrors>
@@ -27500,7 +27503,7 @@
     </row>
     <row r="410" xml:space="preserve">
       <c r="A410" t="str" xml:space="preserve">
-        <v xml:space="preserve">Evelyn
+        <v xml:space="preserve">Evelyn_x000d_
 Tu</v>
       </c>
       <c r="B410">
@@ -32987,7 +32990,7 @@
     </row>
     <row r="621" xml:space="preserve">
       <c r="A621" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jason - 07929 378412 
+        <v xml:space="preserve">Jason - 07929 378412 _x000d_
 020 8050 8286, jbstays.co.uk</v>
       </c>
       <c r="B621">
@@ -57086,6 +57089,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H1547"/>
   </ignoredErrors>
@@ -57094,7 +57098,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P141"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -57137,931 +57141,6 @@
         <v>liveExtLink</v>
       </c>
       <c r="N1" t="str">
-        <v>landlordEmail</v>
-      </c>
-      <c r="O1" t="str">
-        <v>landlordPhone</v>
-      </c>
-      <c r="P1" t="str">
-        <v>landlordName</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>BL0 0DG</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Whalley Rd, Ramsbottom, Bury BL0 0DG, UK</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G2" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66dec40686825cea1b419fa8</v>
-      </c>
-      <c r="M2" t="str">
-        <v>https://www.airbnb.co.uk/rooms/17261329?source_impression_id=p3_1725874088_P3NHABIhhfN58dzE</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>BL0 0LH</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Dearden Fold, Edenfield, Ramsbottom, Bury BL0 0LH, UK</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1.5</v>
-      </c>
-      <c r="F3" t="str">
-        <v>on-site-free</v>
-      </c>
-      <c r="G3" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68962491d650f7dedcce470e</v>
-      </c>
-      <c r="M3" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1277452780154902797?source_impression_id=p3_1759400035_P36tHl-VANGc-BXD</v>
-      </c>
-      <c r="N3" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="O3" t="str">
-        <v>00000000000</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>BL0 9BH</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Square St, Ramsbottom, Bury BL0, UK</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G4" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66e9a69f61683689a517d000</v>
-      </c>
-      <c r="M4" t="str">
-        <v>https://www.airbnb.co.uk/rooms/842095020272578427?source_impression_id=p3_1726588635_P3FP4zpqQhHk4x-_&amp;modal=DESCRIPTION</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>BL0 9BH</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Square St, Ramsbottom, Bury BL0, UK</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="str">
-        <v>on-site-free</v>
-      </c>
-      <c r="G5" t="str">
-        <v>free</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6703ade1225d9354290b7928</v>
-      </c>
-      <c r="M5" t="str">
-        <v>https://www.airbnb.co.uk/rooms/842095020272578427</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>BL2 1JA</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Hilden St, Haulgh, Bolton BL2 1JA, UK</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1.5</v>
-      </c>
-      <c r="F6" t="str">
-        <v>on-site-free</v>
-      </c>
-      <c r="G6" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6901f093103a4d24f8ac3f46</v>
-      </c>
-      <c r="M6" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1066576148268047359?source_impression_id=p3_1761728515_P3stK8c82xYiFqHR&amp;check_in=2025-10-30&amp;guests=1&amp;adults=1&amp;check_out=2025-11-07</v>
-      </c>
-      <c r="N6" t="str">
-        <v>mameikallon@yahoo.co.uk</v>
-      </c>
-      <c r="O6" t="str">
-        <v>07538720652</v>
-      </c>
-      <c r="P6" t="str">
-        <v>Mamei Kallon</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>BL2 2JP</v>
-      </c>
-      <c r="B7" t="str">
-        <v>22 Bleak St, Bolton BL2 2JP, UK</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G7" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68dfde5d56f6ee67fd541991</v>
-      </c>
-      <c r="M7" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1483919622885495783?_set_bev_on_new_domain=1759158878_EAZTQwYzJmZThmNT&amp;source_impression_id=p3_1759501703_P3UpyhHQ6pfadaS-</v>
-      </c>
-      <c r="N7" t="str">
-        <v>hello@brooklandstays.co.uk</v>
-      </c>
-      <c r="O7" t="str">
-        <v>07418611181</v>
-      </c>
-      <c r="P7" t="str">
-        <v>Harrison Crick</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>BL2 2PS</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Ilkley Cl, Tonge Fold, Bolton BL2 2PS, UK</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G8" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68dfbe7656f6ee67fd53e2ee</v>
-      </c>
-      <c r="M8" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1100095524181361568?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=25225c1d-c8c8-454b-b118-eede1508d473&amp;source_impression_id=p3_1759493239_P3pTUTy0rMfR6rQU</v>
-      </c>
-      <c r="N8" t="str">
-        <v>info@thecosycorner.co.uk</v>
-      </c>
-      <c r="O8" t="str">
-        <v>07411 534024</v>
-      </c>
-      <c r="P8" t="str">
-        <v>Richard Applegate</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>BL2 5NH</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Burnmoor Rd, Breightmet, Bolton BL2 5NH, UK</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>0.5</v>
-      </c>
-      <c r="F9" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G9" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67a4da91a5f919f029b18702</v>
-      </c>
-      <c r="M9" t="str">
-        <v>https://www.ideallodgings.com/room/4-bedroom-house-near-bolton?info%5Barrival_date%5D=06%2F02%2F2025&amp;info%5Bdeparture_date%5D=08%2F02%2F2025&amp;info%5Btotal_adult%5D=2</v>
-      </c>
-      <c r="N9" t="str">
-        <v>Laura@ideallodgings.com</v>
-      </c>
-      <c r="O9" t="str">
-        <v>07510 080450</v>
-      </c>
-      <c r="P9" t="str">
-        <v>Laura Harman</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>BL3 3FD</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Duncombe Rd, Bolton BL3 3FD, UK</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G10" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67a4e497a5f919f029b18d3f</v>
-      </c>
-      <c r="M10" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1286176925268645093?source_impression_id=p3_1738859598_P3N4NLlQd2zXiF7e</v>
-      </c>
-      <c r="N10" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="O10" t="str">
-        <v>00000000000</v>
-      </c>
-      <c r="P10" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>BL4 0PZ</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Coniston Ave, Farnworth, Bolton BL4 0PZ, UK</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>1.5</v>
-      </c>
-      <c r="F11" t="str">
-        <v>on-site-free</v>
-      </c>
-      <c r="G11" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/69021fd5f12a30c59f943d70</v>
-      </c>
-      <c r="M11" t="str">
-        <v>https://www.airbnb.co.uk/rooms/986332412757762435?adults=3&amp;check_in=2025-10-30&amp;check_out=2025-11-08&amp;location=BL3%204JH&amp;search_mode=regular_search&amp;children=0&amp;infants=0&amp;pets=0&amp;source_impression_id=p3_1761745802_P3I7xp5dqSxI_ydr&amp;previous_page_section_name=1001&amp;federated_search_id=48df80da-46dd-41f3-b2dc-1f72df2b2e49&amp;modal=DESCRIPTION</v>
-      </c>
-      <c r="N11" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="O11" t="str">
-        <v>00000000000</v>
-      </c>
-      <c r="P11" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>BL4 7RZ</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2 Darley Grove, Farnworth, Bolton BL4 7RZ, UK</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>7</v>
-      </c>
-      <c r="E12">
-        <v>2.5</v>
-      </c>
-      <c r="F12" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G12" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/675c2a2362ab267a27ca9b49</v>
-      </c>
-      <c r="M12" t="str">
-        <v>https://www.bluepuffinstays.co.uk/property/modern-4-br-house-with-parking/</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>BL6 5TQ</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Gresley Ave, Horwich, Bolton BL6 5TQ, UK</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G13" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67bcad631993060ade4a3e2b</v>
-      </c>
-      <c r="M13" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1355707117892284469?adults=2&amp;check_in=2025-02-25&amp;check_out=2025-03-07&amp;children=2&amp;search_mode=regular_search&amp;source_impression_id=p3_1740413842_P3EKKXBSsH8_cp_i&amp;previous_page_section_name=1000&amp;federated_search_id=e8260cb3-4588-4b9a-900b-cb1209e6b40e</v>
-      </c>
-      <c r="N13" t="str">
-        <v>info@kozyguru.com</v>
-      </c>
-      <c r="O13" t="str">
-        <v>07873 407490</v>
-      </c>
-      <c r="P13" t="str">
-        <v>Teresa</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>BL7 9DA</v>
-      </c>
-      <c r="B14" t="str">
-        <v>35 Hough Ln, Bromley Cross, Bolton BL7 9DA, UK</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>5</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" t="str">
-        <v>on-site-free</v>
-      </c>
-      <c r="G14" t="str">
-        <v>no</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6911b6782b4e96e2827cf49b</v>
-      </c>
-      <c r="M14" t="str">
-        <v>https://www.airbnb.co.uk/rooms/912367198286267802?_set_bev_on_new_domain=1760713577_EAZGQzMzc2YmQ1Mj&amp;set_everest_cookie_on_new_domain=1760713577.EAZDQ0ZDU0YmU4ZGU5ZT.lCiWfpfJjgrRoT3FGxqDlyN8dtTe4Xqqgm4DHkQDUGM&amp;source_impression_id=p3_1762768283_P369j1JnXz7k3LW-</v>
-      </c>
-      <c r="N14" t="str">
-        <v>info@regal-shortstays.co.uk</v>
-      </c>
-      <c r="O14" t="str">
-        <v xml:space="preserve">0330 043 7104 </v>
-      </c>
-      <c r="P14" t="str">
-        <v>Charlotte Sandiford | Regal Short Stays</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>BL8 1TS</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Tottington Rd, Bury BL8 1TS, UK</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <v>2.5</v>
-      </c>
-      <c r="F15" t="str">
-        <v>on-site-free</v>
-      </c>
-      <c r="G15" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/690203e9449b53687ace1d5d</v>
-      </c>
-      <c r="M15" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1467433869925990871?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=2b8a7a81-dbf4-4616-8d43-53d52d090762&amp;source_impression_id=p3_1761738265_P3uNfqZ-HEcKccIg</v>
-      </c>
-      <c r="N15" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="O15" t="str">
-        <v>00000000000</v>
-      </c>
-      <c r="P15" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>BL9 0LY</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Parson's Ln, Bury BL9 0LY, UK</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G16" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67e28909c7109816e83a32ca</v>
-      </c>
-      <c r="M16" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1192561597441059137?source_impression_id=p3_1742899128_P34SGgwRaVxxjGHJ</v>
-      </c>
-      <c r="N16" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="O16" t="str">
-        <v>00000000000</v>
-      </c>
-      <c r="P16" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>BL9 7EP</v>
-      </c>
-      <c r="B17" t="str">
-        <v>40 Benson St, Bury BL9 7EP, UK</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17">
-        <v>4</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="str">
-        <v>on-site-free</v>
-      </c>
-      <c r="G17" t="str">
-        <v>no</v>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6911bb7e95be8a43774679cd</v>
-      </c>
-      <c r="M17" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1359268226429033122?_set_bev_on_new_domain=1760713577_EAZGQzMzc2YmQ1Mj&amp;set_everest_cookie_on_new_domain=1760713577.EAZDQ0ZDU0YmU4ZGU5ZT.lCiWfpfJjgrRoT3FGxqDlyN8dtTe4Xqqgm4DHkQDUGM&amp;source_impression_id=p3_1762769521_P3_jc0N5_NLP1366</v>
-      </c>
-      <c r="N17" t="str">
-        <v>info@regal-shortstays.co.uk</v>
-      </c>
-      <c r="O17" t="str">
-        <v xml:space="preserve">0330 043 7104 </v>
-      </c>
-      <c r="P17" t="str">
-        <v>Charlotte Sandiford | Regal Short Stays</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>BL9 7LD</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Inglewood Cl, Bury BL9 7LD, UK</v>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G18" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67e198293270d13c31488827</v>
-      </c>
-      <c r="M18" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1278527037572775677?source_impression_id=p3_1742837498_P3Bvmxp5Ao_qu8Ix</v>
-      </c>
-      <c r="N18" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="O18" t="str">
-        <v>00000000000</v>
-      </c>
-      <c r="P18" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>BL9 7SA</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Rochdale Old Rd, Bury BL9 7SA, UK</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="str">
-        <v>off-site-chargeable</v>
-      </c>
-      <c r="G19" t="str">
-        <v>chargeable</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67e2852fb1abf45ecf494575</v>
-      </c>
-      <c r="M19" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1189979741587178990?_set_bev_on_new_domain=1728309648_EAY2VhNjI4MTFkMz&amp;source_impression_id=p3_1742897875_P3wE1d443pztxb4C&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
-      </c>
-      <c r="N19" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="O19" t="str">
-        <v>00000000000</v>
-      </c>
-      <c r="P19" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P140"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>postcode</v>
-      </c>
-      <c r="B1" t="str">
-        <v>fullAddress</v>
-      </c>
-      <c r="C1" t="str">
-        <v>bedrooms</v>
-      </c>
-      <c r="D1" t="str">
-        <v>beds</v>
-      </c>
-      <c r="E1" t="str">
-        <v>bathrooms</v>
-      </c>
-      <c r="F1" t="str">
-        <v>parking</v>
-      </c>
-      <c r="G1" t="str">
-        <v>pets</v>
-      </c>
-      <c r="H1" t="str">
-        <v>garden</v>
-      </c>
-      <c r="I1" t="str">
-        <v>balcony</v>
-      </c>
-      <c r="J1" t="str">
-        <v>patio</v>
-      </c>
-      <c r="K1" t="str">
-        <v>bbq</v>
-      </c>
-      <c r="L1" t="str">
-        <v>liveLink</v>
-      </c>
-      <c r="M1" t="str">
-        <v>liveExtLink</v>
-      </c>
-      <c r="N1" t="str">
         <v>landlordName</v>
       </c>
       <c r="O1" t="str">
@@ -58176,7 +57255,7 @@
         <v>KT1 4AX</v>
       </c>
       <c r="B4" t="str">
-        <v>33 Park Ct, Park Rd, New Malden KT3 5AE, UK</v>
+        <v>Park Rd, Hampton Wick, Kingston upon Thames KT1 4AX, UK</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -58188,10 +57267,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G4" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -58206,10 +57285,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ad70b2b024c354687660ce</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f0d126f6dcfb01fba97816</v>
       </c>
       <c r="M4" t="str">
-        <v>https://www.airbnb.co.uk/rooms/6066828?viralityEntryPoint=1&amp;unique_share_id=CE936BAF-7ED5-4BAE-8DBE-3DBDC0BE954D&amp;slcid=0794cc086a3c49a6b2aedf7e19bc2686&amp;s=76&amp;adults=1&amp;slug=Fn9BN1yF&amp;source_impression_id=p3_1756196057_P3XltzFJq9oUgXOn</v>
+        <v>https://www.airbnb.com/l/O7ozFtch</v>
       </c>
       <c r="N4" t="str">
         <v>Hannah Dutton-Waller</v>
@@ -58226,7 +57305,7 @@
         <v>KT1 4AX</v>
       </c>
       <c r="B5" t="str">
-        <v>Park Court, Park Rd, Hampton Wick, Kingston upon Thames KT1 4AU, UK</v>
+        <v>33 Park Ct, Park Rd, New Malden KT3 5AE, UK</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -58238,37 +57317,37 @@
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G5" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68dfae1b56f6ee67fd53970a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ad70b2b024c354687660ce</v>
       </c>
       <c r="M5" t="str">
-        <v>https://www.airbnb.co.uk/rooms/6066828?adults=3&amp;check_in=2025-10-15&amp;check_out=2025-10-22&amp;pets=1&amp;search_mode=regular_search&amp;source_impression_id=p3_1759485922_P3TUhbgwSrQ8sJcd&amp;previous_page_section_name=1000&amp;federated_search_id=48af8d57-3400-4bcc-b229-b2d98a1f2ac1</v>
+        <v>https://www.airbnb.co.uk/rooms/6066828?viralityEntryPoint=1&amp;unique_share_id=CE936BAF-7ED5-4BAE-8DBE-3DBDC0BE954D&amp;slcid=0794cc086a3c49a6b2aedf7e19bc2686&amp;s=76&amp;adults=1&amp;slug=Fn9BN1yF&amp;source_impression_id=p3_1756196057_P3XltzFJq9oUgXOn</v>
       </c>
       <c r="N5" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Hannah Dutton-Waller</v>
       </c>
       <c r="O5" t="str">
-        <v>temp@airbnb.com</v>
+        <v>hannahdw29@gmail.com</v>
       </c>
       <c r="P5" t="str">
-        <v>00000000000</v>
+        <v>+44 7977 340378</v>
       </c>
     </row>
     <row r="6">
@@ -58276,7 +57355,7 @@
         <v>KT1 4AX</v>
       </c>
       <c r="B6" t="str">
-        <v>Park Rd, Hampton Wick, Kingston upon Thames KT1 4AX, UK</v>
+        <v>Park Court, Park Rd, Hampton Wick, Kingston upon Thames KT1 4AU, UK</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -58297,28 +57376,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f0d126f6dcfb01fba97816</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68dfae1b56f6ee67fd53970a</v>
       </c>
       <c r="M6" t="str">
-        <v>https://www.airbnb.com/l/O7ozFtch</v>
+        <v>https://www.airbnb.co.uk/rooms/6066828?adults=3&amp;check_in=2025-10-15&amp;check_out=2025-10-22&amp;pets=1&amp;search_mode=regular_search&amp;source_impression_id=p3_1759485922_P3TUhbgwSrQ8sJcd&amp;previous_page_section_name=1000&amp;federated_search_id=48af8d57-3400-4bcc-b229-b2d98a1f2ac1</v>
       </c>
       <c r="N6" t="str">
-        <v>Hannah Dutton-Waller</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O6" t="str">
-        <v>hannahdw29@gmail.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P6" t="str">
-        <v>+44 7977 340378</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="7">
@@ -58426,7 +57505,7 @@
         <v>KT2 7DW</v>
       </c>
       <c r="B9" t="str">
-        <v>7 London Road, Kingston upon Thames, KT2 6PT</v>
+        <v>Manorgate Rd, London KT2, UK</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -58441,7 +57520,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G9" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -58456,7 +57535,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68daa133e8d8423b6968abf7</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/66d6ff553cd0be0c2f91c63a</v>
       </c>
       <c r="M9" t="str">
         <v>https://www.airbnb.co.uk/rooms/743513490080624231?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=44c1e2fd-b4d7-4227-ba62-edfb07f8198c&amp;source_impression_id=p3_1725365646_P3NASfY2ZohVWJ2k</v>
@@ -58476,7 +57555,7 @@
         <v>KT2 7DW</v>
       </c>
       <c r="B10" t="str">
-        <v>Manorgate Rd, London KT2, UK</v>
+        <v>7 London Road, Kingston upon Thames, KT2 6PT</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -58491,7 +57570,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G10" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -58506,7 +57585,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66d6ff553cd0be0c2f91c63a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68daa133e8d8423b6968abf7</v>
       </c>
       <c r="M10" t="str">
         <v>https://www.airbnb.co.uk/rooms/743513490080624231?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=44c1e2fd-b4d7-4227-ba62-edfb07f8198c&amp;source_impression_id=p3_1725365646_P3NASfY2ZohVWJ2k</v>
@@ -58858,7 +57937,7 @@
         <v>SW11 1SX</v>
       </c>
       <c r="B18" t="str">
-        <v>2, 67 St John's Hl, London SW11 1RZ, UK</v>
+        <v>St John's Hl, London SW11 1SX, UK</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -58888,10 +57967,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f62c30b8c1acfaf83a4983</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68fb448ff911141e69a138d7</v>
       </c>
       <c r="M18" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1508080538383464858?viralityEntryPoint=1&amp;unique_share_id=F207E198-E9B9-4D65-89B7-1559903B3C77&amp;slcid=1eba13d36311475d93cfe707ee7c340a&amp;s=76&amp;adults=1&amp;slug=TTXROpB4&amp;source_impression_id=p3_1760963365_P39cHqhtj8jxXxGf</v>
+        <v>https://www.airbnb.co.uk/rooms/1508080538383464858?viralityEntryPoint=1&amp;unique_share_id=E045C9E6-339A-4417-965A-01A0937A442E&amp;slcid=9761453bd8374aa78ecd24f279fe528b&amp;s=76&amp;adults=1&amp;slug=wvL2aonh&amp;source_impression_id=p3_1761297328_P3aSdbJcsW1JLqnY</v>
       </c>
       <c r="N18" t="str">
         <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
@@ -58908,7 +57987,7 @@
         <v>SW11 1SX</v>
       </c>
       <c r="B19" t="str">
-        <v>St John's Hl, London SW11 1SX, UK</v>
+        <v>2, 67 St John's Hl, London SW11 1RZ, UK</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -58938,10 +58017,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68fb448ff911141e69a138d7</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f62c30b8c1acfaf83a4983</v>
       </c>
       <c r="M19" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1508080538383464858?viralityEntryPoint=1&amp;unique_share_id=E045C9E6-339A-4417-965A-01A0937A442E&amp;slcid=9761453bd8374aa78ecd24f279fe528b&amp;s=76&amp;adults=1&amp;slug=wvL2aonh&amp;source_impression_id=p3_1761297328_P3aSdbJcsW1JLqnY</v>
+        <v>https://www.airbnb.co.uk/rooms/1508080538383464858?viralityEntryPoint=1&amp;unique_share_id=F207E198-E9B9-4D65-89B7-1559903B3C77&amp;slcid=1eba13d36311475d93cfe707ee7c340a&amp;s=76&amp;adults=1&amp;slug=TTXROpB4&amp;source_impression_id=p3_1760963365_P39cHqhtj8jxXxGf</v>
       </c>
       <c r="N19" t="str">
         <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
@@ -59311,10 +58390,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/21e176e0a290e4e7d3bd2f92</v>
-      </c>
-      <c r="M27" t="str">
-        <v>https://www.airbnb.co.uk/rooms/700828081910030606?_set_bev_on_new_domain=1725010189_EAYjkxMTczMzE4Y2&amp;source_impression_id=p3_1725010662_P3Za4HTDg8NM5bnL</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6fa61eff78df8625499c1bce</v>
       </c>
     </row>
     <row r="28">
@@ -59352,7 +58428,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6fa61eff78df8625499c1bce</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/21e176e0a290e4e7d3bd2f92</v>
+      </c>
+      <c r="M28" t="str">
+        <v>https://www.airbnb.co.uk/rooms/700828081910030606?_set_bev_on_new_domain=1725010189_EAYjkxMTczMzE4Y2&amp;source_impression_id=p3_1725010662_P3Za4HTDg8NM5bnL</v>
       </c>
     </row>
     <row r="29">
@@ -60789,7 +59868,7 @@
         <v>https://www.myhomeisyours.co.uk/public/property/676431d127d5845172aed08d</v>
       </c>
       <c r="M58" t="str">
-        <v>https://keapartments.com/properties/bournemouth/</v>
+        <v>https://www.airbnb.co.uk/rooms/823105848999902702?source_impression_id=p3_1763040187_P39WBssyUvP5qJV-</v>
       </c>
       <c r="N58" t="str">
         <v>Chris Watson</v>
@@ -60959,13 +60038,13 @@
         <v>Cranbrook Rd, London SW19 4HD, UK</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62" t="str">
         <v>off-site-chargeable</v>
@@ -60980,16 +60059,16 @@
         <v>0</v>
       </c>
       <c r="J62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
       </c>
       <c r="L62" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/682c4ac0a67e14477a753321</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68387fbf6c2ea1f15bd42377</v>
       </c>
       <c r="M62" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1087629888198354779?source_impression_id=p3_1747732987_P3AxGlRbbJ_Gi-WK</v>
+        <v>https://www.airbnb.co.uk/rooms/1413640443053905185?_set_bev_on_new_domain=1745425402_EAMWRkZDRiZWM0NT&amp;source_impression_id=p3_1748532739_P36oi_SGIFxp4UI8</v>
       </c>
       <c r="N62" t="str">
         <v>Shan</v>
@@ -61009,13 +60088,13 @@
         <v>Cranbrook Rd, London SW19 4HD, UK</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" t="str">
         <v>off-site-chargeable</v>
@@ -61030,16 +60109,16 @@
         <v>0</v>
       </c>
       <c r="J63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68387fbf6c2ea1f15bd42377</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/682c4ac0a67e14477a753321</v>
       </c>
       <c r="M63" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1413640443053905185?_set_bev_on_new_domain=1745425402_EAMWRkZDRiZWM0NT&amp;source_impression_id=p3_1748532739_P36oi_SGIFxp4UI8</v>
+        <v>https://www.airbnb.co.uk/rooms/1087629888198354779?source_impression_id=p3_1747732987_P3AxGlRbbJ_Gi-WK</v>
       </c>
       <c r="N63" t="str">
         <v>Shan</v>
@@ -61846,10 +60925,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SW6 5QQ</v>
+        <v>SW6 5QE</v>
       </c>
       <c r="B81" t="str">
-        <v>Cassidy Rd, London SW6 5QQ, UK</v>
+        <v>Fulham Ct, London SW6 5QE, UK</v>
       </c>
       <c r="C81">
         <v>4</v>
@@ -61870,7 +60949,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
@@ -61879,10 +60958,10 @@
         <v>0</v>
       </c>
       <c r="L81" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6900a9342e7dc87a8799951b</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/69147549be7e6aa6430527cd</v>
       </c>
       <c r="M81" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1072946755416021325?adults=1&amp;check_in=2025-10-28&amp;check_out=2025-11-10&amp;children=5&amp;search_mode=regular_search&amp;infants=0&amp;pets=0&amp;source_impression_id=p3_1761647061_P3HjNMoMSugQ0mBC&amp;previous_page_section_name=1000&amp;federated_search_id=9ea658a4-3c21-4533-9c4d-f99b5bd5629b</v>
+        <v>https://www.airbnb.co.uk/rooms/1532447556406552247?source_impression_id=p3_1762948170_P300eBg5HgsK7Cyj&amp;check_in=2025-11-25&amp;guests=1&amp;adults=1&amp;check_out=2025-12-23</v>
       </c>
       <c r="N81" t="str">
         <v>Airbnb Temporary</v>
@@ -61896,16 +60975,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SW6 6AR</v>
+        <v>SW6 5QQ</v>
       </c>
       <c r="B82" t="str">
-        <v>Crabtree Ln, London, UK</v>
+        <v>Cassidy Rd, London SW6 5QQ, UK</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -61920,7 +60999,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
@@ -61929,36 +61008,36 @@
         <v>0</v>
       </c>
       <c r="L82" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f62a88c22a16f688e0406a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6900a9342e7dc87a8799951b</v>
       </c>
       <c r="M82" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1504462203382166627?viralityEntryPoint=1&amp;unique_share_id=EF5986AF-058B-4129-B2A6-973E7103962D&amp;slcid=66d165c7fb1b4623b2d61fbc7ad32e65&amp;s=76&amp;adults=1&amp;slug=PfGrvi7A&amp;source_impression_id=p3_1760961027_P3ffFFVDnBkN5HJi#_gl=1*1v7wizx*_gcl_aw*R0NMLjE3NTkzOTU5MDAuQ2p3S0NBand4ZmpHQmhBVUVpd0FLV1B3RHI1RjRqTXN1ZkN5N1pCYnNQQ3pSUlo4ZExYd1RFYW5ZTU80dWxFMlY2M3NRSGRJQlRsVXF4b0MwR0FRQXZEX0J3RQ..*_gcl_dc*R0NMLjE3NTkzOTU5MDAuQ2p3S0NBand4ZmpHQmhBVUVpd0FLV1B3RHI1RjRqTXN1ZkN5N1pCYnNQQ3pSUlo4ZExYd1RFYW5ZTU80dWxFMlY2M3NRSGRJQlRsVXF4b0MwR0FRQXZEX0J3RQ..*_gcl_au*MTk4NzkwMjc3Mi4xNzU5MTQ1NjUy*FPAU*MTU4NjI5OTU3NC4xNzU5MTQ1MzE0</v>
+        <v>https://www.airbnb.co.uk/rooms/1072946755416021325?adults=1&amp;check_in=2025-10-28&amp;check_out=2025-11-10&amp;children=5&amp;search_mode=regular_search&amp;infants=0&amp;pets=0&amp;source_impression_id=p3_1761647061_P3HjNMoMSugQ0mBC&amp;previous_page_section_name=1000&amp;federated_search_id=9ea658a4-3c21-4533-9c4d-f99b5bd5629b</v>
       </c>
       <c r="N82" t="str">
-        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O82" t="str">
-        <v>Accommodation@calbrahomes.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P82" t="str">
-        <v>02045784820</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SW6 6NU</v>
+        <v>SW6 6AR</v>
       </c>
       <c r="B83" t="str">
-        <v>Inglethorpe St, London SW6 6NU, UK</v>
+        <v>Crabtree Ln, London, UK</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83" t="str">
         <v>off-site-chargeable</v>
@@ -61967,7 +61046,7 @@
         <v>chargeable</v>
       </c>
       <c r="H83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="b">
         <v>0</v>
@@ -61979,27 +61058,27 @@
         <v>0</v>
       </c>
       <c r="L83" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6900ae272e7dc87a87999dec</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f62a88c22a16f688e0406a</v>
       </c>
       <c r="M83" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1043703968021137591?source_impression_id=p3_1761651623_P39RBu6Tjt6GKck_</v>
+        <v>https://www.airbnb.co.uk/rooms/1504462203382166627?viralityEntryPoint=1&amp;unique_share_id=EF5986AF-058B-4129-B2A6-973E7103962D&amp;slcid=66d165c7fb1b4623b2d61fbc7ad32e65&amp;s=76&amp;adults=1&amp;slug=PfGrvi7A&amp;source_impression_id=p3_1760961027_P3ffFFVDnBkN5HJi#_gl=1*1v7wizx*_gcl_aw*R0NMLjE3NTkzOTU5MDAuQ2p3S0NBand4ZmpHQmhBVUVpd0FLV1B3RHI1RjRqTXN1ZkN5N1pCYnNQQ3pSUlo4ZExYd1RFYW5ZTU80dWxFMlY2M3NRSGRJQlRsVXF4b0MwR0FRQXZEX0J3RQ..*_gcl_dc*R0NMLjE3NTkzOTU5MDAuQ2p3S0NBand4ZmpHQmhBVUVpd0FLV1B3RHI1RjRqTXN1ZkN5N1pCYnNQQ3pSUlo4ZExYd1RFYW5ZTU80dWxFMlY2M3NRSGRJQlRsVXF4b0MwR0FRQXZEX0J3RQ..*_gcl_au*MTk4NzkwMjc3Mi4xNzU5MTQ1NjUy*FPAU*MTU4NjI5OTU3NC4xNzU5MTQ1MzE0</v>
       </c>
       <c r="N83" t="str">
-        <v>London base</v>
+        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
       </c>
       <c r="O83" t="str">
-        <v>guest@londonbase.co</v>
+        <v>Accommodation@calbrahomes.com</v>
       </c>
       <c r="P83" t="str">
-        <v>+4420 3189 1677</v>
+        <v>02045784820</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SW6 6PH</v>
+        <v>SW6 6NU</v>
       </c>
       <c r="B84" t="str">
-        <v>Harbord St, London SW6 6PH, UK</v>
+        <v>Inglethorpe St, London SW6 6NU, UK</v>
       </c>
       <c r="C84">
         <v>4</v>
@@ -62008,7 +61087,7 @@
         <v>4</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" t="str">
         <v>off-site-chargeable</v>
@@ -62029,36 +61108,36 @@
         <v>0</v>
       </c>
       <c r="L84" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67337d2ac8526d02b94951c6</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6900ae272e7dc87a87999dec</v>
       </c>
       <c r="M84" t="str">
-        <v>https://www.airbnb.co.uk/rooms/971073232874583193?source_impression_id=p3_1731426909_P30hgRaZaShwo9jU&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
+        <v>https://www.airbnb.co.uk/rooms/1043703968021137591?source_impression_id=p3_1761651623_P39RBu6Tjt6GKck_</v>
       </c>
       <c r="N84" t="str">
-        <v>Airbnb Temporary</v>
+        <v>London base</v>
       </c>
       <c r="O84" t="str">
-        <v>temp@airbnb.com</v>
+        <v>guest@londonbase.co</v>
       </c>
       <c r="P84" t="str">
-        <v>00000000000</v>
+        <v>+4420 3189 1677</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SW6 6QP</v>
+        <v>SW6 6PH</v>
       </c>
       <c r="B85" t="str">
-        <v>Vera Rd, London SW6 6QP, UK</v>
+        <v>Harbord St, London SW6 6PH, UK</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F85" t="str">
         <v>off-site-chargeable</v>
@@ -62067,7 +61146,7 @@
         <v>chargeable</v>
       </c>
       <c r="H85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -62079,10 +61158,10 @@
         <v>0</v>
       </c>
       <c r="L85" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/689a0a6a150fed15c4e0dc25</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67337d2ac8526d02b94951c6</v>
       </c>
       <c r="M85" t="str">
-        <v>https://www.airbnb.co.uk/rooms/47213959?source_impression_id=p3_1754905791_P3elZ9UPa1plP8X3</v>
+        <v>https://www.airbnb.co.uk/rooms/971073232874583193?source_impression_id=p3_1731426909_P30hgRaZaShwo9jU&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
       </c>
       <c r="N85" t="str">
         <v>Airbnb Temporary</v>
@@ -62096,19 +61175,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SW6 6TB</v>
+        <v>SW6 6QP</v>
       </c>
       <c r="B86" t="str">
-        <v>353 Fulham Palace Rd, London SW6 6TB, UK</v>
+        <v>Vera Rd, London SW6 6QP, UK</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F86" t="str">
         <v>off-site-chargeable</v>
@@ -62120,7 +61199,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
@@ -62129,19 +61208,19 @@
         <v>0</v>
       </c>
       <c r="L86" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/685ad139d1fc77c4876c63f6</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/689a0a6a150fed15c4e0dc25</v>
       </c>
       <c r="M86" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj&amp;source_impression_id=p3_1750782139_P3DWqvFlh4ekiIBJ</v>
+        <v>https://www.airbnb.co.uk/rooms/47213959?source_impression_id=p3_1754905791_P3elZ9UPa1plP8X3</v>
       </c>
       <c r="N86" t="str">
-        <v>Shams</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O86" t="str">
-        <v>info@findyourdwelling.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P86" t="str">
-        <v>020 8087 3161</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="87">
@@ -62149,13 +61228,13 @@
         <v>SW6 6TB</v>
       </c>
       <c r="B87" t="str">
-        <v>353 Fulham Palace Rd, London SW6 6TB, UK</v>
+        <v>Fulham Palace Rd, London SW6 6TB, UK</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -62179,10 +61258,10 @@
         <v>0</v>
       </c>
       <c r="L87" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/685ad138a64d265cf905ab30</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/685526b463fbd51c0f5730ca</v>
       </c>
       <c r="M87" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj&amp;source_impression_id=p3_1750782139_P3DWqvFlh4ekiIBJ</v>
+        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?viralityEntryPoint=1&amp;unique_share_id=831155F4-3E8B-4F5B-99B5-B85FA012CDF0&amp;slcid=2c9a58d13d294393adf98b429bad1477&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=A4rtpP1Q&amp;source_impression_id=p3_1750410709_P34EKQvWdwCAv1zY</v>
       </c>
       <c r="N87" t="str">
         <v>Shams</v>
@@ -62202,10 +61281,10 @@
         <v>Fulham Palace Rd, London SW6 6TB, UK</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88">
         <v>1</v>
@@ -62220,7 +61299,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="b">
         <v>0</v>
@@ -62229,10 +61308,10 @@
         <v>0</v>
       </c>
       <c r="L88" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/685526b463fbd51c0f5730ca</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68551fb2f3cc17e4dacd24b6</v>
       </c>
       <c r="M88" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?viralityEntryPoint=1&amp;unique_share_id=831155F4-3E8B-4F5B-99B5-B85FA012CDF0&amp;slcid=2c9a58d13d294393adf98b429bad1477&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=A4rtpP1Q&amp;source_impression_id=p3_1750410709_P34EKQvWdwCAv1zY</v>
+        <v>https://www.airbnb.co.uk/rooms/1366216563172751118?viralityEntryPoint=1&amp;unique_share_id=556BD062-BF7C-41E1-A851-6C32E37FCD0C&amp;slcid=dc9bb1a712364a48bc98100458db6ad7&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=D5k1pgt8&amp;source_impression_id=p3_1750408921_P3dvLS9C2FNxRatw</v>
       </c>
       <c r="N88" t="str">
         <v>Shams</v>
@@ -62249,10 +61328,10 @@
         <v>SW6 6TB</v>
       </c>
       <c r="B89" t="str">
-        <v>Fulham Palace Rd, London SW6 6TB, UK</v>
+        <v>353 Fulham Palace Rd, London SW6 6TB, UK</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <v>4</v>
@@ -62270,7 +61349,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
@@ -62279,10 +61358,10 @@
         <v>0</v>
       </c>
       <c r="L89" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68551fb2f3cc17e4dacd24b6</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/685ad138a64d265cf905ab30</v>
       </c>
       <c r="M89" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1366216563172751118?viralityEntryPoint=1&amp;unique_share_id=556BD062-BF7C-41E1-A851-6C32E37FCD0C&amp;slcid=dc9bb1a712364a48bc98100458db6ad7&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=D5k1pgt8&amp;source_impression_id=p3_1750408921_P3dvLS9C2FNxRatw</v>
+        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj&amp;source_impression_id=p3_1750782139_P3DWqvFlh4ekiIBJ</v>
       </c>
       <c r="N89" t="str">
         <v>Shams</v>
@@ -62296,31 +61375,31 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SW6 7BX</v>
+        <v>SW6 6TB</v>
       </c>
       <c r="B90" t="str">
-        <v>Parkville Rd, London SW6 7BX, UK</v>
+        <v>353 Fulham Palace Rd, London SW6 6TB, UK</v>
       </c>
       <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90">
         <v>4</v>
       </c>
-      <c r="D90">
-        <v>5</v>
-      </c>
       <c r="E90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F90" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G90" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
@@ -62329,45 +61408,45 @@
         <v>0</v>
       </c>
       <c r="L90" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68d54b78c2535f08cb25db69</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/685ad139d1fc77c4876c63f6</v>
       </c>
       <c r="M90" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1499099822600070432?source_impression_id=p3_1758807966_P3zaf67BtFxgUjVk</v>
+        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj&amp;source_impression_id=p3_1750782139_P3DWqvFlh4ekiIBJ</v>
       </c>
       <c r="N90" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Shams</v>
       </c>
       <c r="O90" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@findyourdwelling.com</v>
       </c>
       <c r="P90" t="str">
-        <v>00000000000</v>
+        <v>020 8087 3161</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SW8 1AE</v>
+        <v>SW6 7BX</v>
       </c>
       <c r="B91" t="str">
-        <v>Beaufoy House, 1 Regents Bridge Gardens, London SW8 1JP, UK</v>
+        <v>Parkville Rd, London SW6 7BX, UK</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G91" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" t="b">
         <v>0</v>
@@ -62379,10 +61458,10 @@
         <v>0</v>
       </c>
       <c r="L91" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ee04a01043b950380eb2fc</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68d54b78c2535f08cb25db69</v>
       </c>
       <c r="M91" t="str">
-        <v>https://www.airbnb.co.uk/rooms/32695038?source_impression_id=p3_1760428843_P3mdse_sv0EsPht8&amp;check_in=2025-10-28&amp;guests=2&amp;adults=2&amp;check_out=2026-01-16</v>
+        <v>https://www.airbnb.co.uk/rooms/1499099822600070432?source_impression_id=p3_1758807966_P3zaf67BtFxgUjVk</v>
       </c>
       <c r="N91" t="str">
         <v>Airbnb Temporary</v>
@@ -62396,10 +61475,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SW8 1NB</v>
+        <v>SW8 1AE</v>
       </c>
       <c r="B92" t="str">
-        <v>Stoddart House, Meadow Rd, London SW8 1ND, UK</v>
+        <v>Beaufoy House, 1 Regents Bridge Gardens, London SW8 1JP, UK</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -62429,10 +61508,10 @@
         <v>0</v>
       </c>
       <c r="L92" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ee210f1e6542cc132ac9cc</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ee04a01043b950380eb2fc</v>
       </c>
       <c r="M92" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1507829464694432386?source_impression_id=p3_1760436284_P3WVnq1rOmh-v0re</v>
+        <v>https://www.airbnb.co.uk/rooms/32695038?source_impression_id=p3_1760428843_P3mdse_sv0EsPht8&amp;check_in=2025-10-28&amp;guests=2&amp;adults=2&amp;check_out=2026-01-16</v>
       </c>
       <c r="N92" t="str">
         <v>Airbnb Temporary</v>
@@ -62446,10 +61525,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SW8 2ED</v>
+        <v>SW8 1NB</v>
       </c>
       <c r="B93" t="str">
-        <v>Lansdowne Way, London, UK</v>
+        <v>Stoddart House, Meadow Rd, London SW8 1ND, UK</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -62479,10 +61558,10 @@
         <v>0</v>
       </c>
       <c r="L93" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ee1f001043b950380f06bf</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ee210f1e6542cc132ac9cc</v>
       </c>
       <c r="M93" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1512292868036967810?source_impression_id=p3_1760435767_P3bry31toK2bC0qU</v>
+        <v>https://www.airbnb.co.uk/rooms/1507829464694432386?source_impression_id=p3_1760436284_P3WVnq1rOmh-v0re</v>
       </c>
       <c r="N93" t="str">
         <v>Airbnb Temporary</v>
@@ -62496,10 +61575,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SW8 2XA</v>
+        <v>SW8 2ED</v>
       </c>
       <c r="B94" t="str">
-        <v>Wilcox Rd, London SW8 2XA, UK</v>
+        <v>Lansdowne Way, London, UK</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -62508,7 +61587,7 @@
         <v>2</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" t="str">
         <v>off-site-chargeable</v>
@@ -62529,19 +61608,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67658b4aaafaba5175a9614b</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ee1f001043b950380f06bf</v>
       </c>
       <c r="M94" t="str">
-        <v>https://nq.hostify.club/listing/144286</v>
+        <v>https://www.airbnb.co.uk/rooms/1512292868036967810?source_impression_id=p3_1760435767_P3bry31toK2bC0qU</v>
       </c>
       <c r="N94" t="str">
-        <v>Shloime</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O94" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P94" t="str">
-        <v>07867290839</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="95">
@@ -62552,10 +61631,10 @@
         <v>Wilcox Rd, London SW8 2XA, UK</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -62579,10 +61658,10 @@
         <v>0</v>
       </c>
       <c r="L95" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67658f67631e063f5b98344f</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67659252631e063f5b9834bb</v>
       </c>
       <c r="M95" t="str">
-        <v>https://nq.hostify.club/listing/144285</v>
+        <v>https://nq.hostify.club/listing/87523</v>
       </c>
       <c r="N95" t="str">
         <v>Shloime</v>
@@ -62602,10 +61681,10 @@
         <v>Wilcox Rd, London SW8 2XA, UK</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96">
         <v>1</v>
@@ -62629,10 +61708,10 @@
         <v>0</v>
       </c>
       <c r="L96" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67659252631e063f5b9834bb</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67658f67631e063f5b98344f</v>
       </c>
       <c r="M96" t="str">
-        <v>https://nq.hostify.club/listing/87523</v>
+        <v>https://nq.hostify.club/listing/144285</v>
       </c>
       <c r="N96" t="str">
         <v>Shloime</v>
@@ -62646,19 +61725,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SW8 4XF</v>
+        <v>SW8 2XA</v>
       </c>
       <c r="B97" t="str">
-        <v>Deeley Rd, Nine Elms, London SW8 4XF, UK</v>
+        <v>Wilcox Rd, London SW8 2XA, UK</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" t="str">
         <v>off-site-chargeable</v>
@@ -62679,33 +61758,33 @@
         <v>0</v>
       </c>
       <c r="L97" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/285def14972d9284bf019172</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67658b4aaafaba5175a9614b</v>
       </c>
       <c r="M97" t="str">
-        <v>https://abnb.me/LIMHw5CTtGb</v>
+        <v>https://nq.hostify.club/listing/144286</v>
       </c>
       <c r="N97" t="str">
-        <v>Ayang</v>
+        <v>Shloime</v>
       </c>
       <c r="O97" t="str">
-        <v>hello@bookthatstay.com</v>
+        <v>shloime@hometohost.co.uk</v>
       </c>
       <c r="P97" t="str">
-        <v>07837424985</v>
+        <v>07867290839</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SW8 4XX</v>
+        <v>SW8 4XF</v>
       </c>
       <c r="B98" t="str">
-        <v>Thessaly Rd, Nine Elms, London SW8 4XX, UK</v>
+        <v>Deeley Rd, Nine Elms, London SW8 4XF, UK</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -62729,33 +61808,33 @@
         <v>0</v>
       </c>
       <c r="L98" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/687fa7d41ea8b1a0f73095a8</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/285def14972d9284bf019172</v>
       </c>
       <c r="M98" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1433251646793494676?source_impression_id=p3_1753196080_P3zRtJexIYtWIN4E</v>
+        <v>https://abnb.me/LIMHw5CTtGb</v>
       </c>
       <c r="N98" t="str">
-        <v>Toyin Ogunwomoju</v>
+        <v>Ayang</v>
       </c>
       <c r="O98" t="str">
-        <v>email@emaaaail.com</v>
+        <v>hello@bookthatstay.com</v>
       </c>
       <c r="P98" t="str">
-        <v>07835788872</v>
+        <v>07837424985</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sw18 5na</v>
+        <v>SW8 4XX</v>
       </c>
       <c r="B99" t="str">
-        <v>Pirbright Rd, London SW18 5NA, UK</v>
+        <v>Thessaly Rd, Nine Elms, London SW8 4XX, UK</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -62779,36 +61858,36 @@
         <v>0</v>
       </c>
       <c r="L99" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67ebc6df633e1298a40ad537</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/687fa7d41ea8b1a0f73095a8</v>
       </c>
       <c r="M99" t="str">
-        <v>https://www.airbnb.co.uk/rooms/34944409?source_impression_id=p3_1743504960_P3qhXgZQW46E1oZt</v>
+        <v>https://www.airbnb.co.uk/rooms/1433251646793494676?source_impression_id=p3_1753196080_P3zRtJexIYtWIN4E</v>
       </c>
       <c r="N99" t="str">
-        <v>Mo</v>
+        <v>Toyin Ogunwomoju</v>
       </c>
       <c r="O99" t="str">
-        <v>info@milamanagement.co.uk</v>
+        <v>email@emaaaail.com</v>
       </c>
       <c r="P99" t="str">
-        <v>+447888003322</v>
+        <v>07835788872</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>TW1 1AX</v>
+        <v>Sw18 5na</v>
       </c>
       <c r="B100" t="str">
-        <v>Brewery Ln, Twickenham TW1, UK</v>
+        <v>Pirbright Rd, London SW18 5NA, UK</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" t="str">
         <v>off-site-chargeable</v>
@@ -62829,45 +61908,45 @@
         <v>0</v>
       </c>
       <c r="L100" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e531264742d568c76f4356</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67ebc6df633e1298a40ad537</v>
       </c>
       <c r="M100" t="str">
-        <v>https://vantageapartments.com/apartments/twickenham-wharf-house/</v>
+        <v>https://www.airbnb.co.uk/rooms/34944409?source_impression_id=p3_1743504960_P3qhXgZQW46E1oZt</v>
       </c>
       <c r="N100" t="str">
-        <v xml:space="preserve">Chris </v>
+        <v>Mo</v>
       </c>
       <c r="O100" t="str">
-        <v>res@vantageapartments.com</v>
+        <v>info@milamanagement.co.uk</v>
       </c>
       <c r="P100" t="str">
-        <v>07887954582</v>
+        <v>+447888003322</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>TW1 1ET</v>
+        <v>TW1 1AX</v>
       </c>
       <c r="B101" t="str">
-        <v>Burnside Cl, Twickenham TW1 1ET, UK</v>
+        <v>Brewery Ln, Twickenham TW1, UK</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F101" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G101" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="b">
         <v>0</v>
@@ -62879,33 +61958,42 @@
         <v>0</v>
       </c>
       <c r="L101" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67503f12fa4913aaece1d932</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e531264742d568c76f4356</v>
       </c>
       <c r="M101" t="str">
-        <v>https://www.airbnb.co.uk/rooms/14245764?source_impression_id=p3_1733311223_P3GMFtjyu9hp8_on</v>
+        <v>https://vantageapartments.com/apartments/twickenham-wharf-house/</v>
+      </c>
+      <c r="N101" t="str">
+        <v xml:space="preserve">Chris </v>
+      </c>
+      <c r="O101" t="str">
+        <v>res@vantageapartments.com</v>
+      </c>
+      <c r="P101" t="str">
+        <v>07887954582</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>TW1 2HN</v>
+        <v>TW1 1ET</v>
       </c>
       <c r="B102" t="str">
-        <v>27 Cambridge Rd, Twickenham TW1 2HN, UK</v>
+        <v>Burnside Cl, Twickenham TW1 1ET, UK</v>
       </c>
       <c r="C102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E102">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F102" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G102" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -62914,42 +62002,33 @@
         <v>0</v>
       </c>
       <c r="J102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/690b296a6e4f26241d07138d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67503f12fa4913aaece1d932</v>
       </c>
       <c r="M102" t="str">
-        <v>https://www.airbnb.co.uk/rooms/10328522?source_impression_id=p3_1762338948_P3m61HyGXUPit5Ld&amp;check_in=2026-01-23&amp;guests=3&amp;adults=3&amp;check_out=2026-03-23&amp;pets=1</v>
-      </c>
-      <c r="N102" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-      <c r="O102" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="P102" t="str">
-        <v>00000000000</v>
+        <v>https://www.airbnb.co.uk/rooms/14245764?source_impression_id=p3_1733311223_P3GMFtjyu9hp8_on</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>TW1 3SX</v>
+        <v>TW1 2HN</v>
       </c>
       <c r="B103" t="str">
-        <v>London Rd, Twickenham TW1 3SX, UK</v>
+        <v>27 Cambridge Rd, Twickenham TW1 2HN, UK</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="str">
         <v>off-site-chargeable</v>
@@ -62958,60 +62037,60 @@
         <v>chargeable</v>
       </c>
       <c r="H103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e53fe990b22e68a29caa77</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/690b296a6e4f26241d07138d</v>
       </c>
       <c r="M103" t="str">
-        <v>https://vantageapartments.com/apartments/twickenham-2-beds/</v>
+        <v>https://www.airbnb.co.uk/rooms/10328522?source_impression_id=p3_1762338948_P3m61HyGXUPit5Ld&amp;check_in=2026-01-23&amp;guests=3&amp;adults=3&amp;check_out=2026-03-23&amp;pets=1</v>
       </c>
       <c r="N103" t="str">
-        <v>Chris</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O103" t="str">
-        <v>info@finestay.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P103" t="str">
-        <v>+447514511518</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>TW10 5DF</v>
+        <v>TW1 3SX</v>
       </c>
       <c r="B104" t="str">
-        <v>Sheen Ct Rd, Richmond TW10 5DF, UK</v>
+        <v>London Rd, Twickenham TW1 3SX, UK</v>
       </c>
       <c r="C104">
         <v>2</v>
       </c>
       <c r="D104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F104" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G104" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
       </c>
       <c r="I104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="b">
         <v>0</v>
@@ -63020,42 +62099,42 @@
         <v>0</v>
       </c>
       <c r="L104" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/683973c04c57ed8b6ad53947</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e53fe990b22e68a29caa77</v>
       </c>
       <c r="M104" t="str">
-        <v>https://www.airbnb.co.uk/rooms/673889680829042157?source_impression_id=p3_1748595425_P3D00UuVeB-5YFVu</v>
+        <v>https://vantageapartments.com/apartments/twickenham-2-beds/</v>
       </c>
       <c r="N104" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Chris</v>
       </c>
       <c r="O104" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@finestay.co.uk</v>
       </c>
       <c r="P104" t="str">
-        <v>00000000000</v>
+        <v>+447514511518</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>TW10 5LF</v>
+        <v>TW10 5DF</v>
       </c>
       <c r="B105" t="str">
-        <v>Dryden Court, Parkleys, Richmond TW10 5LJ, UK</v>
+        <v>Sheen Ct Rd, Richmond TW10 5DF, UK</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F105" t="str">
-        <v>off-site-free</v>
+        <v>on-site-free</v>
       </c>
       <c r="G105" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
@@ -63070,39 +62149,39 @@
         <v>0</v>
       </c>
       <c r="L105" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/673f14f4a41ba7207348675d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/683973c04c57ed8b6ad53947</v>
       </c>
       <c r="M105" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1287693453607613837?adults=2&amp;children=1&amp;location=Twickenham%20TW2%205FN%2C%20UK&amp;search_mode=regular_search&amp;check_in=2024-11-25&amp;check_out=2024-12-23&amp;source_impression_id=p3_1732186595_P3eSRUQvTWhYcsu-&amp;previous_page_section_name=1001&amp;federated_search_id=016b6fdd-04c0-4251-a230-0722be645c90</v>
+        <v>https://www.airbnb.co.uk/rooms/673889680829042157?source_impression_id=p3_1748595425_P3D00UuVeB-5YFVu</v>
       </c>
       <c r="N105" t="str">
-        <v>Fiona Teddington</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O105" t="str">
-        <v>fiona@headingtons.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P105" t="str">
-        <v>07769 696464</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TW10 6NQ</v>
+        <v>TW10 5LF</v>
       </c>
       <c r="B106" t="str">
-        <v>Friars Stile Rd, Richmond TW10 6NQ, UK</v>
+        <v>Dryden Court, Parkleys, Richmond TW10 5LJ, UK</v>
       </c>
       <c r="C106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F106" t="str">
-        <v>off-site-chargeable</v>
+        <v>off-site-free</v>
       </c>
       <c r="G106" t="str">
         <v>chargeable</v>
@@ -63120,42 +62199,42 @@
         <v>0</v>
       </c>
       <c r="L106" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/690b23376e4f26241d0700f0</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/673f14f4a41ba7207348675d</v>
       </c>
       <c r="M106" t="str">
-        <v>https://www.airbnb.co.uk/rooms/6131981?source_impression_id=p3_1762337183_P3B65amILc_FLAcx&amp;check_in=2026-01-23&amp;guests=3&amp;adults=3&amp;check_out=2026-03-23&amp;pets=1</v>
+        <v>https://www.airbnb.co.uk/rooms/1287693453607613837?adults=2&amp;children=1&amp;location=Twickenham%20TW2%205FN%2C%20UK&amp;search_mode=regular_search&amp;check_in=2024-11-25&amp;check_out=2024-12-23&amp;source_impression_id=p3_1732186595_P3eSRUQvTWhYcsu-&amp;previous_page_section_name=1001&amp;federated_search_id=016b6fdd-04c0-4251-a230-0722be645c90</v>
       </c>
       <c r="N106" t="str">
-        <v>James Higges Malynn</v>
+        <v>Fiona Teddington</v>
       </c>
       <c r="O106" t="str">
-        <v>jameshiggesmalynn@gmail.com</v>
+        <v>fiona@headingtons.com</v>
       </c>
       <c r="P106" t="str">
-        <v>07775864431</v>
+        <v>07769 696464</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>TW2 6AD</v>
+        <v>TW10 6NQ</v>
       </c>
       <c r="B107" t="str">
-        <v>151 Ellerman Ave, Twickenham TW2 6AD, UK</v>
+        <v>Friars Stile Rd, Richmond TW10 6NQ, UK</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F107" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G107" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
@@ -63170,39 +62249,39 @@
         <v>0</v>
       </c>
       <c r="L107" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6890bc4d5076d27437bbe987</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/690b23376e4f26241d0700f0</v>
       </c>
       <c r="M107" t="str">
-        <v>https://www.booking.com/hotel/gb/large-one-bedroom-flat-in-london-twickenham-with-free-parking.en-gb.html?aid=304142&amp;label=gen173nr-10CAsoUEI9bGFyZ2Utb25lLWJlZHJvb20tZmxhdC1pbi1sb25kb24tdHdpY2tlbmhhbS13aXRoLWZyZWUtcGFya2luZ0gJWARoaYgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAagCAbgCrfTCxAbAAgHSAiQxMDk3ZWQzOS01YjQ2LTQxZTQtYWMzNS04YjYyYWFiYjM5MTjYAgHgAgE&amp;sid=7c380fb8cafd8760226e8cee0417ae8a&amp;all_sr_blocks=1197316701_403932345_1_0_0_706331&amp;checkin=2025-08-17&amp;checkout=2025-08-24&amp;dist=0&amp;group_adults=1&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1197316701_403932345_1_0_0_706331&amp;hpos=1&amp;matching_block_id=1197316701_403932345_1_0_0_706331&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=1&amp;req_adults=1&amp;req_children=0&amp;room1=A&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=1197316701_403932345_1_0_0_706331_58441&amp;srepoch=1754315309&amp;srpvid=d42e97c4701d325dac390210bafaa6cd&amp;type=total&amp;ucfs=1&amp;</v>
+        <v>https://www.airbnb.co.uk/rooms/6131981?source_impression_id=p3_1762337183_P3B65amILc_FLAcx&amp;check_in=2026-01-23&amp;guests=3&amp;adults=3&amp;check_out=2026-03-23&amp;pets=1</v>
       </c>
       <c r="N107" t="str">
-        <v>Booking.Com Temporary</v>
+        <v>James Higges Malynn</v>
       </c>
       <c r="O107" t="str">
-        <v>fake@booking.com</v>
+        <v>jameshiggesmalynn@gmail.com</v>
       </c>
       <c r="P107" t="str">
-        <v>00000000000</v>
+        <v>07775864431</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>TW2 6QW</v>
+        <v>TW2 6AD</v>
       </c>
       <c r="B108" t="str">
-        <v>1a May Rd, London, Twickenham TW2 6QW, UK</v>
+        <v>151 Ellerman Ave, Twickenham TW2 6AD, UK</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G108" t="str">
         <v>no</v>
@@ -63220,10 +62299,10 @@
         <v>0</v>
       </c>
       <c r="L108" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e669cf5a715acf5518c7b5</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6890bc4d5076d27437bbe987</v>
       </c>
       <c r="M108" t="str">
-        <v>https://www.booking.com/hotel/gb/modern-stylish-townhouse.en-gb.html?aid=304142&amp;label=gen173rf-10CAQoggJCKnNlYXJjaF9lbG10cmVlK3JkLCt0ZWRkaW5ndG9uK3R3MTErOHN0LCt1a0gJWANoUIgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAaICE215aG9tZWlzeW91cnMuY28udWuoAgG4Ar32mMcGwAIB0gIkNTkxYzEwYzctNTViNy00ZWM1LWIyMzMtZmI5ZTFkMTI2YzZh2AIB4AIB&amp;sid=325a167012db26cb7644e17756f19220&amp;age=15&amp;age=15&amp;age=15&amp;all_sr_blocks=903932101_366522376_5_0_0&amp;checkin=2025-10-09&amp;checkout=2025-10-16&amp;dist=0&amp;group_adults=1&amp;group_children=3&amp;hapos=1&amp;highlighted_blocks=903932101_366522376_5_0_0&amp;hpos=1&amp;matching_block_id=903932101_366522376_5_0_0&amp;nflt=distance%3D3220&amp;no_rooms=1&amp;req_adults=1&amp;req_age=15&amp;req_age=15&amp;req_age=15&amp;req_children=3&amp;room1=A%2C15%2C15%2C15&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=903932101_366522376_5_0_0__214500&amp;srepoch=1759919013&amp;srpvid=b705490de835031e&amp;type=total&amp;ucfs=1&amp;#availability</v>
+        <v>https://www.booking.com/hotel/gb/large-one-bedroom-flat-in-london-twickenham-with-free-parking.en-gb.html?aid=304142&amp;label=gen173nr-10CAsoUEI9bGFyZ2Utb25lLWJlZHJvb20tZmxhdC1pbi1sb25kb24tdHdpY2tlbmhhbS13aXRoLWZyZWUtcGFya2luZ0gJWARoaYgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAagCAbgCrfTCxAbAAgHSAiQxMDk3ZWQzOS01YjQ2LTQxZTQtYWMzNS04YjYyYWFiYjM5MTjYAgHgAgE&amp;sid=7c380fb8cafd8760226e8cee0417ae8a&amp;all_sr_blocks=1197316701_403932345_1_0_0_706331&amp;checkin=2025-08-17&amp;checkout=2025-08-24&amp;dist=0&amp;group_adults=1&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1197316701_403932345_1_0_0_706331&amp;hpos=1&amp;matching_block_id=1197316701_403932345_1_0_0_706331&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=1&amp;req_adults=1&amp;req_children=0&amp;room1=A&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=1197316701_403932345_1_0_0_706331_58441&amp;srepoch=1754315309&amp;srpvid=d42e97c4701d325dac390210bafaa6cd&amp;type=total&amp;ucfs=1&amp;</v>
       </c>
       <c r="N108" t="str">
         <v>Booking.Com Temporary</v>
@@ -63237,25 +62316,25 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>TW2 7AJ</v>
+        <v>TW2 6QW</v>
       </c>
       <c r="B109" t="str">
-        <v>Nelson Rd TW2 7AJ</v>
+        <v>1a May Rd, London, Twickenham TW2 6QW, UK</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E109">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F109" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G109" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
@@ -63270,27 +62349,27 @@
         <v>0</v>
       </c>
       <c r="L109" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/59d73edef15abbc0bbd7b735</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e669cf5a715acf5518c7b5</v>
       </c>
       <c r="M109" t="str">
-        <v>https://air.tl/LNCnb516</v>
+        <v>https://www.booking.com/hotel/gb/modern-stylish-townhouse.en-gb.html?aid=304142&amp;label=gen173rf-10CAQoggJCKnNlYXJjaF9lbG10cmVlK3JkLCt0ZWRkaW5ndG9uK3R3MTErOHN0LCt1a0gJWANoUIgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAaICE215aG9tZWlzeW91cnMuY28udWuoAgG4Ar32mMcGwAIB0gIkNTkxYzEwYzctNTViNy00ZWM1LWIyMzMtZmI5ZTFkMTI2YzZh2AIB4AIB&amp;sid=325a167012db26cb7644e17756f19220&amp;age=15&amp;age=15&amp;age=15&amp;all_sr_blocks=903932101_366522376_5_0_0&amp;checkin=2025-10-09&amp;checkout=2025-10-16&amp;dist=0&amp;group_adults=1&amp;group_children=3&amp;hapos=1&amp;highlighted_blocks=903932101_366522376_5_0_0&amp;hpos=1&amp;matching_block_id=903932101_366522376_5_0_0&amp;nflt=distance%3D3220&amp;no_rooms=1&amp;req_adults=1&amp;req_age=15&amp;req_age=15&amp;req_age=15&amp;req_children=3&amp;room1=A%2C15%2C15%2C15&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=903932101_366522376_5_0_0__214500&amp;srepoch=1759919013&amp;srpvid=b705490de835031e&amp;type=total&amp;ucfs=1&amp;#availability</v>
       </c>
       <c r="N109" t="str">
-        <v>Daniella</v>
+        <v>Booking.Com Temporary</v>
       </c>
       <c r="O109" t="str">
-        <v>fake@regalstay.co.uk</v>
+        <v>fake@booking.com</v>
       </c>
       <c r="P109" t="str">
-        <v>07588733241</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>TW9 1UP</v>
+        <v>TW2 7AJ</v>
       </c>
       <c r="B110" t="str">
-        <v>Sheen Park, Richmond TW9 1UP, UK</v>
+        <v>Nelson Rd TW2 7AJ</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -63299,7 +62378,7 @@
         <v>1</v>
       </c>
       <c r="E110">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F110" t="str">
         <v>off-site-chargeable</v>
@@ -63320,27 +62399,27 @@
         <v>0</v>
       </c>
       <c r="L110" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68499aafab93726599bbdc3a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/59d73edef15abbc0bbd7b735</v>
       </c>
       <c r="M110" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1352162318526789141?adults=2&amp;check_in=2025-06-15&amp;check_out=2025-06-26&amp;location=TW9%204QQ&amp;search_mode=regular_search&amp;source_impression_id=p3_1748527649_P3gObTFTw4qoUYJu&amp;previous_page_section_name=1001&amp;federated_search_id=f6fcb773-7310-4092-a5b2-0b0400d495f7</v>
+        <v>https://air.tl/LNCnb516</v>
       </c>
       <c r="N110" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Daniella</v>
       </c>
       <c r="O110" t="str">
-        <v>temp@airbnb.com</v>
+        <v>fake@regalstay.co.uk</v>
       </c>
       <c r="P110" t="str">
-        <v>00000000000</v>
+        <v>07588733241</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>TW9 1YA</v>
+        <v>TW9 1UP</v>
       </c>
       <c r="B111" t="str">
-        <v>Manor Rd., Richmond TW9 1YA, UK</v>
+        <v>Sheen Park, Richmond TW9 1UP, UK</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -63352,13 +62431,13 @@
         <v>1</v>
       </c>
       <c r="F111" t="str">
-        <v>off-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G111" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -63370,10 +62449,10 @@
         <v>0</v>
       </c>
       <c r="L111" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68a48edcb70315aefd180cc5</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68499aafab93726599bbdc3a</v>
       </c>
       <c r="M111" t="str">
-        <v>https://www.airbnb.co.uk/rooms/48657532?adults=1&amp;check_in=2025-09-07&amp;check_out=2025-10-05&amp;search_mode=regular_search&amp;source_impression_id=p3_1755614553_P3ukIx0sYBmgXqRE&amp;previous_page_section_name=1000&amp;federated_search_id=f24e86bf-2b74-4122-b727-6745f41a15f1</v>
+        <v>https://www.airbnb.co.uk/rooms/1352162318526789141?adults=2&amp;check_in=2025-06-15&amp;check_out=2025-06-26&amp;location=TW9%204QQ&amp;search_mode=regular_search&amp;source_impression_id=p3_1748527649_P3gObTFTw4qoUYJu&amp;previous_page_section_name=1001&amp;federated_search_id=f6fcb773-7310-4092-a5b2-0b0400d495f7</v>
       </c>
       <c r="N111" t="str">
         <v>Airbnb Temporary</v>
@@ -63387,28 +62466,28 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>TW9 1YJ</v>
+        <v>TW9 1YA</v>
       </c>
       <c r="B112" t="str">
-        <v>Sheen Rd, Richmond TW9 1YJ, UK</v>
+        <v>Manor Rd., Richmond TW9 1YA, UK</v>
       </c>
       <c r="C112">
         <v>1</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>1</v>
       </c>
       <c r="F112" t="str">
-        <v>off-site-chargeable</v>
+        <v>off-site-free</v>
       </c>
       <c r="G112" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="b">
         <v>0</v>
@@ -63420,36 +62499,36 @@
         <v>0</v>
       </c>
       <c r="L112" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6893273aee11b286d6069d02</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68a48edcb70315aefd180cc5</v>
       </c>
       <c r="M112" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1477591205589843186?adults=1&amp;infants=1&amp;location=Melliss%20Avenue%2C%20Richmond%20TW9%204BF&amp;search_mode=regular_search&amp;source_impression_id=p3_1754411594_P3BbX2nMh-WG77LT&amp;previous_page_section_name=1001&amp;federated_search_id=69450dfd-662d-4ca9-8f69-ac92a539e93f&amp;guests=1</v>
+        <v>https://www.airbnb.co.uk/rooms/48657532?adults=1&amp;check_in=2025-09-07&amp;check_out=2025-10-05&amp;search_mode=regular_search&amp;source_impression_id=p3_1755614553_P3ukIx0sYBmgXqRE&amp;previous_page_section_name=1000&amp;federated_search_id=f24e86bf-2b74-4122-b727-6745f41a15f1</v>
       </c>
       <c r="N112" t="str">
-        <v>Stress Free Homes</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O112" t="str">
-        <v>enquiries@yourstressfreeproperties.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P112" t="str">
-        <v>020 3488 9972</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>TW9 2HN</v>
+        <v>TW9 1YJ</v>
       </c>
       <c r="B113" t="str">
-        <v>Stanmore Gardens, Richmond TW9 2HN, UK</v>
+        <v>Sheen Rd, Richmond TW9 1YJ, UK</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" t="str">
         <v>off-site-chargeable</v>
@@ -63458,45 +62537,45 @@
         <v>chargeable</v>
       </c>
       <c r="H113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="b">
         <v>0</v>
       </c>
       <c r="J113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/690c66323c528d855ec7b238</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6893273aee11b286d6069d02</v>
       </c>
       <c r="M113" t="str">
-        <v>https://www.airbnb.co.uk/rooms/643556548223968524?source_impression_id=p3_1762419895_P3NGJkno2kkUO9E_</v>
+        <v>https://www.airbnb.co.uk/rooms/1477591205589843186?adults=1&amp;infants=1&amp;location=Melliss%20Avenue%2C%20Richmond%20TW9%204BF&amp;search_mode=regular_search&amp;source_impression_id=p3_1754411594_P3BbX2nMh-WG77LT&amp;previous_page_section_name=1001&amp;federated_search_id=69450dfd-662d-4ca9-8f69-ac92a539e93f&amp;guests=1</v>
       </c>
       <c r="N113" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Stress Free Homes</v>
       </c>
       <c r="O113" t="str">
-        <v>temp@airbnb.com</v>
+        <v>enquiries@yourstressfreeproperties.com</v>
       </c>
       <c r="P113" t="str">
-        <v>00000000000</v>
+        <v>020 3488 9972</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>W12 7BT</v>
+        <v>TW9 2HN</v>
       </c>
       <c r="B114" t="str">
-        <v>Bloemfontein Rd, London W12 7BT, UK</v>
+        <v>Stanmore Gardens, Richmond TW9 2HN, UK</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E114">
         <v>2</v>
@@ -63508,22 +62587,22 @@
         <v>chargeable</v>
       </c>
       <c r="H114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="b">
         <v>0</v>
       </c>
       <c r="J114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68275e86976de26b249e7b25</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/690c66323c528d855ec7b238</v>
       </c>
       <c r="M114" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1369060821699399859?source_impression_id=p3_1747410227_P3EjSWJPblet4bzY</v>
+        <v>https://www.airbnb.co.uk/rooms/643556548223968524?source_impression_id=p3_1762419895_P3NGJkno2kkUO9E_</v>
       </c>
       <c r="N114" t="str">
         <v>Airbnb Temporary</v>
@@ -63537,19 +62616,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>W12 7DP</v>
+        <v>W12 7BT</v>
       </c>
       <c r="B115" t="str">
-        <v>Wood Ln, London W12 7DP, UK</v>
+        <v>Bloemfontein Rd, London W12 7BT, UK</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" t="str">
         <v>off-site-chargeable</v>
@@ -63570,10 +62649,10 @@
         <v>0</v>
       </c>
       <c r="L115" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6808b4568f291c91ba324822</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68275e86976de26b249e7b25</v>
       </c>
       <c r="M115" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1262304556462702075?source_impression_id=p3_1745400881_P3248y-DWTiJCqcM</v>
+        <v>https://www.airbnb.co.uk/rooms/1369060821699399859?source_impression_id=p3_1747410227_P3EjSWJPblet4bzY</v>
       </c>
       <c r="N115" t="str">
         <v>Airbnb Temporary</v>
@@ -63587,16 +62666,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>W12 7EN</v>
+        <v>W12 7DP</v>
       </c>
       <c r="B116" t="str">
-        <v>Bakery House, 2A Loftus Rd, Greater, London W12 7EN, UK</v>
+        <v>Wood Ln, London W12 7DP, UK</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -63605,7 +62684,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G116" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H116" t="b">
         <v>0</v>
@@ -63620,27 +62699,27 @@
         <v>0</v>
       </c>
       <c r="L116" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68aeeca46ecc2a70681e8fb6</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6808b4568f291c91ba324822</v>
       </c>
       <c r="M116" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1427356510827612998?adults=3&amp;check_in=2025-08-10&amp;check_out=2025-08-15&amp;search_mode=regular_search&amp;source_impression_id=p3_1749545813_P3GO8TG-fJu7iQB0&amp;previous_page_section_name=1000&amp;federated_search_id=3376fb03-300d-4453-b532-0a265f06f74d&amp;_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj</v>
+        <v>https://www.airbnb.co.uk/rooms/1262304556462702075?source_impression_id=p3_1745400881_P3248y-DWTiJCqcM</v>
       </c>
       <c r="N116" t="str">
-        <v>Mark Hudson | Nestor Stay</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O116" t="str">
-        <v>corporate@nestorstay.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P116" t="str">
-        <v>0203 695 1065</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>W12 7LZ</v>
+        <v>W12 7EN</v>
       </c>
       <c r="B117" t="str">
-        <v>MacKenzie Cl, London W12 7LZ, UK</v>
+        <v>Bakery House, 2A Loftus Rd, Greater, London W12 7EN, UK</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -63649,13 +62728,13 @@
         <v>2</v>
       </c>
       <c r="E117">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F117" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G117" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
@@ -63670,36 +62749,36 @@
         <v>0</v>
       </c>
       <c r="L117" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68271847e8098e7bbe61ae18</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68aeeca46ecc2a70681e8fb6</v>
       </c>
       <c r="M117" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1299926267625673607?source_impression_id=p3_1747390962_P3A7UrRiMm-pAV2r</v>
+        <v>https://www.airbnb.co.uk/rooms/1427356510827612998?adults=3&amp;check_in=2025-08-10&amp;check_out=2025-08-15&amp;search_mode=regular_search&amp;source_impression_id=p3_1749545813_P3GO8TG-fJu7iQB0&amp;previous_page_section_name=1000&amp;federated_search_id=3376fb03-300d-4453-b532-0a265f06f74d&amp;_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj</v>
       </c>
       <c r="N117" t="str">
-        <v>Gerda &amp; Chris</v>
+        <v>Mark Hudson | Nestor Stay</v>
       </c>
       <c r="O117" t="str">
-        <v>hello@nournestapartments.com</v>
+        <v>corporate@nestorstay.com</v>
       </c>
       <c r="P117" t="str">
-        <v xml:space="preserve"> +44 208 064 0268</v>
+        <v>0203 695 1065</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>W12 7QZ</v>
+        <v>W12 7LZ</v>
       </c>
       <c r="B118" t="str">
-        <v>36 Dunraven Road, Shepherd's Bush, London, W12 7QZ</v>
+        <v>MacKenzie Cl, London W12 7LZ, UK</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F118" t="str">
         <v>off-site-chargeable</v>
@@ -63720,33 +62799,33 @@
         <v>0</v>
       </c>
       <c r="L118" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66c831222034c569bc234fab</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68271847e8098e7bbe61ae18</v>
       </c>
       <c r="M118" t="str">
-        <v>https://www.airbnb.com/rooms/1154551953402165238?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=624645d7-d6f3-4145-999f-0a74538bf77f&amp;source_impression_id=p3_1715708177_pd0Y0%2FRJ0wWn1hXa</v>
+        <v>https://www.airbnb.co.uk/rooms/1299926267625673607?source_impression_id=p3_1747390962_P3A7UrRiMm-pAV2r</v>
       </c>
       <c r="N118" t="str">
-        <v>Dolly</v>
+        <v>Gerda &amp; Chris</v>
       </c>
       <c r="O118" t="str">
-        <v>info@citygateproperty.com</v>
+        <v>hello@nournestapartments.com</v>
       </c>
       <c r="P118" t="str">
-        <v>07958 571 307</v>
+        <v xml:space="preserve"> +44 208 064 0268</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>W12 7SF</v>
+        <v>W12 7QZ</v>
       </c>
       <c r="B119" t="str">
-        <v>Fountain Park Wy, London W12, UK</v>
+        <v>36 Dunraven Road, Shepherd's Bush, London, W12 7QZ</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119">
         <v>2</v>
@@ -63770,42 +62849,42 @@
         <v>0</v>
       </c>
       <c r="L119" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68bed9c329edaa5d143ebb98</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/66c831222034c569bc234fab</v>
       </c>
       <c r="M119" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1478234898769467858?source_impression_id=p3_1757337796_P3k3cbuyZDmInulR</v>
+        <v>https://www.airbnb.com/rooms/1154551953402165238?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=624645d7-d6f3-4145-999f-0a74538bf77f&amp;source_impression_id=p3_1715708177_pd0Y0%2FRJ0wWn1hXa</v>
       </c>
       <c r="N119" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Dolly</v>
       </c>
       <c r="O119" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@citygateproperty.com</v>
       </c>
       <c r="P119" t="str">
-        <v>00000000000</v>
+        <v>07958 571 307</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>W12 8LQ</v>
+        <v>W12 7SF</v>
       </c>
       <c r="B120" t="str">
-        <v>2, 11 Richmond Way, London W12 8LQ, UK</v>
+        <v>Fountain Park Wy, London W12, UK</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G120" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
@@ -63820,36 +62899,36 @@
         <v>0</v>
       </c>
       <c r="L120" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/684192d86e40fb463e0c7ea1</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68bed9c329edaa5d143ebb98</v>
       </c>
       <c r="M120" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1399201898792819142?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=aa839f79-dbd8-4fd0-868c-739405e0b33e&amp;source_impression_id=p3_1749127712_P3eR1pth3FE1L7T3</v>
+        <v>https://www.airbnb.co.uk/rooms/1478234898769467858?source_impression_id=p3_1757337796_P3k3cbuyZDmInulR</v>
       </c>
       <c r="N120" t="str">
-        <v>Fernando</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O120" t="str">
-        <v>info@urbanview-rentals.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P120" t="str">
-        <v>07946446163</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>W14 8AS</v>
+        <v>W12 8LQ</v>
       </c>
       <c r="B121" t="str">
-        <v>147A Holland Rd, London W14 8AS, UK</v>
+        <v>2, 11 Richmond Way, London W12 8LQ, UK</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" t="str">
         <v>off-site-chargeable</v>
@@ -63858,7 +62937,7 @@
         <v>no</v>
       </c>
       <c r="H121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" t="b">
         <v>0</v>
@@ -63870,18 +62949,27 @@
         <v>0</v>
       </c>
       <c r="L121" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6728b8cbd1ab2037750b678d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/684192d86e40fb463e0c7ea1</v>
       </c>
       <c r="M121" t="str">
-        <v>https://www.booking.com/hotel/gb/luxury-designer-flat-holland-park.en-gb.html?aid=2276424&amp;label=msn-HEC27qPyOZmLPBxa2YE3Nw-80676810309425%3Atikwd-80676960770001%3Aloc-41471%3Aneo%3Amte%3Alp41471%3Adec%3Aqsapart%20hotels%20w14%20london&amp;sid=c56aa9f495ded14af2d4d054a903fa6d&amp;all_sr_blocks=143034801_130622008_6_0_0;checkin=2024-11-04;checkout=2024-11-25;dist=0;group_adults=2;group_children=0;hapos=1;highlighted_blocks=143034801_130622008_6_0_0;hpos=1;matching_block_id=143034801_130622008_6_0_0;nflt=price%3DGBP-min-max-1%3Bht_id%3D201%3Baccessible_room_facilities%3D131;no_rooms=2;req_adults=2;req_children=0;room1=A;room2=A;sb_price_type=total;sr_order=distance_from_search;sr_pri_blocks=143034801_130622008_6_0_0__598100;srepoch=1730721405;srpvid=13ca53d733e1142c;type=total;ucfs=1&amp;</v>
+        <v>https://www.airbnb.co.uk/rooms/1399201898792819142?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=aa839f79-dbd8-4fd0-868c-739405e0b33e&amp;source_impression_id=p3_1749127712_P3eR1pth3FE1L7T3</v>
+      </c>
+      <c r="N121" t="str">
+        <v>Fernando</v>
+      </c>
+      <c r="O121" t="str">
+        <v>info@urbanview-rentals.co.uk</v>
+      </c>
+      <c r="P121" t="str">
+        <v>07946446163</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>W14 8BA</v>
+        <v>W14 8AS</v>
       </c>
       <c r="B122" t="str">
-        <v>Holland Rd, London W14 8BA, UK</v>
+        <v>147A Holland Rd, London W14 8AS, UK</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -63890,16 +62978,16 @@
         <v>3</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G122" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" t="b">
         <v>0</v>
@@ -63911,33 +62999,24 @@
         <v>0</v>
       </c>
       <c r="L122" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e538654742d568c76f5319</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6728b8cbd1ab2037750b678d</v>
       </c>
       <c r="M122" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1445520707647119008?viralityEntryPoint=1&amp;unique_share_id=DDB5C481-F3E7-4572-85B3-009A630913F4&amp;slcid=d978484b14934a44a2aa7208d3b8352b&amp;s=76&amp;adults=1&amp;slug=SGWujO2T&amp;source_impression_id=p3_1759851881_P3qGxUy-MB3E94D0</v>
-      </c>
-      <c r="N122" t="str">
-        <v>Annie</v>
-      </c>
-      <c r="O122" t="str">
-        <v>info@elev8stays.co.uk</v>
-      </c>
-      <c r="P122" t="str">
-        <v>07940950065</v>
+        <v>https://www.booking.com/hotel/gb/luxury-designer-flat-holland-park.en-gb.html?aid=2276424&amp;label=msn-HEC27qPyOZmLPBxa2YE3Nw-80676810309425%3Atikwd-80676960770001%3Aloc-41471%3Aneo%3Amte%3Alp41471%3Adec%3Aqsapart%20hotels%20w14%20london&amp;sid=c56aa9f495ded14af2d4d054a903fa6d&amp;all_sr_blocks=143034801_130622008_6_0_0;checkin=2024-11-04;checkout=2024-11-25;dist=0;group_adults=2;group_children=0;hapos=1;highlighted_blocks=143034801_130622008_6_0_0;hpos=1;matching_block_id=143034801_130622008_6_0_0;nflt=price%3DGBP-min-max-1%3Bht_id%3D201%3Baccessible_room_facilities%3D131;no_rooms=2;req_adults=2;req_children=0;room1=A;room2=A;sb_price_type=total;sr_order=distance_from_search;sr_pri_blocks=143034801_130622008_6_0_0__598100;srepoch=1730721405;srpvid=13ca53d733e1142c;type=total;ucfs=1&amp;</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">W14 8HP </v>
+        <v>W14 8BA</v>
       </c>
       <c r="B123" t="str">
-        <v>Holland Rd, London, UK</v>
+        <v>Holland Rd, London W14 8BA, UK</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -63961,36 +63040,36 @@
         <v>0</v>
       </c>
       <c r="L123" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6762bce39705f8f6fd8d9054</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e538654742d568c76f5319</v>
       </c>
       <c r="M123" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1281747887308361861?source_impression_id=p3_1734524064_P3yRQ2coR16ZqEqM</v>
+        <v>https://www.airbnb.co.uk/rooms/1445520707647119008?viralityEntryPoint=1&amp;unique_share_id=DDB5C481-F3E7-4572-85B3-009A630913F4&amp;slcid=d978484b14934a44a2aa7208d3b8352b&amp;s=76&amp;adults=1&amp;slug=SGWujO2T&amp;source_impression_id=p3_1759851881_P3qGxUy-MB3E94D0</v>
       </c>
       <c r="N123" t="str">
-        <v>Hugh Nuemann</v>
+        <v>Annie</v>
       </c>
       <c r="O123" t="str">
-        <v>info@huemanhome.com</v>
+        <v>info@elev8stays.co.uk</v>
       </c>
       <c r="P123" t="str">
-        <v>07812 036218</v>
+        <v>07940950065</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>W14 8RS</v>
+        <v xml:space="preserve">W14 8HP </v>
       </c>
       <c r="B124" t="str">
-        <v>Avonmore Rd, London W14 8RS, UK</v>
+        <v>Holland Rd, London, UK</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" t="str">
         <v>off-site-chargeable</v>
@@ -63999,7 +63078,7 @@
         <v>chargeable</v>
       </c>
       <c r="H124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="b">
         <v>0</v>
@@ -64011,36 +63090,45 @@
         <v>0</v>
       </c>
       <c r="L124" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/670502cd6c4c8dd90f1e022c</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6762bce39705f8f6fd8d9054</v>
       </c>
       <c r="M124" t="str">
-        <v>https://www.airbnb.co.uk/rooms/697860747839065994?source_impression_id=p3_1728380263_P3jxe6ldu5BvBmRf</v>
+        <v>https://www.airbnb.co.uk/rooms/1281747887308361861?source_impression_id=p3_1734524064_P3yRQ2coR16ZqEqM</v>
+      </c>
+      <c r="N124" t="str">
+        <v>Hugh Nuemann</v>
+      </c>
+      <c r="O124" t="str">
+        <v>info@huemanhome.com</v>
+      </c>
+      <c r="P124" t="str">
+        <v>07812 036218</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>W14 9AD</v>
+        <v>W14 8RS</v>
       </c>
       <c r="B125" t="str">
-        <v>Edith Villas, London W14, UK</v>
+        <v>Avonmore Rd, London W14 8RS, UK</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G125" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -64052,33 +63140,24 @@
         <v>0</v>
       </c>
       <c r="L125" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/688c9e9dcd02201a20dec8ce</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/670502cd6c4c8dd90f1e022c</v>
       </c>
       <c r="M125" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1421018748466196226?adults=1&amp;check_in=2025-08-18&amp;location=SW6%206AF&amp;search_mode=regular_search&amp;source_impression_id=p3_1754040229_P3gmT3e7jVNgGycf&amp;previous_page_section_name=1001&amp;federated_search_id=594e0e91-a148-448a-8f2b-0d25837a4931&amp;guests=1&amp;check_out=2025-09-01</v>
-      </c>
-      <c r="N125" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-      <c r="O125" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="P125" t="str">
-        <v>00000000000</v>
+        <v>https://www.airbnb.co.uk/rooms/697860747839065994?source_impression_id=p3_1728380263_P3jxe6ldu5BvBmRf</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>W14 9EQ</v>
+        <v>W14 9AD</v>
       </c>
       <c r="B126" t="str">
-        <v>Palliser Rd, London W14, UK</v>
+        <v>Edith Villas, London W14, UK</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -64087,7 +63166,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G126" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H126" t="b">
         <v>0</v>
@@ -64102,27 +63181,27 @@
         <v>0</v>
       </c>
       <c r="L126" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6733760fc8526d02b9494b9b</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/688c9e9dcd02201a20dec8ce</v>
       </c>
       <c r="M126" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1241856898090759613?source_impression_id=p3_1731425623_P31tbe-SFNfSoLlP</v>
+        <v>https://www.airbnb.co.uk/rooms/1421018748466196226?adults=1&amp;check_in=2025-08-18&amp;location=SW6%206AF&amp;search_mode=regular_search&amp;source_impression_id=p3_1754040229_P3gmT3e7jVNgGycf&amp;previous_page_section_name=1001&amp;federated_search_id=594e0e91-a148-448a-8f2b-0d25837a4931&amp;guests=1&amp;check_out=2025-09-01</v>
       </c>
       <c r="N126" t="str">
-        <v>Rashid</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O126" t="str">
-        <v>q@propertyy.io</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P126" t="str">
-        <v>0000000000</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>W14 9NX</v>
+        <v>W14 9EQ</v>
       </c>
       <c r="B127" t="str">
-        <v>212 North End Rd, London W14 9NX, UK</v>
+        <v>Palliser Rd, London W14, UK</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -64131,7 +63210,7 @@
         <v>2</v>
       </c>
       <c r="E127">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F127" t="str">
         <v>off-site-chargeable</v>
@@ -64152,45 +63231,45 @@
         <v>0</v>
       </c>
       <c r="L127" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68713870be8ece05b88b745f</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6733760fc8526d02b9494b9b</v>
       </c>
       <c r="M127" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1447993240658552749?adults=2&amp;check_in=2025-07-15&amp;check_out=2025-08-05&amp;children=2&amp;location=W14%200DY&amp;pets=1&amp;search_mode=regular_search&amp;source_impression_id=p3_1752249131_P3VbKqI2fz4MC43G&amp;previous_page_section_name=1001&amp;federated_search_id=f1f0314e-a10d-4f96-905a-f2ffcc26190b</v>
+        <v>https://www.airbnb.co.uk/rooms/1241856898090759613?source_impression_id=p3_1731425623_P31tbe-SFNfSoLlP</v>
       </c>
       <c r="N127" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Rashid</v>
       </c>
       <c r="O127" t="str">
-        <v>temp@airbnb.com</v>
+        <v>q@propertyy.io</v>
       </c>
       <c r="P127" t="str">
-        <v>00000000000</v>
+        <v>0000000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>W14 9PA</v>
+        <v>W14 9NX</v>
       </c>
       <c r="B128" t="str">
-        <v>Bramber Rd, London W14 9PA, UK</v>
+        <v>212 North End Rd, London W14 9NX, UK</v>
       </c>
       <c r="C128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E128">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F128" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G128" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -64202,24 +63281,33 @@
         <v>0</v>
       </c>
       <c r="L128" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6703e70b225d9354290bd1ce</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68713870be8ece05b88b745f</v>
       </c>
       <c r="M128" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1229169634762318402?source_impression_id=p3_1728308297_P3DdlK7LNWV8Wkr1</v>
+        <v>https://www.airbnb.co.uk/rooms/1447993240658552749?adults=2&amp;check_in=2025-07-15&amp;check_out=2025-08-05&amp;children=2&amp;location=W14%200DY&amp;pets=1&amp;search_mode=regular_search&amp;source_impression_id=p3_1752249131_P3VbKqI2fz4MC43G&amp;previous_page_section_name=1001&amp;federated_search_id=f1f0314e-a10d-4f96-905a-f2ffcc26190b</v>
+      </c>
+      <c r="N128" t="str">
+        <v>Airbnb Temporary</v>
+      </c>
+      <c r="O128" t="str">
+        <v>temp@airbnb.com</v>
+      </c>
+      <c r="P128" t="str">
+        <v>00000000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>W14 9SR</v>
+        <v>W14 9PA</v>
       </c>
       <c r="B129" t="str">
-        <v>29 Perham Rd, London W14 9SR, UK</v>
+        <v>Bramber Rd, London W14 9PA, UK</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -64231,7 +63319,7 @@
         <v>no</v>
       </c>
       <c r="H129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="b">
         <v>0</v>
@@ -64243,19 +63331,10 @@
         <v>0</v>
       </c>
       <c r="L129" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b852c8fead75d2c44e37a9</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6703e70b225d9354290bd1ce</v>
       </c>
       <c r="M129" t="str">
-        <v>https://www.airbnb.co.uk/rooms/779893715432977998?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909996_P320kjk6r2HDmdXw</v>
-      </c>
-      <c r="N129" t="str">
-        <v>Waleed Khalid</v>
-      </c>
-      <c r="O129" t="str">
-        <v>fakewaleed@gmail.com</v>
-      </c>
-      <c r="P129" t="str">
-        <v>+44 7930 000039</v>
+        <v>https://www.airbnb.co.uk/rooms/1229169634762318402?source_impression_id=p3_1728308297_P3DdlK7LNWV8Wkr1</v>
       </c>
     </row>
     <row r="130">
@@ -64293,10 +63372,10 @@
         <v>0</v>
       </c>
       <c r="L130" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b85250fead75d2c44e3756</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b8516436569b00e6f88d5c</v>
       </c>
       <c r="M130" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1014323013581423016?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909995_P3pKaGIDjb9Eqxi2</v>
+        <v>https://www.airbnb.co.uk/rooms/916062053365126516?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909399_P3aPPHZLh9R4sgCq</v>
       </c>
       <c r="N130" t="str">
         <v>Waleed Khalid</v>
@@ -64343,10 +63422,10 @@
         <v>0</v>
       </c>
       <c r="L131" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b8516436569b00e6f88d5c</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b8532d36569b00e6f88f23</v>
       </c>
       <c r="M131" t="str">
-        <v>https://www.airbnb.co.uk/rooms/916062053365126516?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909399_P3aPPHZLh9R4sgCq</v>
+        <v>https://www.airbnb.co.uk/rooms/1046492595924875175?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909999_P30xyAZGPUFJ-QQQ</v>
       </c>
       <c r="N131" t="str">
         <v>Waleed Khalid</v>
@@ -64393,10 +63472,10 @@
         <v>0</v>
       </c>
       <c r="L132" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b8532d36569b00e6f88f23</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b85250fead75d2c44e3756</v>
       </c>
       <c r="M132" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1046492595924875175?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909999_P30xyAZGPUFJ-QQQ</v>
+        <v>https://www.airbnb.co.uk/rooms/1014323013581423016?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909995_P3pKaGIDjb9Eqxi2</v>
       </c>
       <c r="N132" t="str">
         <v>Waleed Khalid</v>
@@ -64410,16 +63489,16 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>W6 0NW</v>
+        <v>W14 9SR</v>
       </c>
       <c r="B133" t="str">
-        <v>Verulam House, Hammersmith Grove, London W6 0NW, UK</v>
+        <v>29 Perham Rd, London W14 9SR, UK</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -64443,33 +63522,33 @@
         <v>0</v>
       </c>
       <c r="L133" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6797bd109b48e7bffd8e6e71</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b852c8fead75d2c44e37a9</v>
       </c>
       <c r="M133" t="str">
-        <v>https://www.airbnb.co.uk/rooms/846987931855578729?source_impression_id=p3_1737997474_P34IR7Y5umGSGePy</v>
+        <v>https://www.airbnb.co.uk/rooms/779893715432977998?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909996_P320kjk6r2HDmdXw</v>
       </c>
       <c r="N133" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Waleed Khalid</v>
       </c>
       <c r="O133" t="str">
-        <v>temp@airbnb.com</v>
+        <v>fakewaleed@gmail.com</v>
       </c>
       <c r="P133" t="str">
-        <v>00000000000</v>
+        <v>+44 7930 000039</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>W6 0RR</v>
+        <v>W6 0NW</v>
       </c>
       <c r="B134" t="str">
-        <v>308 King St, London W6 0RR, UK</v>
+        <v>Verulam House, Hammersmith Grove, London W6 0NW, UK</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -64493,16 +63572,16 @@
         <v>0</v>
       </c>
       <c r="L134" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6797c3519b48e7bffd8e7610</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6797bd109b48e7bffd8e6e71</v>
       </c>
       <c r="M134" t="str">
-        <v>https://www.booking.com/hotel/gb/cozy-1-bedroom-flat-greater-london.en-gb.html?aid=304142&amp;label=gen173rf-1FCAQoggJCKXNlYXJjaF9vYWtsYW5kcytncm92ZSwrbG9uZG9uK3cxMiswamQsK3VrSAlYA2hQiAEBmAEJuAEXyAEM2AEB6AEB-AEDiAIBogITbXlob21laXN5b3Vycy5jby51a6gCA7gC6ITfvAbAAgHSAiQ0MDQ3NmQ5NS01MzdlLTRkNGEtYmMyNy00NGM5OGFiYjQxMTLYAgXgAgE&amp;sid=52fce589b709a7c1281b11adf2d9f4bf&amp;all_sr_blocks=1300187401_402907111_2_41_0&amp;checkin=2025-01-28&amp;checkout=2025-02-25&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1300187401_402907111_2_41_0&amp;hpos=1&amp;matching_block_id=1300187401_402907111_2_41_0&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1300187401_402907111_2_41_0__356048&amp;srepoch=1737999019&amp;srpvid=5cb77af44b8709e9&amp;type=total&amp;ucfs=1&amp;</v>
+        <v>https://www.airbnb.co.uk/rooms/846987931855578729?source_impression_id=p3_1737997474_P34IR7Y5umGSGePy</v>
       </c>
       <c r="N134" t="str">
-        <v>Booking.Com Temporary</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O134" t="str">
-        <v>fake@booking.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P134" t="str">
         <v>00000000000</v>
@@ -64510,16 +63589,16 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>W6 7HA</v>
+        <v>W6 0RR</v>
       </c>
       <c r="B135" t="str">
-        <v>Hammersmith Grove, London W6 7HA, UK</v>
+        <v>308 King St, London W6 0RR, UK</v>
       </c>
       <c r="C135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -64528,7 +63607,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G135" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H135" t="b">
         <v>0</v>
@@ -64543,16 +63622,16 @@
         <v>0</v>
       </c>
       <c r="L135" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6798be3e4222378e6f18a545</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6797c3519b48e7bffd8e7610</v>
       </c>
       <c r="M135" t="str">
-        <v>https://www.airbnb.co.uk/rooms/846987931855578729?source_impression_id=p3_1738063351_P39Vma0mlvFkhxdD</v>
+        <v>https://www.booking.com/hotel/gb/cozy-1-bedroom-flat-greater-london.en-gb.html?aid=304142&amp;label=gen173rf-1FCAQoggJCKXNlYXJjaF9vYWtsYW5kcytncm92ZSwrbG9uZG9uK3cxMiswamQsK3VrSAlYA2hQiAEBmAEJuAEXyAEM2AEB6AEB-AEDiAIBogITbXlob21laXN5b3Vycy5jby51a6gCA7gC6ITfvAbAAgHSAiQ0MDQ3NmQ5NS01MzdlLTRkNGEtYmMyNy00NGM5OGFiYjQxMTLYAgXgAgE&amp;sid=52fce589b709a7c1281b11adf2d9f4bf&amp;all_sr_blocks=1300187401_402907111_2_41_0&amp;checkin=2025-01-28&amp;checkout=2025-02-25&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1300187401_402907111_2_41_0&amp;hpos=1&amp;matching_block_id=1300187401_402907111_2_41_0&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1300187401_402907111_2_41_0__356048&amp;srepoch=1737999019&amp;srpvid=5cb77af44b8709e9&amp;type=total&amp;ucfs=1&amp;</v>
       </c>
       <c r="N135" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Booking.Com Temporary</v>
       </c>
       <c r="O135" t="str">
-        <v>temp@airbnb.com</v>
+        <v>fake@booking.com</v>
       </c>
       <c r="P135" t="str">
         <v>00000000000</v>
@@ -64560,10 +63639,10 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>W6 7LY</v>
+        <v>W6 7HA</v>
       </c>
       <c r="B136" t="str">
-        <v>The Grampians, Shepherds Bush Rd, London W6 7LN, UK</v>
+        <v>Hammersmith Grove, London W6 7HA, UK</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -64593,10 +63672,10 @@
         <v>0</v>
       </c>
       <c r="L136" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6797bf7c0f58a7d7cea7e892</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6798be3e4222378e6f18a545</v>
       </c>
       <c r="M136" t="str">
-        <v>https://www.airbnb.co.uk/rooms/36418219?source_impression_id=p3_1737998044_P3i72K2eLJjQljBK</v>
+        <v>https://www.airbnb.co.uk/rooms/846987931855578729?source_impression_id=p3_1738063351_P39Vma0mlvFkhxdD</v>
       </c>
       <c r="N136" t="str">
         <v>Airbnb Temporary</v>
@@ -64610,19 +63689,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>W6 9EZ</v>
+        <v>W6 7LY</v>
       </c>
       <c r="B137" t="str">
-        <v>Colwith Rd, London W6 9EZ, UK</v>
+        <v>The Grampians, Shepherds Bush Rd, London W6 7LN, UK</v>
       </c>
       <c r="C137">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" t="str">
         <v>off-site-chargeable</v>
@@ -64637,42 +63716,42 @@
         <v>0</v>
       </c>
       <c r="J137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137" t="b">
         <v>0</v>
       </c>
       <c r="L137" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/682c609078091bb5b4b335db</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6797bf7c0f58a7d7cea7e892</v>
       </c>
       <c r="M137" t="str">
-        <v>https://nournestapartments.com/listing/refined-hammersmith-3-bedroom-with-rooftop/</v>
+        <v>https://www.airbnb.co.uk/rooms/36418219?source_impression_id=p3_1737998044_P3i72K2eLJjQljBK</v>
       </c>
       <c r="N137" t="str">
-        <v>Gerda &amp; Chris</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O137" t="str">
-        <v>hello@nournestapartments.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P137" t="str">
-        <v xml:space="preserve"> +44 208 064 0268</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>W6 9HA</v>
+        <v>W6 9EZ</v>
       </c>
       <c r="B138" t="str">
-        <v>3 Rainville Rd, London W6 9HA, UK</v>
+        <v>Colwith Rd, London W6 9EZ, UK</v>
       </c>
       <c r="C138">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D138">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" t="str">
         <v>off-site-chargeable</v>
@@ -64687,39 +63766,39 @@
         <v>0</v>
       </c>
       <c r="J138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138" t="b">
         <v>0</v>
       </c>
       <c r="L138" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6728d956d1ab2037750b823c</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/682c609078091bb5b4b335db</v>
       </c>
       <c r="M138" t="str">
-        <v>https://www.airbnb.com/rooms/786221755699867670?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=3d016987-df10-4fae-8716-1c1edb9b9dfa</v>
+        <v>https://nournestapartments.com/listing/refined-hammersmith-3-bedroom-with-rooftop/</v>
       </c>
       <c r="N138" t="str">
-        <v>Shloime</v>
+        <v>Gerda &amp; Chris</v>
       </c>
       <c r="O138" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>hello@nournestapartments.com</v>
       </c>
       <c r="P138" t="str">
-        <v>07867290839</v>
+        <v xml:space="preserve"> +44 208 064 0268</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>W6 9LF</v>
+        <v>W6 9HA</v>
       </c>
       <c r="B139" t="str">
-        <v>Holcombe St, London W6, UK</v>
+        <v>3 Rainville Rd, London W6 9HA, UK</v>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -64743,45 +63822,45 @@
         <v>0</v>
       </c>
       <c r="L139" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6870e5e327c01b288f21fc21</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6728d956d1ab2037750b823c</v>
       </c>
       <c r="M139" t="str">
-        <v>https://www.booking.com/hotel/gb/hammersmith-gem-bright-flat-close-to-the-tube.en-gb.html?aid=304142&amp;label=gen173nr-1FCAsoUEItaGFtbWVyc21pdGgtZ2VtLWJyaWdodC1mbGF0LWNsb3NlLXRvLXRoZS10dWJlSAlYBGhQiAEBmAEJuAEXyAEM2AEB6AEB-AEGiAIBqAIDuALrw8PDBsACAdICJGRlMzkxMGYzLTI2ODMtNGQzZS04NDVjLThhODZhYzY5ODU5M9gCBeACAQ&amp;sid=7c380fb8cafd8760226e8cee0417ae8a&amp;all_sr_blocks=1410890301_412848739_4_0_0&amp;checkin=2025-07-14&amp;checkout=2025-08-11&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=3&amp;highlighted_blocks=1410890301_412848739_4_0_0&amp;hpos=3&amp;matching_block_id=1410890301_412848739_4_0_0&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1410890301_412848739_4_0_0__659700&amp;srepoch=1752228330&amp;srpvid=b7d5a0eaeb115dc254a20010ecf9f4a6&amp;type=total&amp;ucfs=1&amp;</v>
+        <v>https://www.airbnb.com/rooms/786221755699867670?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=3d016987-df10-4fae-8716-1c1edb9b9dfa</v>
       </c>
       <c r="N139" t="str">
-        <v>Booking.Com Temporary</v>
+        <v>Shloime</v>
       </c>
       <c r="O139" t="str">
-        <v>fake@booking.com</v>
+        <v>shloime@hometohost.co.uk</v>
       </c>
       <c r="P139" t="str">
-        <v>00000000000</v>
+        <v>07867290839</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>W6 9SP</v>
+        <v>W6 9LF</v>
       </c>
       <c r="B140" t="str">
-        <v>78 Rannoch Rd, London W6 9SP, UK</v>
+        <v>Holcombe St, London W6, UK</v>
       </c>
       <c r="C140">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E140">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F140" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G140" t="str">
         <v>chargeable</v>
       </c>
       <c r="H140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" t="b">
         <v>0</v>
@@ -64793,24 +63872,74 @@
         <v>0</v>
       </c>
       <c r="L140" t="str">
+        <v>https://www.myhomeisyours.co.uk/public/property/6870e5e327c01b288f21fc21</v>
+      </c>
+      <c r="M140" t="str">
+        <v>https://www.booking.com/hotel/gb/hammersmith-gem-bright-flat-close-to-the-tube.en-gb.html?aid=304142&amp;label=gen173nr-1FCAsoUEItaGFtbWVyc21pdGgtZ2VtLWJyaWdodC1mbGF0LWNsb3NlLXRvLXRoZS10dWJlSAlYBGhQiAEBmAEJuAEXyAEM2AEB6AEB-AEGiAIBqAIDuALrw8PDBsACAdICJGRlMzkxMGYzLTI2ODMtNGQzZS04NDVjLThhODZhYzY5ODU5M9gCBeACAQ&amp;sid=7c380fb8cafd8760226e8cee0417ae8a&amp;all_sr_blocks=1410890301_412848739_4_0_0&amp;checkin=2025-07-14&amp;checkout=2025-08-11&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=3&amp;highlighted_blocks=1410890301_412848739_4_0_0&amp;hpos=3&amp;matching_block_id=1410890301_412848739_4_0_0&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1410890301_412848739_4_0_0__659700&amp;srepoch=1752228330&amp;srpvid=b7d5a0eaeb115dc254a20010ecf9f4a6&amp;type=total&amp;ucfs=1&amp;</v>
+      </c>
+      <c r="N140" t="str">
+        <v>Booking.Com Temporary</v>
+      </c>
+      <c r="O140" t="str">
+        <v>fake@booking.com</v>
+      </c>
+      <c r="P140" t="str">
+        <v>00000000000</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>W6 9SP</v>
+      </c>
+      <c r="B141" t="str">
+        <v>78 Rannoch Rd, London W6 9SP, UK</v>
+      </c>
+      <c r="C141">
+        <v>5</v>
+      </c>
+      <c r="D141">
+        <v>5</v>
+      </c>
+      <c r="E141">
+        <v>4.5</v>
+      </c>
+      <c r="F141" t="str">
+        <v>on-site-free</v>
+      </c>
+      <c r="G141" t="str">
+        <v>chargeable</v>
+      </c>
+      <c r="H141" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" t="b">
+        <v>0</v>
+      </c>
+      <c r="J141" t="b">
+        <v>0</v>
+      </c>
+      <c r="K141" t="b">
+        <v>0</v>
+      </c>
+      <c r="L141" t="str">
         <v>https://www.myhomeisyours.co.uk/public/property/68dd223b699b101f6e5120d3</v>
       </c>
-      <c r="M140" t="str">
+      <c r="M141" t="str">
         <v>https://www.airbnb.co.uk/rooms/1221077715659269159?source_impression_id=p3_1759322347_P3thUDdzPZoe4FeP&amp;check_in=2025-10-06&amp;guests=1&amp;adults=1&amp;check_out=2025-10-13</v>
       </c>
-      <c r="N140" t="str">
+      <c r="N141" t="str">
         <v>Yoko Property Management</v>
       </c>
-      <c r="O140" t="str">
+      <c r="O141" t="str">
         <v>info@yokoproperty.co.uk</v>
       </c>
-      <c r="P140" t="str">
+      <c r="P141" t="str">
         <v>use whatsapp group / 0333 772 7478</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P141"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/property_list.xlsx
+++ b/scripts/property_list.xlsx
@@ -57098,7 +57098,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P146"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -57255,7 +57255,7 @@
         <v>KT1 4AX</v>
       </c>
       <c r="B4" t="str">
-        <v>Park Rd, Hampton Wick, Kingston upon Thames KT1 4AX, UK</v>
+        <v>Park Court, Park Rd, Hampton Wick, Kingston upon Thames KT1 4AU, UK</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -57276,28 +57276,28 @@
         <v>0</v>
       </c>
       <c r="I4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f0d126f6dcfb01fba97816</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68dfae1b56f6ee67fd53970a</v>
       </c>
       <c r="M4" t="str">
-        <v>https://www.airbnb.com/l/O7ozFtch</v>
+        <v>https://www.airbnb.co.uk/rooms/6066828?adults=3&amp;check_in=2025-10-15&amp;check_out=2025-10-22&amp;pets=1&amp;search_mode=regular_search&amp;source_impression_id=p3_1759485922_P3TUhbgwSrQ8sJcd&amp;previous_page_section_name=1000&amp;federated_search_id=48af8d57-3400-4bcc-b229-b2d98a1f2ac1</v>
       </c>
       <c r="N4" t="str">
-        <v>Hannah Dutton-Waller</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O4" t="str">
-        <v>hannahdw29@gmail.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P4" t="str">
-        <v>+44 7977 340378</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="5">
@@ -57355,7 +57355,7 @@
         <v>KT1 4AX</v>
       </c>
       <c r="B6" t="str">
-        <v>Park Court, Park Rd, Hampton Wick, Kingston upon Thames KT1 4AU, UK</v>
+        <v>Park Rd, Hampton Wick, Kingston upon Thames KT1 4AX, UK</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -57376,28 +57376,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68dfae1b56f6ee67fd53970a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f0d126f6dcfb01fba97816</v>
       </c>
       <c r="M6" t="str">
-        <v>https://www.airbnb.co.uk/rooms/6066828?adults=3&amp;check_in=2025-10-15&amp;check_out=2025-10-22&amp;pets=1&amp;search_mode=regular_search&amp;source_impression_id=p3_1759485922_P3TUhbgwSrQ8sJcd&amp;previous_page_section_name=1000&amp;federated_search_id=48af8d57-3400-4bcc-b229-b2d98a1f2ac1</v>
+        <v>https://www.airbnb.com/l/O7ozFtch</v>
       </c>
       <c r="N6" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Hannah Dutton-Waller</v>
       </c>
       <c r="O6" t="str">
-        <v>temp@airbnb.com</v>
+        <v>hannahdw29@gmail.com</v>
       </c>
       <c r="P6" t="str">
-        <v>00000000000</v>
+        <v>+44 7977 340378</v>
       </c>
     </row>
     <row r="7">
@@ -57505,7 +57505,7 @@
         <v>KT2 7DW</v>
       </c>
       <c r="B9" t="str">
-        <v>Manorgate Rd, London KT2, UK</v>
+        <v>7 London Road, Kingston upon Thames, KT2 6PT</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -57520,7 +57520,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G9" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -57535,7 +57535,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66d6ff553cd0be0c2f91c63a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68daa133e8d8423b6968abf7</v>
       </c>
       <c r="M9" t="str">
         <v>https://www.airbnb.co.uk/rooms/743513490080624231?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=44c1e2fd-b4d7-4227-ba62-edfb07f8198c&amp;source_impression_id=p3_1725365646_P3NASfY2ZohVWJ2k</v>
@@ -57585,7 +57585,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68daa133e8d8423b6968abf7</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/66d6fe4d3cd0be0c2f91c420</v>
       </c>
       <c r="M10" t="str">
         <v>https://www.airbnb.co.uk/rooms/743513490080624231?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=44c1e2fd-b4d7-4227-ba62-edfb07f8198c&amp;source_impression_id=p3_1725365646_P3NASfY2ZohVWJ2k</v>
@@ -57605,7 +57605,7 @@
         <v>KT2 7DW</v>
       </c>
       <c r="B11" t="str">
-        <v>7 London Road, Kingston upon Thames, KT2 6PT</v>
+        <v>Manorgate Rd, London KT2, UK</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -57620,7 +57620,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G11" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -57635,7 +57635,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66d6fe4d3cd0be0c2f91c420</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/66d6ff553cd0be0c2f91c63a</v>
       </c>
       <c r="M11" t="str">
         <v>https://www.airbnb.co.uk/rooms/743513490080624231?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=44c1e2fd-b4d7-4227-ba62-edfb07f8198c&amp;source_impression_id=p3_1725365646_P3NASfY2ZohVWJ2k</v>
@@ -57843,10 +57843,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SW11 1JJ</v>
+        <v>SW10 9JH</v>
       </c>
       <c r="B16" t="str">
-        <v>Altenburg Gardens, London SW11 1JJ, UK</v>
+        <v>Redcliffe Gardens, London SW10 9JH, UK</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -57876,110 +57876,110 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67d7f2b580e7464cfd71c50d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/691f4becccb75a8daee514e4</v>
       </c>
       <c r="M16" t="str">
-        <v>https://www.airbnb.co.uk/rooms/38536870?source_impression_id=p3_1742205006_P3o0EwvC1tjfxDca</v>
+        <v>https://www.airbnb.co.uk/rooms/1340623068327691661?guests=1&amp;adults=1&amp;check_in=2025-11-24&amp;check_out=2025-12-08&amp;source_impression_id=p3_1763657374_P3c7r-RkO-dwMFlh</v>
       </c>
       <c r="N16" t="str">
-        <v>Gioacchino Grand</v>
+        <v>Hugh Nuemann</v>
       </c>
       <c r="O16" t="str">
-        <v>gio.grand@me.com</v>
+        <v>info@huemanhome.com</v>
       </c>
       <c r="P16" t="str">
-        <v>07951 318689</v>
+        <v>07812 036218</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">SW11 1PL </v>
+        <v>SW11 1JJ</v>
       </c>
       <c r="B17" t="str">
-        <v>13C Severus Rd, London SW11 1PL, UK</v>
+        <v>Altenburg Gardens, London SW11 1JJ, UK</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G17" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6707a878f8cceeaf7f989480</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67d7f2b580e7464cfd71c50d</v>
       </c>
       <c r="M17" t="str">
-        <v>https://www.airbnb.co.uk/rooms/839262263156152735?adults=4&amp;children=0&amp;enable_m3_private_room=true&amp;infants=0&amp;pets=0&amp;search_mode=regular_search&amp;check_in=2024-11-03&amp;check_out=2024-11-08&amp;source_impression_id=p3_1728474347_P3DWGXAa_2QtXi1E&amp;previous_page_section_name=1000&amp;federated_search_id=d3615a41-61fe-477e-9eab-e516627a3f3f</v>
+        <v>https://www.airbnb.co.uk/rooms/38536870?source_impression_id=p3_1742205006_P3o0EwvC1tjfxDca</v>
+      </c>
+      <c r="N17" t="str">
+        <v>Gioacchino Grand</v>
+      </c>
+      <c r="O17" t="str">
+        <v>gio.grand@me.com</v>
+      </c>
+      <c r="P17" t="str">
+        <v>07951 318689</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SW11 1SX</v>
+        <v xml:space="preserve">SW11 1PL </v>
       </c>
       <c r="B18" t="str">
-        <v>St John's Hl, London SW11 1SX, UK</v>
+        <v>13C Severus Rd, London SW11 1PL, UK</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G18" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68fb448ff911141e69a138d7</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6707a878f8cceeaf7f989480</v>
       </c>
       <c r="M18" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1508080538383464858?viralityEntryPoint=1&amp;unique_share_id=E045C9E6-339A-4417-965A-01A0937A442E&amp;slcid=9761453bd8374aa78ecd24f279fe528b&amp;s=76&amp;adults=1&amp;slug=wvL2aonh&amp;source_impression_id=p3_1761297328_P3aSdbJcsW1JLqnY</v>
-      </c>
-      <c r="N18" t="str">
-        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
-      </c>
-      <c r="O18" t="str">
-        <v>Accommodation@calbrahomes.com</v>
-      </c>
-      <c r="P18" t="str">
-        <v>02045784820</v>
+        <v>https://www.airbnb.co.uk/rooms/839262263156152735?adults=4&amp;children=0&amp;enable_m3_private_room=true&amp;infants=0&amp;pets=0&amp;search_mode=regular_search&amp;check_in=2024-11-03&amp;check_out=2024-11-08&amp;source_impression_id=p3_1728474347_P3DWGXAa_2QtXi1E&amp;previous_page_section_name=1000&amp;federated_search_id=d3615a41-61fe-477e-9eab-e516627a3f3f</v>
       </c>
     </row>
     <row r="19">
@@ -57987,7 +57987,7 @@
         <v>SW11 1SX</v>
       </c>
       <c r="B19" t="str">
-        <v>2, 67 St John's Hl, London SW11 1RZ, UK</v>
+        <v>St John's Hl, London SW11 1SX, UK</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -58017,10 +58017,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f62c30b8c1acfaf83a4983</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68fb448ff911141e69a138d7</v>
       </c>
       <c r="M19" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1508080538383464858?viralityEntryPoint=1&amp;unique_share_id=F207E198-E9B9-4D65-89B7-1559903B3C77&amp;slcid=1eba13d36311475d93cfe707ee7c340a&amp;s=76&amp;adults=1&amp;slug=TTXROpB4&amp;source_impression_id=p3_1760963365_P39cHqhtj8jxXxGf</v>
+        <v>https://www.airbnb.co.uk/rooms/1508080538383464858?viralityEntryPoint=1&amp;unique_share_id=E045C9E6-339A-4417-965A-01A0937A442E&amp;slcid=9761453bd8374aa78ecd24f279fe528b&amp;s=76&amp;adults=1&amp;slug=wvL2aonh&amp;source_impression_id=p3_1761297328_P3aSdbJcsW1JLqnY</v>
       </c>
       <c r="N19" t="str">
         <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
@@ -58034,16 +58034,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SW11 1YF</v>
+        <v>SW11 1SX</v>
       </c>
       <c r="B20" t="str">
-        <v>Hazel Court, Haydon Way, London SW11 1YF, UK</v>
+        <v>2, 67 St John's Hl, London SW11 1RZ, UK</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -58052,10 +58052,10 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G20" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -58067,19 +58067,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/688102a4b268cad7327802c1</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f62c30b8c1acfaf83a4983</v>
       </c>
       <c r="M20" t="str">
-        <v>https://dandi.com/cityliving/dandi-battersea/</v>
+        <v>https://www.airbnb.co.uk/rooms/1508080538383464858?viralityEntryPoint=1&amp;unique_share_id=F207E198-E9B9-4D65-89B7-1559903B3C77&amp;slcid=1eba13d36311475d93cfe707ee7c340a&amp;s=76&amp;adults=1&amp;slug=TTXROpB4&amp;source_impression_id=p3_1760963365_P39cHqhtj8jxXxGf</v>
       </c>
       <c r="N20" t="str">
-        <v>Darius - ask Orla before offering - Adult only</v>
+        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
       </c>
       <c r="O20" t="str">
-        <v>social@dandi.com</v>
+        <v>Accommodation@calbrahomes.com</v>
       </c>
       <c r="P20" t="str">
-        <v>+44 (0) 20 3927 8955</v>
+        <v>02045784820</v>
       </c>
     </row>
     <row r="21">
@@ -58125,16 +58125,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SW11 2RD</v>
+        <v>SW11 1YF</v>
       </c>
       <c r="B22" t="str">
-        <v>159 Harbut Rd, London SW11, UK</v>
+        <v>Hazel Court, Haydon Way, London SW11 1YF, UK</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -58146,7 +58146,7 @@
         <v>no</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -58158,33 +58158,33 @@
         <v>0</v>
       </c>
       <c r="L22" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66e860e4b87a37d3a810d9ee</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/688102a4b268cad7327802c1</v>
       </c>
       <c r="M22" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1176308231606979330?source_impression_id=p3_1726504391_P3JYNKytn_Wf5rFD</v>
+        <v>https://dandi.com/cityliving/dandi-battersea/</v>
       </c>
       <c r="N22" t="str">
-        <v>Shloime</v>
+        <v>Darius - ask Orla before offering - Adult only</v>
       </c>
       <c r="O22" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>social@dandi.com</v>
       </c>
       <c r="P22" t="str">
-        <v>07867290839</v>
+        <v>+44 (0) 20 3927 8955</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SW11 2TS</v>
+        <v>SW11 2RD</v>
       </c>
       <c r="B23" t="str">
-        <v>Wayford St, London SW11 2TS, UK</v>
+        <v>159 Harbut Rd, London SW11, UK</v>
       </c>
       <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
         <v>3</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -58208,39 +58208,39 @@
         <v>0</v>
       </c>
       <c r="L23" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6862bb2c87dcaa2b6427c8b5</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/66e860e4b87a37d3a810d9ee</v>
       </c>
       <c r="M23" t="str">
-        <v>https://www.airbnb.co.uk/rooms/679497470813562921?viralityEntryPoint=1&amp;unique_share_id=5EF6C3CF-C8CD-4F92-B492-FD3A27995AAB&amp;slcid=87d6d0498cd64f6291fb1c00685201b9&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=DvW9UhNp&amp;source_impression_id=p3_1754925699_P3dKE7lGrs31rwXU</v>
+        <v>https://www.airbnb.co.uk/rooms/1176308231606979330?source_impression_id=p3_1726504391_P3JYNKytn_Wf5rFD</v>
       </c>
       <c r="N23" t="str">
-        <v>Tetteh Johnson</v>
+        <v>Shloime</v>
       </c>
       <c r="O23" t="str">
-        <v>info@tjohnrealestate.com</v>
+        <v>shloime@hometohost.co.uk</v>
       </c>
       <c r="P23" t="str">
-        <v>+44 7938 164087</v>
+        <v>07867290839</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SW11 3GU</v>
+        <v>SW11 2TS</v>
       </c>
       <c r="B24" t="str">
-        <v>York St, London, UK</v>
+        <v>Wayford St, London SW11 2TS, UK</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G24" t="str">
         <v>no</v>
@@ -58258,45 +58258,45 @@
         <v>0</v>
       </c>
       <c r="L24" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/5cbaf6a39fed45b995050ac1</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6862bb2c87dcaa2b6427c8b5</v>
       </c>
       <c r="M24" t="str">
-        <v>https://www.airbnb.co.uk/rooms/41897511?guests=1&amp;adults=1&amp;viralityEntryPoint=1&amp;s=76</v>
+        <v>https://www.airbnb.co.uk/rooms/679497470813562921?viralityEntryPoint=1&amp;unique_share_id=5EF6C3CF-C8CD-4F92-B492-FD3A27995AAB&amp;slcid=87d6d0498cd64f6291fb1c00685201b9&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=DvW9UhNp&amp;source_impression_id=p3_1754925699_P3dKE7lGrs31rwXU</v>
       </c>
       <c r="N24" t="str">
-        <v>Jela</v>
+        <v>Tetteh Johnson</v>
       </c>
       <c r="O24" t="str">
-        <v>danijelaukovic@icloud.com</v>
+        <v>info@tjohnrealestate.com</v>
       </c>
       <c r="P24" t="str">
-        <v>07919231122</v>
+        <v>+44 7938 164087</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SW11 3JS</v>
+        <v>SW11 3GU</v>
       </c>
       <c r="B25" t="str">
-        <v>Battersea High St, London SW11 3JS, UK</v>
+        <v>York St, London, UK</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G25" t="str">
         <v>no</v>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -58308,36 +58308,45 @@
         <v>0</v>
       </c>
       <c r="L25" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6703e236225d9354290bce2d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/5cbaf6a39fed45b995050ac1</v>
       </c>
       <c r="M25" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1218807051302828024?source_impression_id=p3_1728307055_P3QUPy_S2FPPwuYG</v>
+        <v>https://www.airbnb.co.uk/rooms/41897511?guests=1&amp;adults=1&amp;viralityEntryPoint=1&amp;s=76</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Jela</v>
+      </c>
+      <c r="O25" t="str">
+        <v>danijelaukovic@icloud.com</v>
+      </c>
+      <c r="P25" t="str">
+        <v>07919231122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SW11 4FS</v>
+        <v>SW11 3JS</v>
       </c>
       <c r="B26" t="str">
-        <v>Palmer Rd, Nine Elms, London SW11 4FA, UK</v>
+        <v>Battersea High St, London SW11 3JS, UK</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G26" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -58349,27 +58358,27 @@
         <v>0</v>
       </c>
       <c r="L26" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/673cb4b4d961917ed259119a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6703e236225d9354290bce2d</v>
       </c>
       <c r="M26" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1291879731913910424?source_impression_id=p3_1732030853_P3AZuJO2O6rn31UJ&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
+        <v>https://www.airbnb.co.uk/rooms/1218807051302828024?source_impression_id=p3_1728307055_P3QUPy_S2FPPwuYG</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">SW11 4LD </v>
+        <v>SW11 4FS</v>
       </c>
       <c r="B27" t="str">
-        <v xml:space="preserve">110 park court, Battersea park Road, SW11 4LD </v>
+        <v>Palmer Rd, Nine Elms, London SW11 4FA, UK</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F27" t="str">
         <v>off-site-chargeable</v>
@@ -58390,7 +58399,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6fa61eff78df8625499c1bce</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/673cb4b4d961917ed259119a</v>
+      </c>
+      <c r="M27" t="str">
+        <v>https://www.airbnb.co.uk/rooms/1291879731913910424?source_impression_id=p3_1732030853_P3AZuJO2O6rn31UJ&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
       </c>
     </row>
     <row r="28">
@@ -58436,10 +58448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SW11 4LW</v>
+        <v xml:space="preserve">SW11 4LD </v>
       </c>
       <c r="B29" t="str">
-        <v>501 Battersea Park Rd, London SW11 4LW, UK</v>
+        <v xml:space="preserve">110 park court, Battersea park Road, SW11 4LD </v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -58448,13 +58460,13 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F29" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G29" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -58469,36 +58481,24 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/69121d1d2b4e96e2827db30a</v>
-      </c>
-      <c r="M29" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1465792999936214199?source_impression_id=p3_1760533293_P3j_fiSyeOShGomp</v>
-      </c>
-      <c r="N29" t="str">
-        <v>Amanah Properties</v>
-      </c>
-      <c r="O29" t="str">
-        <v>info@amanahproperties.com</v>
-      </c>
-      <c r="P29" t="str">
-        <v>+447775950729</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6fa61eff78df8625499c1bce</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SW11 4PS</v>
+        <v>SW11 4LW</v>
       </c>
       <c r="B30" t="str">
-        <v>Kersley Mews, London SW11 4PS, UK</v>
+        <v>501 Battersea Park Rd, London SW11 4LW, UK</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
         <v>off-site-chargeable</v>
@@ -58507,7 +58507,7 @@
         <v>no</v>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -58519,45 +58519,45 @@
         <v>0</v>
       </c>
       <c r="L30" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e91315c4c1683dabfe605b</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/69121d1d2b4e96e2827db30a</v>
       </c>
       <c r="M30" t="str">
-        <v>https://www.airbnb.co.uk/rooms/16676789?source_impression_id=p3_1760102765_P3PdkRzUiMhPtptL&amp;check_in=2025-10-13&amp;guests=4&amp;adults=2&amp;check_out=2025-10-20&amp;children=2</v>
+        <v>https://www.airbnb.co.uk/rooms/1465792999936214199?source_impression_id=p3_1760533293_P3j_fiSyeOShGomp</v>
       </c>
       <c r="N30" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Amanah Properties</v>
       </c>
       <c r="O30" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@amanahproperties.com</v>
       </c>
       <c r="P30" t="str">
-        <v>00000000000</v>
+        <v>+447775950729</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SW11 4SS</v>
+        <v>SW11 4PS</v>
       </c>
       <c r="B31" t="str">
-        <v>Wendle Square, London SW11 4SS, UK</v>
+        <v>Kersley Mews, London SW11 4PS, UK</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F31" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G31" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -58569,42 +58569,42 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/683990bc4c57ed8b6ad54b58</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e91315c4c1683dabfe605b</v>
       </c>
       <c r="M31" t="str">
-        <v>https://www.airbnb.co.uk/rooms/41099953?viralityEntryPoint=1&amp;unique_share_id=FF598AD2-5A73-461B-BD14-28DA0DBB988F&amp;slcid=ec38368a76174e3fbadcc764c4ae8b58&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=cYxROAif&amp;source_impression_id=p3_1748602915_P3YQp2jMiu-spgg0</v>
+        <v>https://www.airbnb.co.uk/rooms/16676789?source_impression_id=p3_1760102765_P3PdkRzUiMhPtptL&amp;check_in=2025-10-13&amp;guests=4&amp;adults=2&amp;check_out=2025-10-20&amp;children=2</v>
       </c>
       <c r="N31" t="str">
-        <v>Jela</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O31" t="str">
-        <v>danijelaukovic@icloud.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P31" t="str">
-        <v>07919231122</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SW11 5DW</v>
+        <v>SW11 4SS</v>
       </c>
       <c r="B32" t="str">
-        <v>31 Dagnall St, London SW11 4LH, UK</v>
+        <v>Wendle Square, London SW11 4SS, UK</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F32" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G32" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -58619,10 +58619,10 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/d73aa935ad510ee1e1fd23f9</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/683990bc4c57ed8b6ad54b58</v>
       </c>
       <c r="M32" t="str">
-        <v>https://www.airbnb.co.uk/rooms/635926379073554092?guests=1&amp;adults=1&amp;viralityEntryPoint=1&amp;s=76</v>
+        <v>https://www.airbnb.co.uk/rooms/41099953?viralityEntryPoint=1&amp;unique_share_id=FF598AD2-5A73-461B-BD14-28DA0DBB988F&amp;slcid=ec38368a76174e3fbadcc764c4ae8b58&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=cYxROAif&amp;source_impression_id=p3_1748602915_P3YQp2jMiu-spgg0</v>
       </c>
       <c r="N32" t="str">
         <v>Jela</v>
@@ -58636,16 +58636,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SW11 5JH</v>
+        <v>SW11 5DW</v>
       </c>
       <c r="B33" t="str">
-        <v>Ashley Cres, London, UK</v>
+        <v>31 Dagnall St, London SW11 4LH, UK</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -58654,7 +58654,7 @@
         <v>on-site-free</v>
       </c>
       <c r="G33" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -58669,30 +58669,30 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/689b01adf6c5180f2121f973</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/d73aa935ad510ee1e1fd23f9</v>
       </c>
       <c r="M33" t="str">
-        <v>https://www.airbnb.co.uk/rooms/634068780359008334?source_impression_id=p3_1754988557_P3UdUdVJENWRZYNW</v>
+        <v>https://www.airbnb.co.uk/rooms/635926379073554092?guests=1&amp;adults=1&amp;viralityEntryPoint=1&amp;s=76</v>
       </c>
       <c r="N33" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Jela</v>
       </c>
       <c r="O33" t="str">
-        <v>temp@airbnb.com</v>
+        <v>danijelaukovic@icloud.com</v>
       </c>
       <c r="P33" t="str">
-        <v>00000000000</v>
+        <v>07919231122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SW11 5RA</v>
+        <v>SW11 5JH</v>
       </c>
       <c r="B34" t="str">
-        <v>Lavender Hill, London SW11 5RA, UK</v>
+        <v>Ashley Cres, London, UK</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -58701,7 +58701,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G34" t="str">
         <v>chargeable</v>
@@ -58719,33 +58719,33 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68a4a511ceebdc6ba09336cc</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/689b01adf6c5180f2121f973</v>
       </c>
       <c r="M34" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1139946404963605588?adults=1&amp;check_in=2025-08-22&amp;check_out=2025-09-12&amp;location=SW11%205SS&amp;search_mode=regular_search&amp;source_impression_id=p3_1755619405_P3ZlX1r4fGGTWZ0K&amp;previous_page_section_name=1001&amp;federated_search_id=978238a8-df2e-42b9-8635-323c56010509</v>
+        <v>https://www.airbnb.co.uk/rooms/634068780359008334?source_impression_id=p3_1754988557_P3UdUdVJENWRZYNW</v>
       </c>
       <c r="N34" t="str">
-        <v>Finesse Stays</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O34" t="str">
-        <v>info@finessestays.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P34" t="str">
-        <v>07950581172</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SW11 7DF</v>
+        <v>SW11 5RA</v>
       </c>
       <c r="B35" t="str">
-        <v>57 Nine Elms Ln, Nine Elms, London SW11 7DE, UK</v>
+        <v>Lavender Hill, London SW11 5RA, UK</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -58760,7 +58760,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -58769,18 +58769,27 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66db1e453354af67ffc221db</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68a4a511ceebdc6ba09336cc</v>
       </c>
       <c r="M35" t="str">
-        <v>https://www.stayurbanrest.com/apartments/united-kingdom/london/urban-rest-battersea</v>
+        <v>https://www.airbnb.co.uk/rooms/1139946404963605588?adults=1&amp;check_in=2025-08-22&amp;check_out=2025-09-12&amp;location=SW11%205SS&amp;search_mode=regular_search&amp;source_impression_id=p3_1755619405_P3ZlX1r4fGGTWZ0K&amp;previous_page_section_name=1001&amp;federated_search_id=978238a8-df2e-42b9-8635-323c56010509</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Finesse Stays</v>
+      </c>
+      <c r="O35" t="str">
+        <v>info@finessestays.co.uk</v>
+      </c>
+      <c r="P35" t="str">
+        <v>07950581172</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SW11 8EL</v>
+        <v>SW11 7DF</v>
       </c>
       <c r="B36" t="str">
-        <v>Circus Rd W, Nine Elms, London, UK</v>
+        <v>57 Nine Elms Ln, Nine Elms, London SW11 7DE, UK</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -58795,7 +58804,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G36" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
@@ -58810,24 +58819,24 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67334181c8526d02b9491e70</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/66db1e453354af67ffc221db</v>
       </c>
       <c r="M36" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1178916688306956402?source_impression_id=p3_1731410975_P32NzDjIDYGJVEFV</v>
+        <v>https://www.stayurbanrest.com/apartments/united-kingdom/london/urban-rest-battersea</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SW12 0PF</v>
+        <v>SW11 8EL</v>
       </c>
       <c r="B37" t="str">
-        <v>61 Scholars Rd., London SW12 0PF, UK</v>
+        <v>Circus Rd W, Nine Elms, London, UK</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -58842,7 +58851,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -58851,18 +58860,18 @@
         <v>0</v>
       </c>
       <c r="L37" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6773eba77b3e2fd7904b79df</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67334181c8526d02b9491e70</v>
       </c>
       <c r="M37" t="str">
-        <v>https://www.booking.com/hotel/gb/cosy-2-bed-in-balham.en-gb.html?aid=304142&amp;label=gen173rf-1FCAQoggJCDnNlYXJjaF9zdzggMnJySDNYA2hQiAEBmAEJuAEXyAEM2AEB6AEB-AEDiAIBogITbXlob21laXN5b3Vycy5jby51a6gCA7gCy9PPuwbAAgHSAiRhMTYzYzE5Yi02ZTU0LTQwMjYtOWYwMC03MmExMzY0MzMxZGXYAgXgAgE&amp;sid=0869d3739adbfeb7a58d7dab3d611b0a&amp;all_sr_blocks=1333899101_405891125_2_0_0&amp;checkin=2025-01-06&amp;checkout=2025-01-30&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1333899101_405891125_2_0_0&amp;hpos=1&amp;matching_block_id=1333899101_405891125_2_0_0&amp;nflt=privacy_type%3D3&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=upsort_bh&amp;sr_pri_blocks=1333899101_405891125_2_0_0__180326&amp;srepoch=1735650119&amp;srpvid=a8035af4720b01f2&amp;type=total&amp;ucfs=1&amp;</v>
+        <v>https://www.airbnb.co.uk/rooms/1178916688306956402?source_impression_id=p3_1731410975_P32NzDjIDYGJVEFV</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SW12 9DJ</v>
+        <v>SW12 0PF</v>
       </c>
       <c r="B38" t="str">
-        <v>153 Balham hill SW12 9DJ</v>
+        <v>61 Scholars Rd., London SW12 0PF, UK</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -58877,7 +58886,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G38" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
@@ -58892,18 +58901,18 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/73af19058d55055f6f12f3c2</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6773eba77b3e2fd7904b79df</v>
       </c>
       <c r="M38" t="str">
-        <v>https://www.airbnb.com/h/balhamjb</v>
+        <v>https://www.booking.com/hotel/gb/cosy-2-bed-in-balham.en-gb.html?aid=304142&amp;label=gen173rf-1FCAQoggJCDnNlYXJjaF9zdzggMnJySDNYA2hQiAEBmAEJuAEXyAEM2AEB6AEB-AEDiAIBogITbXlob21laXN5b3Vycy5jby51a6gCA7gCy9PPuwbAAgHSAiRhMTYzYzE5Yi02ZTU0LTQwMjYtOWYwMC03MmExMzY0MzMxZGXYAgXgAgE&amp;sid=0869d3739adbfeb7a58d7dab3d611b0a&amp;all_sr_blocks=1333899101_405891125_2_0_0&amp;checkin=2025-01-06&amp;checkout=2025-01-30&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1333899101_405891125_2_0_0&amp;hpos=1&amp;matching_block_id=1333899101_405891125_2_0_0&amp;nflt=privacy_type%3D3&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=upsort_bh&amp;sr_pri_blocks=1333899101_405891125_2_0_0__180326&amp;srepoch=1735650119&amp;srpvid=a8035af4720b01f2&amp;type=total&amp;ucfs=1&amp;</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SW12 9HW</v>
+        <v>SW12 9DJ</v>
       </c>
       <c r="B39" t="str">
-        <v>Bedford Hill, London SW12 9HW, UK</v>
+        <v>153 Balham hill SW12 9DJ</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -58921,7 +58930,7 @@
         <v>chargeable</v>
       </c>
       <c r="H39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -58933,33 +58942,24 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68778dbac5ac8b4dba165c09</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/73af19058d55055f6f12f3c2</v>
       </c>
       <c r="M39" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1320932616081269147?adults=1&amp;location=SW17%200HG&amp;search_mode=regular_search&amp;source_impression_id=p3_1752661801_P3KMDuT5dLVzPOTn&amp;previous_page_section_name=1001&amp;federated_search_id=51ee307a-d692-43e6-a4bd-d5edb28570bd&amp;guests=1</v>
-      </c>
-      <c r="N39" t="str">
-        <v>Steven Rich</v>
-      </c>
-      <c r="O39" t="str">
-        <v>steven@stevenrichproperty.co.uk</v>
-      </c>
-      <c r="P39" t="str">
-        <v>07383659689</v>
+        <v>https://www.airbnb.com/h/balhamjb</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SW12 9HZ</v>
+        <v>SW12 9HW</v>
       </c>
       <c r="B40" t="str">
-        <v>7 Byrne Rd, London SW12 9HZ, UK</v>
+        <v>Bedford Hill, London SW12 9HW, UK</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -58971,7 +58971,7 @@
         <v>chargeable</v>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -58983,45 +58983,45 @@
         <v>0</v>
       </c>
       <c r="L40" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67c0684b5139c18f3e607dd9</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68778dbac5ac8b4dba165c09</v>
       </c>
       <c r="M40" t="str">
-        <v>https://www.airbnb.co.uk/rooms/19357738?source_impression_id=p3_1740662677_P3Amf1OTLPMkzKe-</v>
+        <v>https://www.airbnb.co.uk/rooms/1320932616081269147?adults=1&amp;location=SW17%200HG&amp;search_mode=regular_search&amp;source_impression_id=p3_1752661801_P3KMDuT5dLVzPOTn&amp;previous_page_section_name=1001&amp;federated_search_id=51ee307a-d692-43e6-a4bd-d5edb28570bd&amp;guests=1</v>
       </c>
       <c r="N40" t="str">
-        <v>Julie madison-hill</v>
+        <v>Steven Rich</v>
       </c>
       <c r="O40" t="str">
-        <v>enquiries@madison-hill.com</v>
+        <v>steven@stevenrichproperty.co.uk</v>
       </c>
       <c r="P40" t="str">
-        <v>0208 675 8308</v>
+        <v>07383659689</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SW12 9PB</v>
+        <v>SW12 9HZ</v>
       </c>
       <c r="B41" t="str">
-        <v>Englewood Road, London SW12 9PB</v>
+        <v>7 Byrne Rd, London SW12 9HZ, UK</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G41" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -59033,24 +59033,33 @@
         <v>0</v>
       </c>
       <c r="L41" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/2d3fdb9413b46301a34b45e9</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67c0684b5139c18f3e607dd9</v>
       </c>
       <c r="M41" t="str">
-        <v>https://air.tl/ruW1v2CN</v>
+        <v>https://www.airbnb.co.uk/rooms/19357738?source_impression_id=p3_1740662677_P3Amf1OTLPMkzKe-</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Julie madison-hill</v>
+      </c>
+      <c r="O41" t="str">
+        <v>enquiries@madison-hill.com</v>
+      </c>
+      <c r="P41" t="str">
+        <v>0208 675 8308</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SW12 9RT</v>
+        <v>SW12 9LE</v>
       </c>
       <c r="B42" t="str">
-        <v>Fernlea Rd, London SW12 9RT, UK</v>
+        <v>Cathles Rd, London SW12 9LE, UK</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -59068,51 +59077,51 @@
         <v>0</v>
       </c>
       <c r="J42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
       </c>
       <c r="L42" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67c065595139c18f3e607cb5</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/691b4135288d46fdd5bfc6de</v>
       </c>
       <c r="M42" t="str">
-        <v>https://www.airbnb.co.uk/rooms/10871197?source_impression_id=p3_1740661668_P3_fwWlj1bivR6H3</v>
+        <v>https://www.airbnb.co.uk/rooms/51934747?viralityEntryPoint=1&amp;unique_share_id=280280D3-196D-4375-9B58-8FF86E7EBE4A&amp;slcid=38c444deb09341219c6ca12571e5816c&amp;s=76&amp;set_everest_cookie_on_new_domain=1763389850.EAMTU1OWQ3NTQ2ZDFiOG.XV6T12sKRWC7EKIiTAk4y3A_8-n_a-NjP8ad81Kk9BE&amp;adults=1&amp;slug=r5JDBqL7&amp;source_impression_id=p3_1763392796_P3BATNGa0g9jlEMG&amp;_set_bev_on_new_domain=1763389850_EAMWJhNDYwNDNhYT</v>
       </c>
       <c r="N42" t="str">
-        <v>Julie madison-hill</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O42" t="str">
-        <v>enquiries@madison-hill.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P42" t="str">
-        <v>0208 675 8308</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SW13 9JR</v>
+        <v>SW12 9PB</v>
       </c>
       <c r="B43" t="str">
-        <v>49 LONSDALE ROAD SW13 9JR</v>
+        <v>Englewood Road, London SW12 9PB</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G43" t="str">
         <v>no</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -59124,36 +59133,27 @@
         <v>0</v>
       </c>
       <c r="L43" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/7287af9dc25b38afd8678b4c</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/2d3fdb9413b46301a34b45e9</v>
       </c>
       <c r="M43" t="str">
-        <v>https://www.airbnb.co.uk/rooms/25441054?preview_for_ml=true&amp;source_impression_id=p3_1706274270_mwukjB1UTePRs7SA</v>
-      </c>
-      <c r="N43" t="str">
-        <v>Plamena</v>
-      </c>
-      <c r="O43" t="str">
-        <v>manage@lettsgetsmart.com</v>
-      </c>
-      <c r="P43" t="str">
-        <v>07414 549781</v>
+        <v>https://air.tl/ruW1v2CN</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SW15 1JS</v>
+        <v>SW12 9RT</v>
       </c>
       <c r="B44" t="str">
-        <v>17 Glendarvon St, London SW15 1JS, UK</v>
+        <v>Fernlea Rd, London SW12 9RT, UK</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="str">
         <v>off-site-chargeable</v>
@@ -59162,57 +59162,57 @@
         <v>chargeable</v>
       </c>
       <c r="H44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ff8a80804aadcabd6ed89e</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67c065595139c18f3e607cb5</v>
       </c>
       <c r="M44" t="str">
-        <v>https://www.booking.com/hotel/gb/ivy-glendarvon-street-pro-managed-greater-london.en-gb.html?aid=304142&amp;label=gen173rf-10CAQoggJCJHNlYXJjaF9iYXJ0b24rcmQsK2xvbmRvbit3MTQrOWhiLCt1a0gJWANoUIgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAaICE215aG9tZWlzeW91cnMuY28udWuoAgG4AtuO_scGwAIB0gIkODdiYWFkNmYtNDI1YS00MjcwLWI0NzEtY2U5MjEyYzQ5ZDc12AIB4AIB&amp;sid=4cf42517a0ba06b7a74d7b58c5f8698a&amp;all_sr_blocks=1187533302_391336208_1_0_0&amp;checkin=2025-11-05&amp;checkout=2025-12-17&amp;dist=0&amp;group_adults=1&amp;group_children=0&amp;hapos=15&amp;highlighted_blocks=1187533302_391336208_1_0_0&amp;hpos=15&amp;matching_block_id=1187533302_391336208_1_0_0&amp;nflt=entire_place_bedroom_count%3D3&amp;no_rooms=1&amp;req_adults=1&amp;req_children=0&amp;room1=A&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=1187533302_391336208_1_0_0__1249385&amp;srepoch=1761576919&amp;srpvid=52a968ad2b3a01d5&amp;type=total&amp;ucfs=1&amp;#map_closed</v>
+        <v>https://www.airbnb.co.uk/rooms/10871197?source_impression_id=p3_1740661668_P3_fwWlj1bivR6H3</v>
       </c>
       <c r="N44" t="str">
-        <v>Ivy Letting</v>
+        <v>Julie madison-hill</v>
       </c>
       <c r="O44" t="str">
-        <v>guests@ivylettings.com</v>
+        <v>enquiries@madison-hill.com</v>
       </c>
       <c r="P44" t="str">
-        <v>+44 20 7349 7015</v>
+        <v>0208 675 8308</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SW15 3JA</v>
+        <v>SW13 9JR</v>
       </c>
       <c r="B45" t="str">
-        <v>West Hill, London SW15 3JA, UK</v>
+        <v>49 LONSDALE ROAD SW13 9JR</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
         <v>on-site-free</v>
       </c>
       <c r="G45" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -59224,45 +59224,45 @@
         <v>0</v>
       </c>
       <c r="L45" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6862996087dcaa2b6427acce</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/7287af9dc25b38afd8678b4c</v>
       </c>
       <c r="M45" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1001938310104497891?source_impression_id=p3_1751292063_P3yrtfXNUxr4FnUj</v>
+        <v>https://www.airbnb.co.uk/rooms/25441054?preview_for_ml=true&amp;source_impression_id=p3_1706274270_mwukjB1UTePRs7SA</v>
       </c>
       <c r="N45" t="str">
-        <v>George</v>
+        <v>Plamena</v>
       </c>
       <c r="O45" t="str">
-        <v>fake@eeemail.com</v>
+        <v>manage@lettsgetsmart.com</v>
       </c>
       <c r="P45" t="str">
-        <v>07985386107</v>
+        <v>07414 549781</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SW15 6DG</v>
+        <v>SW15 1JS</v>
       </c>
       <c r="B46" t="str">
-        <v>Humphry House, Whitnell Way, London SW15 6DG, UK</v>
+        <v>17 Glendarvon St, London SW15 1JS, UK</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G46" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -59274,36 +59274,36 @@
         <v>0</v>
       </c>
       <c r="L46" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6870e89a27c01b288f21fd70</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ff8a80804aadcabd6ed89e</v>
       </c>
       <c r="M46" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1440383975046450645?source_impression_id=p3_1752229867_P3kvC1_2DKAJi0on</v>
+        <v>https://www.booking.com/hotel/gb/ivy-glendarvon-street-pro-managed-greater-london.en-gb.html?aid=304142&amp;label=gen173rf-10CAQoggJCJHNlYXJjaF9iYXJ0b24rcmQsK2xvbmRvbit3MTQrOWhiLCt1a0gJWANoUIgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAaICE215aG9tZWlzeW91cnMuY28udWuoAgG4AtuO_scGwAIB0gIkODdiYWFkNmYtNDI1YS00MjcwLWI0NzEtY2U5MjEyYzQ5ZDc12AIB4AIB&amp;sid=4cf42517a0ba06b7a74d7b58c5f8698a&amp;all_sr_blocks=1187533302_391336208_1_0_0&amp;checkin=2025-11-05&amp;checkout=2025-12-17&amp;dist=0&amp;group_adults=1&amp;group_children=0&amp;hapos=15&amp;highlighted_blocks=1187533302_391336208_1_0_0&amp;hpos=15&amp;matching_block_id=1187533302_391336208_1_0_0&amp;nflt=entire_place_bedroom_count%3D3&amp;no_rooms=1&amp;req_adults=1&amp;req_children=0&amp;room1=A&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=1187533302_391336208_1_0_0__1249385&amp;srepoch=1761576919&amp;srpvid=52a968ad2b3a01d5&amp;type=total&amp;ucfs=1&amp;#map_closed</v>
       </c>
       <c r="N46" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Ivy Letting</v>
       </c>
       <c r="O46" t="str">
-        <v>temp@airbnb.com</v>
+        <v>guests@ivylettings.com</v>
       </c>
       <c r="P46" t="str">
-        <v>00000000000</v>
+        <v>+44 20 7349 7015</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SW18 1AG</v>
+        <v>SW15 2SY</v>
       </c>
       <c r="B47" t="str">
-        <v>Causeway House, 5 Creek Ln, London SW18 1AG, UK</v>
+        <v>Woodlands Gate, Woodlands Way, London SW15 2SY, UK</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
         <v>off-site-chargeable</v>
@@ -59324,27 +59324,27 @@
         <v>0</v>
       </c>
       <c r="L47" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68398ec84c57ed8b6ad5496d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/691f386a8f355e3a298ff2ac</v>
       </c>
       <c r="M47" t="str">
-        <v>https://www.airbnb.co.uk/rooms/635926438522081129?viralityEntryPoint=1&amp;unique_share_id=63E88097-C1F8-49B6-9B9C-6B3108DA8A54&amp;slcid=d3631a9b903840b6aed6c1dae8b7c06f&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=5IQgcw6S&amp;source_impression_id=p3_1748602421_P3mez1C14qWjq0U3</v>
+        <v>https://www.airbnb.co.uk/rooms/1483926552425480336?source_impression_id=p3_1763653589_P3ByqoqK_yuKJ2iE</v>
       </c>
       <c r="N47" t="str">
-        <v>Jela</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O47" t="str">
-        <v>danijelaukovic@icloud.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P47" t="str">
-        <v>07919231122</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SW18 1DB</v>
+        <v>SW15 3JA</v>
       </c>
       <c r="B48" t="str">
-        <v>Smugglers Way, London SW18 1DB, UK</v>
+        <v>West Hill, London SW15 3JA, UK</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -59353,16 +59353,16 @@
         <v>2</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G48" t="str">
         <v>chargeable</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -59374,27 +59374,27 @@
         <v>0</v>
       </c>
       <c r="L48" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67d44db8dbd5b96138954bef</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6862996087dcaa2b6427acce</v>
       </c>
       <c r="M48" t="str">
-        <v>https://www.airbnb.co.uk/rooms/987571324722900124?source_impression_id=p3_1741966693_P3swdzkwQsdxlkv6</v>
+        <v>https://www.airbnb.co.uk/rooms/1001938310104497891?source_impression_id=p3_1751292063_P3yrtfXNUxr4FnUj</v>
       </c>
       <c r="N48" t="str">
-        <v>Airbnb Temporary</v>
+        <v>George</v>
       </c>
       <c r="O48" t="str">
-        <v>temp@airbnb.com</v>
+        <v>fake@eeemail.com</v>
       </c>
       <c r="P48" t="str">
-        <v>00000000000</v>
+        <v>07985386107</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SW18 1SA</v>
+        <v>SW15 6DG</v>
       </c>
       <c r="B49" t="str">
-        <v>Enterprise Way, London SW18 1FZ, UK</v>
+        <v>Humphry House, Whitnell Way, London SW15 6DG, UK</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -59415,7 +59415,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
@@ -59424,27 +59424,27 @@
         <v>0</v>
       </c>
       <c r="L49" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67ebfd9f5be5942dcde57535</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6870e89a27c01b288f21fd70</v>
       </c>
       <c r="M49" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1364312467482435180?adults=1&amp;children=3&amp;search_mode=regular_search&amp;source_impression_id=p3_1743517923_P32JIriwn2jQy_BP&amp;previous_page_section_name=1000&amp;federated_search_id=394715b1-afd3-4176-ade9-9f38b910847c&amp;guests=1&amp;check_in=2025-04-02&amp;check_out=2025-04-09</v>
+        <v>https://www.airbnb.co.uk/rooms/1440383975046450645?source_impression_id=p3_1752229867_P3kvC1_2DKAJi0on</v>
       </c>
       <c r="N49" t="str">
-        <v>Conor | CTO Properties</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O49" t="str">
-        <v>conor@ctoproperty.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P49" t="str">
-        <v>07961843895</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SW18 1TS</v>
+        <v>SW18 1AG</v>
       </c>
       <c r="B50" t="str">
-        <v>Juniper Dr, London, UK</v>
+        <v>Causeway House, 5 Creek Ln, London SW18 1AG, UK</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -59474,36 +59474,36 @@
         <v>0</v>
       </c>
       <c r="L50" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/69136a93d7a9e69c6219c48f</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68398ec84c57ed8b6ad5496d</v>
       </c>
       <c r="M50" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1257283505659972907?source_impression_id=p3_1762879878_P3ydb_qCGfPnnU2k&amp;check_in=2025-11-12&amp;guests=1&amp;adults=1&amp;check_out=2025-11-25</v>
+        <v>https://www.airbnb.co.uk/rooms/635926438522081129?viralityEntryPoint=1&amp;unique_share_id=63E88097-C1F8-49B6-9B9C-6B3108DA8A54&amp;slcid=d3631a9b903840b6aed6c1dae8b7c06f&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=5IQgcw6S&amp;source_impression_id=p3_1748602421_P3mez1C14qWjq0U3</v>
       </c>
       <c r="N50" t="str">
-        <v>Conor | CTO Properties</v>
+        <v>Jela</v>
       </c>
       <c r="O50" t="str">
-        <v>conor@ctoproperty.co.uk</v>
+        <v>danijelaukovic@icloud.com</v>
       </c>
       <c r="P50" t="str">
-        <v>07961843895</v>
+        <v>07919231122</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SW18 2RT</v>
+        <v>SW18 1DB</v>
       </c>
       <c r="B51" t="str">
-        <v>194 St Ann's Hill, London SW18 2RT, UK</v>
+        <v>Smugglers Way, London SW18 1DB, UK</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
         <v>off-site-chargeable</v>
@@ -59524,33 +59524,33 @@
         <v>0</v>
       </c>
       <c r="L51" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/673cae0ad961917ed25910a1</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67d44db8dbd5b96138954bef</v>
       </c>
       <c r="M51" t="str">
-        <v>https://www.booking.com/hotel/gb/stunning-3-bed-apartment-in-wandsworth.en-gb.html?aid=304142&amp;label=gen173nr-1FCAEoggI46AdIM1gEaLgCiAEBmAEJuAEXyAEM2AEB6AEB-AEMiAIBqAIDuAKd0PK5BsACAdICJDQ5OGE1MmNkLWU1NzAtNDY0MS1hYjcxLTNiZGFhYmQyODFhOdgCBuACAQ&amp;sid=c56aa9f495ded14af2d4d054a903fa6d&amp;all_sr_blocks=1268913901_399618370_6_0_0&amp;checkin=2024-11-22&amp;checkout=2024-11-29&amp;dist=0&amp;group_adults=3&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1268913901_399618370_6_0_0&amp;hpos=1&amp;matching_block_id=1268913901_399618370_6_0_0&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=2&amp;req_adults=3&amp;req_children=0&amp;room1=A&amp;room2=A%2CA&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=1268913901_399618370_6_0_0__293170&amp;srepoch=1732029116&amp;srpvid=229b6a8f540900fd&amp;type=total&amp;ucfs=1&amp;</v>
+        <v>https://www.airbnb.co.uk/rooms/987571324722900124?source_impression_id=p3_1741966693_P3swdzkwQsdxlkv6</v>
       </c>
       <c r="N51" t="str">
-        <v>Starhost Residences</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O51" t="str">
-        <v>enquiries@starhost-residences.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P51" t="str">
-        <v xml:space="preserve"> +44 (0)333 900 1300</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SW18 4RD</v>
+        <v>SW18 1SA</v>
       </c>
       <c r="B52" t="str">
-        <v>10 Red Lion Square, London SW18 4RD, UK</v>
+        <v>Enterprise Way, London SW18 1FZ, UK</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -59559,13 +59559,13 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G52" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
       </c>
       <c r="I52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
@@ -59574,36 +59574,36 @@
         <v>0</v>
       </c>
       <c r="L52" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/688b8052cd02201a20de8d6f</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67ebfd9f5be5942dcde57535</v>
       </c>
       <c r="M52" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1009270252443231371?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=d98cbd2a-2989-4877-accc-cd2b46dd64d7&amp;source_impression_id=p3_1753972112_P3xoMZh5DMyyyF-l&amp;check_in=2025-08-18&amp;check_out=2025-09-01&amp;translate_ugc=true</v>
+        <v>https://www.airbnb.co.uk/rooms/1364312467482435180?adults=1&amp;children=3&amp;search_mode=regular_search&amp;source_impression_id=p3_1743517923_P32JIriwn2jQy_BP&amp;previous_page_section_name=1000&amp;federated_search_id=394715b1-afd3-4176-ade9-9f38b910847c&amp;guests=1&amp;check_in=2025-04-02&amp;check_out=2025-04-09</v>
       </c>
       <c r="N52" t="str">
-        <v>Shloime</v>
+        <v>Conor | CTO Properties</v>
       </c>
       <c r="O52" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>conor@ctoproperty.co.uk</v>
       </c>
       <c r="P52" t="str">
-        <v>07867290839</v>
+        <v>07961843895</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SW18 5HL</v>
+        <v>SW18 1TS</v>
       </c>
       <c r="B53" t="str">
-        <v xml:space="preserve"> SW18 5HL</v>
+        <v>Juniper Dr, London, UK</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
         <v>off-site-chargeable</v>
@@ -59624,24 +59624,33 @@
         <v>0</v>
       </c>
       <c r="L53" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/f80ff91c809100041d39121a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/69136a93d7a9e69c6219c48f</v>
       </c>
       <c r="M53" t="str">
-        <v>https://air.tl/EyQdXeMH</v>
+        <v>https://www.airbnb.co.uk/rooms/1257283505659972907?source_impression_id=p3_1762879878_P3ydb_qCGfPnnU2k&amp;check_in=2025-11-12&amp;guests=1&amp;adults=1&amp;check_out=2025-11-25</v>
+      </c>
+      <c r="N53" t="str">
+        <v>Conor | CTO Properties</v>
+      </c>
+      <c r="O53" t="str">
+        <v>conor@ctoproperty.co.uk</v>
+      </c>
+      <c r="P53" t="str">
+        <v>07961843895</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SW18 5NA</v>
+        <v>SW18 2RT</v>
       </c>
       <c r="B54" t="str">
-        <v>Pirbright Rd, London SW18 5NA, UK</v>
+        <v>194 St Ann's Hill, London SW18 2RT, UK</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -59653,7 +59662,7 @@
         <v>chargeable</v>
       </c>
       <c r="H54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -59665,27 +59674,27 @@
         <v>0</v>
       </c>
       <c r="L54" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68386d36307566446d3b927b</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/673cae0ad961917ed25910a1</v>
       </c>
       <c r="M54" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1079637894119073554?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1748528182_P32GOVYgGhQshwSA</v>
+        <v>https://www.booking.com/hotel/gb/stunning-3-bed-apartment-in-wandsworth.en-gb.html?aid=304142&amp;label=gen173nr-1FCAEoggI46AdIM1gEaLgCiAEBmAEJuAEXyAEM2AEB6AEB-AEMiAIBqAIDuAKd0PK5BsACAdICJDQ5OGE1MmNkLWU1NzAtNDY0MS1hYjcxLTNiZGFhYmQyODFhOdgCBuACAQ&amp;sid=c56aa9f495ded14af2d4d054a903fa6d&amp;all_sr_blocks=1268913901_399618370_6_0_0&amp;checkin=2024-11-22&amp;checkout=2024-11-29&amp;dist=0&amp;group_adults=3&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1268913901_399618370_6_0_0&amp;hpos=1&amp;matching_block_id=1268913901_399618370_6_0_0&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=2&amp;req_adults=3&amp;req_children=0&amp;room1=A&amp;room2=A%2CA&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=1268913901_399618370_6_0_0__293170&amp;srepoch=1732029116&amp;srpvid=229b6a8f540900fd&amp;type=total&amp;ucfs=1&amp;</v>
       </c>
       <c r="N54" t="str">
-        <v>Mo</v>
+        <v>Starhost Residences</v>
       </c>
       <c r="O54" t="str">
-        <v>info@milamanagement.co.uk</v>
+        <v>enquiries@starhost-residences.uk</v>
       </c>
       <c r="P54" t="str">
-        <v>+447888003322</v>
+        <v xml:space="preserve"> +44 (0)333 900 1300</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SW18 5PU</v>
+        <v>SW18 4RD</v>
       </c>
       <c r="B55" t="str">
-        <v>2 Sutherland Grove, London SW18 5PU, UK</v>
+        <v>10 Red Lion Square, London SW18 4RD, UK</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -59697,10 +59706,10 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G55" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
@@ -59715,27 +59724,27 @@
         <v>0</v>
       </c>
       <c r="L55" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b855b1fead75d2c44e3a36</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/688b8052cd02201a20de8d6f</v>
       </c>
       <c r="M55" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1228407659228370029?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756910897_P3d4rGNOSuNMzb73</v>
+        <v>https://www.airbnb.co.uk/rooms/1009270252443231371?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=d98cbd2a-2989-4877-accc-cd2b46dd64d7&amp;source_impression_id=p3_1753972112_P3xoMZh5DMyyyF-l&amp;check_in=2025-08-18&amp;check_out=2025-09-01&amp;translate_ugc=true</v>
       </c>
       <c r="N55" t="str">
-        <v>Waleed Khalid</v>
+        <v>Shloime</v>
       </c>
       <c r="O55" t="str">
-        <v>fakewaleed@gmail.com</v>
+        <v>shloime@hometohost.co.uk</v>
       </c>
       <c r="P55" t="str">
-        <v>+44 7930 000039</v>
+        <v>07867290839</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SW19 1EW</v>
+        <v>SW18 5HL</v>
       </c>
       <c r="B56" t="str">
-        <v>Latimer Rd, London SW19 1EW, UK</v>
+        <v xml:space="preserve"> SW18 5HL</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -59744,10 +59753,10 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F56" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G56" t="str">
         <v>chargeable</v>
@@ -59765,36 +59774,27 @@
         <v>0</v>
       </c>
       <c r="L56" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6911fc4095be8a437746e3ef</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/f80ff91c809100041d39121a</v>
       </c>
       <c r="M56" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1413655981726899322?source_impression_id=p3_1762786273_P3yy5MtR-yAASgOI</v>
-      </c>
-      <c r="N56" t="str">
-        <v>Shan</v>
-      </c>
-      <c r="O56" t="str">
-        <v>shan@locateproperties.co.uk</v>
-      </c>
-      <c r="P56" t="str">
-        <v>+447984978371</v>
+        <v>https://air.tl/EyQdXeMH</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SW19 1HL</v>
+        <v>SW18 5NA</v>
       </c>
       <c r="B57" t="str">
-        <v>Haydons Rd, London SW19 1HL, UK</v>
+        <v>Pirbright Rd, London SW18 5NA, UK</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="str">
         <v>off-site-chargeable</v>
@@ -59815,42 +59815,42 @@
         <v>0</v>
       </c>
       <c r="L57" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68bffa60c7272e799e743a1c</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68386d36307566446d3b927b</v>
       </c>
       <c r="M57" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1484591287869484431?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1757411751_P35Om4HzLwUvoenR</v>
+        <v>https://www.airbnb.co.uk/rooms/1079637894119073554?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1748528182_P32GOVYgGhQshwSA</v>
       </c>
       <c r="N57" t="str">
-        <v>Sophia Dick</v>
+        <v>Mo</v>
       </c>
       <c r="O57" t="str">
-        <v>info@iturastay.com</v>
+        <v>info@milamanagement.co.uk</v>
       </c>
       <c r="P57" t="str">
-        <v xml:space="preserve"> 0203 576 5615</v>
+        <v>+447888003322</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SW19 1HQ</v>
+        <v>SW18 5PU</v>
       </c>
       <c r="B58" t="str">
-        <v>Haydons Rd, London SW19 1HQ, UK</v>
+        <v>2 Sutherland Grove, London SW18 5PU, UK</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G58" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
@@ -59865,42 +59865,42 @@
         <v>0</v>
       </c>
       <c r="L58" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/676431d127d5845172aed08d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b855b1fead75d2c44e3a36</v>
       </c>
       <c r="M58" t="str">
-        <v>https://www.airbnb.co.uk/rooms/823105848999902702?source_impression_id=p3_1763040187_P39WBssyUvP5qJV-</v>
+        <v>https://www.airbnb.co.uk/rooms/1228407659228370029?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756910897_P3d4rGNOSuNMzb73</v>
       </c>
       <c r="N58" t="str">
-        <v>Chris Watson</v>
+        <v>Waleed Khalid</v>
       </c>
       <c r="O58" t="str">
-        <v>info@keapartments.com</v>
+        <v>waleed.khalid2021@hotmail.com</v>
       </c>
       <c r="P58" t="str">
-        <v>02080793044</v>
+        <v>+44 7930 000039</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SW19 1PA</v>
+        <v>SW19 1EW</v>
       </c>
       <c r="B59" t="str">
-        <v xml:space="preserve">84 Pelham Road, London, SW19 1PA, United Kingdom </v>
+        <v>Latimer Rd, London SW19 1EW, UK</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>on-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G59" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H59" t="b">
         <v>0</v>
@@ -59915,45 +59915,45 @@
         <v>0</v>
       </c>
       <c r="L59" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/17d8dded2953a8cdbb425040</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6911fc4095be8a437746e3ef</v>
       </c>
       <c r="M59" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1146401263521647389?viralityEntryPoint=1&amp;unique_share_id=7E53F433-AB53-4615-B766-34A1AD169DFE&amp;slcid=38cac691d6a347cab7fc06f2eba91f33&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=eWdcAVFa&amp;source_impression_id=p3_1721814798_P39ZC0rCy3MEU2d0</v>
+        <v>https://www.airbnb.co.uk/rooms/1413655981726899322?source_impression_id=p3_1762786273_P3yy5MtR-yAASgOI</v>
       </c>
       <c r="N59" t="str">
-        <v>Omar</v>
+        <v>Shan</v>
       </c>
       <c r="O59" t="str">
-        <v>owner@simms-service-accommodation.co.uk</v>
+        <v>shan@locateproperties.co.uk</v>
       </c>
       <c r="P59" t="str">
-        <v>07961327520</v>
+        <v>+447984978371</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SW19 2DE</v>
+        <v>SW19 1HL</v>
       </c>
       <c r="B60" t="str">
-        <v>123 Boundary Rd, London SW19 2DE, UK</v>
+        <v>Haydons Rd, London SW19 1HL, UK</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G60" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -59965,42 +59965,42 @@
         <v>0</v>
       </c>
       <c r="L60" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f750219dfafc38bc901e25</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68bffa60c7272e799e743a1c</v>
       </c>
       <c r="M60" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1131681478410995049?adults=3&amp;check_in=2025-10-24&amp;check_out=2025-12-05&amp;children=2&amp;location=CR4%203DE&amp;search_mode=regular_search&amp;source_impression_id=p3_1761038118_P3Iem5BVKcMk9Rpo&amp;previous_page_section_name=1001&amp;federated_search_id=2cacceb0-4bf7-480c-8a1c-237b208a783e</v>
+        <v>https://www.airbnb.co.uk/rooms/1484591287869484431?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1757411751_P35Om4HzLwUvoenR</v>
       </c>
       <c r="N60" t="str">
-        <v>Edison Keith</v>
+        <v>Sophia Dick</v>
       </c>
       <c r="O60" t="str">
-        <v>fabholidayrentals@zoho.com</v>
+        <v>info@iturastay.com</v>
       </c>
       <c r="P60" t="str">
-        <v>07899 983398</v>
+        <v xml:space="preserve"> 0203 576 5615</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SW19 2EA</v>
+        <v>SW19 1HQ</v>
       </c>
       <c r="B61" t="str">
-        <v>Fortescue Rd, London SW19 2EA, UK</v>
+        <v>Haydons Rd, London SW19 1HQ, UK</v>
       </c>
       <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61">
         <v>4</v>
       </c>
-      <c r="D61">
-        <v>6</v>
-      </c>
       <c r="E61">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F61" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G61" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
@@ -60015,27 +60015,27 @@
         <v>0</v>
       </c>
       <c r="L61" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68fb8366f911141e69a1a80e</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/676431d127d5845172aed08d</v>
       </c>
       <c r="M61" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1352378687658872800?adults=3&amp;check_in=2025-10-24&amp;check_out=2025-12-05&amp;children=2&amp;location=CR4%203DE&amp;search_mode=regular_search&amp;source_impression_id=p3_1761313174_P3jJqX0h6CGCVL4m&amp;previous_page_section_name=1001&amp;federated_search_id=20d7c7cf-0c57-41de-8f34-9fbb15ab9f8c</v>
+        <v>https://www.airbnb.co.uk/rooms/823105848999902702?source_impression_id=p3_1763040187_P39WBssyUvP5qJV-</v>
       </c>
       <c r="N61" t="str">
-        <v>Edison Keith</v>
+        <v>Chris Watson</v>
       </c>
       <c r="O61" t="str">
-        <v>fabholidayrentals@zoho.com</v>
+        <v>info@keapartments.com</v>
       </c>
       <c r="P61" t="str">
-        <v>07899 983398</v>
+        <v>02080793044</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SW19 4HD</v>
+        <v>SW19 1PA</v>
       </c>
       <c r="B62" t="str">
-        <v>Cranbrook Rd, London SW19 4HD, UK</v>
+        <v xml:space="preserve">84 Pelham Road, London, SW19 1PA, United Kingdom </v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -60044,13 +60044,13 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-chargeable</v>
       </c>
       <c r="G62" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H62" t="b">
         <v>0</v>
@@ -60065,42 +60065,42 @@
         <v>0</v>
       </c>
       <c r="L62" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68387fbf6c2ea1f15bd42377</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/17d8dded2953a8cdbb425040</v>
       </c>
       <c r="M62" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1413640443053905185?_set_bev_on_new_domain=1745425402_EAMWRkZDRiZWM0NT&amp;source_impression_id=p3_1748532739_P36oi_SGIFxp4UI8</v>
+        <v>https://www.airbnb.co.uk/rooms/1146401263521647389?viralityEntryPoint=1&amp;unique_share_id=7E53F433-AB53-4615-B766-34A1AD169DFE&amp;slcid=38cac691d6a347cab7fc06f2eba91f33&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=eWdcAVFa&amp;source_impression_id=p3_1721814798_P39ZC0rCy3MEU2d0</v>
       </c>
       <c r="N62" t="str">
-        <v>Shan</v>
+        <v>Omar</v>
       </c>
       <c r="O62" t="str">
-        <v>shan@locateproperties.co.uk</v>
+        <v>owner@simms-service-accommodation.co.uk</v>
       </c>
       <c r="P62" t="str">
-        <v>+447984978371</v>
+        <v>07961327520</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SW19 4HD</v>
+        <v>SW19 2DE</v>
       </c>
       <c r="B63" t="str">
-        <v>Cranbrook Rd, London SW19 4HD, UK</v>
+        <v>123 Boundary Rd, London SW19 2DE, UK</v>
       </c>
       <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
         <v>3</v>
       </c>
-      <c r="D63">
-        <v>4</v>
-      </c>
       <c r="E63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G63" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H63" t="b">
         <v>0</v>
@@ -60109,48 +60109,48 @@
         <v>0</v>
       </c>
       <c r="J63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/682c4ac0a67e14477a753321</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f750219dfafc38bc901e25</v>
       </c>
       <c r="M63" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1087629888198354779?source_impression_id=p3_1747732987_P3AxGlRbbJ_Gi-WK</v>
+        <v>https://www.airbnb.co.uk/rooms/1131681478410995049?adults=3&amp;check_in=2025-10-24&amp;check_out=2025-12-05&amp;children=2&amp;location=CR4%203DE&amp;search_mode=regular_search&amp;source_impression_id=p3_1761038118_P3Iem5BVKcMk9Rpo&amp;previous_page_section_name=1001&amp;federated_search_id=2cacceb0-4bf7-480c-8a1c-237b208a783e</v>
       </c>
       <c r="N63" t="str">
-        <v>Shan</v>
+        <v>Edison Keith / Ryan</v>
       </c>
       <c r="O63" t="str">
-        <v>shan@locateproperties.co.uk</v>
+        <v>fabholidayrentals@zoho.com</v>
       </c>
       <c r="P63" t="str">
-        <v>+447984978371</v>
+        <v>07899 983398</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SW19 6BU</v>
+        <v>SW19 2EA</v>
       </c>
       <c r="B64" t="str">
-        <v>50 Cambium, 1 Beatrice Place SW19 6BU</v>
+        <v>Fortescue Rd, London SW19 2EA, UK</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E64">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F64" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G64" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H64" t="b">
         <v>0</v>
@@ -60165,24 +60165,36 @@
         <v>0</v>
       </c>
       <c r="L64" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/711c358e33e9555c68a99103</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68fb8366f911141e69a1a80e</v>
+      </c>
+      <c r="M64" t="str">
+        <v>https://www.airbnb.co.uk/rooms/1352378687658872800?adults=3&amp;check_in=2025-10-24&amp;check_out=2025-12-05&amp;children=2&amp;location=CR4%203DE&amp;search_mode=regular_search&amp;source_impression_id=p3_1761313174_P3jJqX0h6CGCVL4m&amp;previous_page_section_name=1001&amp;federated_search_id=20d7c7cf-0c57-41de-8f34-9fbb15ab9f8c</v>
+      </c>
+      <c r="N64" t="str">
+        <v>Edison Keith / Ryan</v>
+      </c>
+      <c r="O64" t="str">
+        <v>fabholidayrentals@zoho.com</v>
+      </c>
+      <c r="P64" t="str">
+        <v>07899 983398</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SW19 8HB</v>
+        <v>SW19 4HD</v>
       </c>
       <c r="B65" t="str">
-        <v>Havelock Rd, London SW19 8HB, UK</v>
+        <v>Cranbrook Rd, London SW19 4HD, UK</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65">
         <v>3</v>
-      </c>
-      <c r="E65">
-        <v>1</v>
       </c>
       <c r="F65" t="str">
         <v>off-site-chargeable</v>
@@ -60191,7 +60203,7 @@
         <v>chargeable</v>
       </c>
       <c r="H65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -60203,18 +60215,27 @@
         <v>0</v>
       </c>
       <c r="L65" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6723ae0bce987810b2b275d4</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/682c4ac0a67e14477a753321</v>
       </c>
       <c r="M65" t="str">
-        <v>https://www.airbnb.co.uk/rooms/49684638?source_impression_id=p3_1730391072_P3ceGnz6iP_5CwIn</v>
+        <v>https://www.airbnb.co.uk/rooms/1087629888198354779?source_impression_id=p3_1747732987_P3AxGlRbbJ_Gi-WK</v>
+      </c>
+      <c r="N65" t="str">
+        <v>Shan</v>
+      </c>
+      <c r="O65" t="str">
+        <v>shan@locateproperties.co.uk</v>
+      </c>
+      <c r="P65" t="str">
+        <v>+447984978371</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SW4 0NG</v>
+        <v>SW19 4HD</v>
       </c>
       <c r="B66" t="str">
-        <v>The Chase, London SW4, UK</v>
+        <v>Cranbrook Rd, London SW19 4HD, UK</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -60223,13 +60244,13 @@
         <v>2</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G66" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
@@ -60244,27 +60265,36 @@
         <v>0</v>
       </c>
       <c r="L66" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6774102b757ee58fb648005a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68387fbf6c2ea1f15bd42377</v>
       </c>
       <c r="M66" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1142646551983468696?adults=2&amp;search_mode=regular_search&amp;check_in=2024-12-31&amp;check_out=2025-01-10&amp;source_impression_id=p3_1735659108_P3YXF9jCJbpHyxmd&amp;previous_page_section_name=1000&amp;federated_search_id=ea1b650c-bcc8-4ec1-9e70-2c6e9702f7e4&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
+        <v>https://www.airbnb.co.uk/rooms/1413640443053905185?_set_bev_on_new_domain=1745425402_EAMWRkZDRiZWM0NT&amp;source_impression_id=p3_1748532739_P36oi_SGIFxp4UI8</v>
+      </c>
+      <c r="N66" t="str">
+        <v>Shan</v>
+      </c>
+      <c r="O66" t="str">
+        <v>shan@locateproperties.co.uk</v>
+      </c>
+      <c r="P66" t="str">
+        <v>+447984978371</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SW4 6ER</v>
+        <v>SW19 6BU</v>
       </c>
       <c r="B67" t="str">
-        <v>28 Edgeley Rd, London SW4 6ER, UK</v>
+        <v>50 Cambium, 1 Beatrice Place SW19 6BU</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F67" t="str">
         <v>off-site-chargeable</v>
@@ -60285,33 +60315,21 @@
         <v>0</v>
       </c>
       <c r="L67" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f6210db8c1acfaf83a2dd9</v>
-      </c>
-      <c r="M67" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1518286992453752193?source_impression_id=p3_1760960361_P366lJydUUjWbW4N</v>
-      </c>
-      <c r="N67" t="str">
-        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
-      </c>
-      <c r="O67" t="str">
-        <v>Accommodation@calbrahomes.com</v>
-      </c>
-      <c r="P67" t="str">
-        <v>02045784820</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/711c358e33e9555c68a99103</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SW4 6ER</v>
+        <v>SW19 8HB</v>
       </c>
       <c r="B68" t="str">
-        <v>28 Edgeley Rd, London SW4 6ER, UK</v>
+        <v>Havelock Rd, London SW19 8HB, UK</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -60323,7 +60341,7 @@
         <v>chargeable</v>
       </c>
       <c r="H68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -60335,33 +60353,24 @@
         <v>0</v>
       </c>
       <c r="L68" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f62078b8c1acfaf83a293f</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6723ae0bce987810b2b275d4</v>
       </c>
       <c r="M68" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1520225287965889439?source_impression_id=p3_1760960259_P3-e1vBE0lb2sVw-</v>
-      </c>
-      <c r="N68" t="str">
-        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
-      </c>
-      <c r="O68" t="str">
-        <v>Accommodation@calbrahomes.com</v>
-      </c>
-      <c r="P68" t="str">
-        <v>02045784820</v>
+        <v>https://www.airbnb.co.uk/rooms/49684638?source_impression_id=p3_1730391072_P3ceGnz6iP_5CwIn</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SW4 7DW</v>
+        <v>SW4 0NG</v>
       </c>
       <c r="B69" t="str">
-        <v>13B Northbourne Rd, London SW4 7DW, UK</v>
+        <v>The Chase, London SW4, UK</v>
       </c>
       <c r="C69">
         <v>2</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -60370,7 +60379,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G69" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H69" t="b">
         <v>0</v>
@@ -60385,27 +60394,18 @@
         <v>0</v>
       </c>
       <c r="L69" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f6050fc22a16f688dffa98</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6774102b757ee58fb648005a</v>
       </c>
       <c r="M69" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1292903886306266660?source_impression_id=p3_1760953353_P35Kl9WUh6aiA7pg</v>
-      </c>
-      <c r="N69" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-      <c r="O69" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="P69" t="str">
-        <v>00000000000</v>
+        <v>https://www.airbnb.co.uk/rooms/1142646551983468696?adults=2&amp;search_mode=regular_search&amp;check_in=2024-12-31&amp;check_out=2025-01-10&amp;source_impression_id=p3_1735659108_P3YXF9jCJbpHyxmd&amp;previous_page_section_name=1000&amp;federated_search_id=ea1b650c-bcc8-4ec1-9e70-2c6e9702f7e4&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SW4 7NA</v>
+        <v>SW4 6ER</v>
       </c>
       <c r="B70" t="str">
-        <v>47 Tremadoc Road SW4 7NA</v>
+        <v>28 Edgeley Rd, London SW4 6ER, UK</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -60417,13 +60417,13 @@
         <v>1</v>
       </c>
       <c r="F70" t="str">
-        <v>on-site-chargeable</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G70" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="b">
         <v>0</v>
@@ -60435,18 +60435,27 @@
         <v>0</v>
       </c>
       <c r="L70" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/38cd6b55e9e8a0efc5eea30f</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f6210db8c1acfaf83a2dd9</v>
       </c>
       <c r="M70" t="str">
-        <v>https://thehomehandover.bookeddirectly.com/g/greater-london/the-finest-flat-in-clapham/aafd79?number_of_guests=1</v>
+        <v>https://www.airbnb.co.uk/rooms/1518286992453752193?source_impression_id=p3_1760960361_P366lJydUUjWbW4N</v>
+      </c>
+      <c r="N70" t="str">
+        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
+      </c>
+      <c r="O70" t="str">
+        <v>Accommodation@calbrahomes.com</v>
+      </c>
+      <c r="P70" t="str">
+        <v>02045784820</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SW4 7NE</v>
+        <v>SW4 6ER</v>
       </c>
       <c r="B71" t="str">
-        <v>Tremadoc Rd, London SW4, UK</v>
+        <v>28 Edgeley Rd, London SW4 6ER, UK</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -60464,22 +60473,22 @@
         <v>chargeable</v>
       </c>
       <c r="H71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
       </c>
       <c r="J71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f61e62b8c1acfaf83a1edd</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f62078b8c1acfaf83a293f</v>
       </c>
       <c r="M71" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1526228704852171095?source_impression_id=p3_1760959759_P3agcgCrYgwr91KV</v>
+        <v>https://www.airbnb.co.uk/rooms/1520225287965889439?source_impression_id=p3_1760960259_P3-e1vBE0lb2sVw-</v>
       </c>
       <c r="N71" t="str">
         <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
@@ -60493,25 +60502,25 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SW6 1FX</v>
+        <v>SW4 7DW</v>
       </c>
       <c r="B72" t="str">
-        <v>Columbia Gdns, London SW6 1FX, UK</v>
+        <v>13B Northbourne Rd, London SW4 7DW, UK</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G72" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
@@ -60526,145 +60535,136 @@
         <v>0</v>
       </c>
       <c r="L72" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67376830ab26894a88dc87eb</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f6050fc22a16f688dffa98</v>
       </c>
       <c r="M72" t="str">
-        <v>No Link</v>
+        <v>https://www.airbnb.co.uk/rooms/1292903886306266660?source_impression_id=p3_1760953353_P35Kl9WUh6aiA7pg</v>
       </c>
       <c r="N72" t="str">
-        <v>Dolly</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O72" t="str">
-        <v>info@citygateproperty.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P72" t="str">
-        <v>07958 571 307</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SW6 1JH</v>
+        <v>SW4 7NA</v>
       </c>
       <c r="B73" t="str">
-        <v>Knivet Rd, London SW6 1JH, UK</v>
+        <v>47 Tremadoc Road SW4 7NA</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F73" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-chargeable</v>
       </c>
       <c r="G73" t="str">
         <v>no</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
       </c>
       <c r="J73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="b">
         <v>0</v>
       </c>
       <c r="L73" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/681c81bb28ec8ecc9f26de98</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/38cd6b55e9e8a0efc5eea30f</v>
       </c>
       <c r="M73" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1410810886390500896?adults=1&amp;children=2&amp;search_mode=regular_search&amp;source_impression_id=p3_1746695048_P3uXZCuiO0qb01IY&amp;previous_page_section_name=1000&amp;federated_search_id=6a30acab-4353-4f2d-bb54-360d829c8d37&amp;guests=1&amp;check_in=2025-05-12&amp;check_out=2025-07-07</v>
-      </c>
-      <c r="N73" t="str">
-        <v>Smarthost</v>
-      </c>
-      <c r="O73" t="str">
-        <v>london@smarthost.co.uk</v>
-      </c>
-      <c r="P73" t="str">
-        <v>02078702393</v>
+        <v>https://thehomehandover.bookeddirectly.com/g/greater-london/the-finest-flat-in-clapham/aafd79?number_of_guests=1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SW6 2FH</v>
+        <v>SW4 7NE</v>
       </c>
       <c r="B74" t="str">
-        <v>213 Townmead Rd, London SW6 2FH, UK</v>
+        <v>Tremadoc Rd, London SW4, UK</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="F74" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G74" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
       </c>
       <c r="J74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68c7c84f12dadd6bb99cf8b0</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f61e62b8c1acfaf83a1edd</v>
       </c>
       <c r="M74" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1425306148594274436?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=644bdb1c-1904-4c32-8a33-371e3066d4b7&amp;source_impression_id=p3_1757923022_P3K1O7V68RZh8vEO</v>
+        <v>https://www.airbnb.co.uk/rooms/1526228704852171095?source_impression_id=p3_1760959759_P3agcgCrYgwr91KV</v>
       </c>
       <c r="N74" t="str">
-        <v>Maeve / Fernando</v>
+        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
       </c>
       <c r="O74" t="str">
-        <v>kingshomeaccommodation@gmail.com</v>
+        <v>Accommodation@calbrahomes.com</v>
       </c>
       <c r="P74" t="str">
-        <v>07462384273</v>
+        <v>02045784820</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SW6 2FW</v>
+        <v>SW6 1FX</v>
       </c>
       <c r="B75" t="str">
-        <v>Bagleys Ln, London SW6 2FW, UK</v>
+        <v>Columbia Gdns, London SW6 1FX, UK</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G75" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
@@ -60676,27 +60676,36 @@
         <v>0</v>
       </c>
       <c r="L75" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6717937c142c11ebc6764d85</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67376830ab26894a88dc87eb</v>
       </c>
       <c r="M75" t="str">
-        <v>https://www.airbnb.co.uk/rooms/710957353439782738?source_impression_id=p3_1729598092_P3jl9PbbjkkqEUDj</v>
+        <v>No Link</v>
+      </c>
+      <c r="N75" t="str">
+        <v>Dolly</v>
+      </c>
+      <c r="O75" t="str">
+        <v>info@citygateproperty.com</v>
+      </c>
+      <c r="P75" t="str">
+        <v>07958 571 307</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SW6 2NL</v>
+        <v>SW6 1JH</v>
       </c>
       <c r="B76" t="str">
-        <v>Oakbury Rd, London SW6 2NL, UK</v>
+        <v>Knivet Rd, London SW6 1JH, UK</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F76" t="str">
         <v>off-site-chargeable</v>
@@ -60705,60 +60714,60 @@
         <v>no</v>
       </c>
       <c r="H76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
       </c>
       <c r="J76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="b">
         <v>0</v>
       </c>
       <c r="L76" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67efc34d94f6397aff6e6b09</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/681c81bb28ec8ecc9f26de98</v>
       </c>
       <c r="M76" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1284644523885104959?adults=1&amp;check_in=2025-04-06&amp;check_out=2025-04-13&amp;children=3&amp;search_mode=regular_search&amp;infants=0&amp;pets=0&amp;source_impression_id=p3_1743758248_P3VqCK_hccSxRsPh&amp;previous_page_section_name=1000&amp;federated_search_id=10371133-7d29-445c-9bc9-91351f2190bc</v>
+        <v>https://www.airbnb.co.uk/rooms/1410810886390500896?adults=1&amp;children=2&amp;search_mode=regular_search&amp;source_impression_id=p3_1746695048_P3uXZCuiO0qb01IY&amp;previous_page_section_name=1000&amp;federated_search_id=6a30acab-4353-4f2d-bb54-360d829c8d37&amp;guests=1&amp;check_in=2025-05-12&amp;check_out=2025-07-07</v>
       </c>
       <c r="N76" t="str">
-        <v>Property By Capital</v>
+        <v>Smarthost</v>
       </c>
       <c r="O76" t="str">
-        <v>reservations@propertybycapital.com</v>
+        <v>london@smarthost.co.uk</v>
       </c>
       <c r="P76" t="str">
-        <v>0203 740 4160</v>
+        <v>02078702393</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SW6 2SX</v>
+        <v>SW6 2FH</v>
       </c>
       <c r="B77" t="str">
-        <v>Imperial Wharf the Boulevard, London SW6 2AN, UK</v>
+        <v>213 Townmead Rd, London SW6 2FH, UK</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G77" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
       </c>
       <c r="I77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -60767,33 +60776,33 @@
         <v>0</v>
       </c>
       <c r="L77" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68d25a48632451371295f1de</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68c7c84f12dadd6bb99cf8b0</v>
       </c>
       <c r="M77" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1170992155617631322?adults=1&amp;check_in=2025-09-26&amp;check_out=2025-10-24&amp;children=2&amp;search_mode=regular_search&amp;source_impression_id=p3_1758558357_P3Nq3_VYm0wF9ZmO&amp;previous_page_section_name=1000&amp;federated_search_id=6abfda14-088e-4a5c-99e3-2d1a8d51a64a</v>
+        <v>https://www.airbnb.co.uk/rooms/1425306148594274436?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=644bdb1c-1904-4c32-8a33-371e3066d4b7&amp;source_impression_id=p3_1757923022_P3K1O7V68RZh8vEO</v>
       </c>
       <c r="N77" t="str">
-        <v>Selina - Maison Christo Property</v>
+        <v>Maeve / Fernando</v>
       </c>
       <c r="O77" t="str">
-        <v>info@maisonchristoproperty.com</v>
+        <v>kingshomeaccommodation@gmail.com</v>
       </c>
       <c r="P77" t="str">
-        <v>07904842776</v>
+        <v>07462384273</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SW6 3JH</v>
+        <v>SW6 2FW</v>
       </c>
       <c r="B78" t="str">
-        <v>Fulham High St, London SW6 3JH, UK</v>
+        <v>Bagleys Ln, London SW6 2FW, UK</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -60802,48 +60811,39 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G78" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
       </c>
       <c r="J78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="b">
         <v>0</v>
       </c>
       <c r="L78" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/683dbbbaeffa632a8c42e6b8</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6717937c142c11ebc6764d85</v>
       </c>
       <c r="M78" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1334904307717044796?source_impression_id=p3_1748873697_P3wRlcH9ZGrgj6t-&amp;check_in=2025-06-09&amp;guests=1&amp;adults=1&amp;check_out=2025-07-11</v>
-      </c>
-      <c r="N78" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-      <c r="O78" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="P78" t="str">
-        <v>00000000000</v>
+        <v>https://www.airbnb.co.uk/rooms/710957353439782738?source_impression_id=p3_1729598092_P3jl9PbbjkkqEUDj</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SW6 3JH</v>
+        <v>SW6 2NL</v>
       </c>
       <c r="B79" t="str">
-        <v>Bishops Park House, 19A Fulham High St, London SW6 3JH, UK</v>
+        <v>Oakbury Rd, London SW6 2NL, UK</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -60852,7 +60852,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G79" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -60867,48 +60867,48 @@
         <v>0</v>
       </c>
       <c r="L79" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ff7398cc74457d5fc6c6f0</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67efc34d94f6397aff6e6b09</v>
       </c>
       <c r="M79" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1334904307717044796?source_impression_id=p3_1748622479_P3YMXSP6nC5WmynM</v>
+        <v>https://www.airbnb.co.uk/rooms/1284644523885104959?adults=1&amp;check_in=2025-04-06&amp;check_out=2025-04-13&amp;children=3&amp;search_mode=regular_search&amp;infants=0&amp;pets=0&amp;source_impression_id=p3_1743758248_P3VqCK_hccSxRsPh&amp;previous_page_section_name=1000&amp;federated_search_id=10371133-7d29-445c-9bc9-91351f2190bc</v>
       </c>
       <c r="N79" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Property By Capital</v>
       </c>
       <c r="O79" t="str">
-        <v>temp@airbnb.com</v>
+        <v>reservations@propertybycapital.com</v>
       </c>
       <c r="P79" t="str">
-        <v>00000000000</v>
+        <v>0203 740 4160</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SW6 5LN</v>
+        <v>SW6 2SX</v>
       </c>
       <c r="B80" t="str">
-        <v>Waldemar SW6 5LN</v>
+        <v>Imperial Wharf the Boulevard, London SW6 2AN, UK</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G80" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
       </c>
       <c r="I80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
@@ -60917,33 +60917,42 @@
         <v>0</v>
       </c>
       <c r="L80" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/2e912ae5a794cdf1916a0e67</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68d25a48632451371295f1de</v>
       </c>
       <c r="M80" t="str">
-        <v>https://www.airbnb.co.uk/rooms/600644958346284457?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=a8566da1-220b-4e6a-8919-5b3ecc90ebde&amp;source_impression_id=p3_1707324329_RZQTZjwM%2FyFvZC6T</v>
+        <v>https://www.airbnb.co.uk/rooms/1170992155617631322?adults=1&amp;check_in=2025-09-26&amp;check_out=2025-10-24&amp;children=2&amp;search_mode=regular_search&amp;source_impression_id=p3_1758558357_P3Nq3_VYm0wF9ZmO&amp;previous_page_section_name=1000&amp;federated_search_id=6abfda14-088e-4a5c-99e3-2d1a8d51a64a</v>
+      </c>
+      <c r="N80" t="str">
+        <v>Selina - Maison Christo Property</v>
+      </c>
+      <c r="O80" t="str">
+        <v>info@maisonchristoproperty.com</v>
+      </c>
+      <c r="P80" t="str">
+        <v>07904842776</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SW6 5QE</v>
+        <v>SW6 3JH</v>
       </c>
       <c r="B81" t="str">
-        <v>Fulham Ct, London SW6 5QE, UK</v>
+        <v>Fulham High St, London SW6 3JH, UK</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G81" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
@@ -60952,16 +60961,16 @@
         <v>0</v>
       </c>
       <c r="J81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="b">
         <v>0</v>
       </c>
       <c r="L81" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/69147549be7e6aa6430527cd</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/683dbbbaeffa632a8c42e6b8</v>
       </c>
       <c r="M81" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1532447556406552247?source_impression_id=p3_1762948170_P300eBg5HgsK7Cyj&amp;check_in=2025-11-25&amp;guests=1&amp;adults=1&amp;check_out=2025-12-23</v>
+        <v>https://www.airbnb.co.uk/rooms/1334904307717044796?source_impression_id=p3_1748873697_P3wRlcH9ZGrgj6t-&amp;check_in=2025-06-09&amp;guests=1&amp;adults=1&amp;check_out=2025-07-11</v>
       </c>
       <c r="N81" t="str">
         <v>Airbnb Temporary</v>
@@ -60975,19 +60984,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SW6 5QQ</v>
+        <v>SW6 3JH</v>
       </c>
       <c r="B82" t="str">
-        <v>Cassidy Rd, London SW6 5QQ, UK</v>
+        <v>Bishops Park House, 19A Fulham High St, London SW6 3JH, UK</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" t="str">
         <v>off-site-chargeable</v>
@@ -60996,10 +61005,10 @@
         <v>chargeable</v>
       </c>
       <c r="H82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
@@ -61008,10 +61017,10 @@
         <v>0</v>
       </c>
       <c r="L82" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6900a9342e7dc87a8799951b</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ff7398cc74457d5fc6c6f0</v>
       </c>
       <c r="M82" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1072946755416021325?adults=1&amp;check_in=2025-10-28&amp;check_out=2025-11-10&amp;children=5&amp;search_mode=regular_search&amp;infants=0&amp;pets=0&amp;source_impression_id=p3_1761647061_P3HjNMoMSugQ0mBC&amp;previous_page_section_name=1000&amp;federated_search_id=9ea658a4-3c21-4533-9c4d-f99b5bd5629b</v>
+        <v>https://www.airbnb.co.uk/rooms/1334904307717044796?source_impression_id=p3_1748622479_P3YMXSP6nC5WmynM</v>
       </c>
       <c r="N82" t="str">
         <v>Airbnb Temporary</v>
@@ -61025,25 +61034,25 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SW6 6AR</v>
+        <v>SW6 5LN</v>
       </c>
       <c r="B83" t="str">
-        <v>Crabtree Ln, London, UK</v>
+        <v>Waldemar SW6 5LN</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G83" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H83" t="b">
         <v>0</v>
@@ -61058,27 +61067,18 @@
         <v>0</v>
       </c>
       <c r="L83" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68f62a88c22a16f688e0406a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/2e912ae5a794cdf1916a0e67</v>
       </c>
       <c r="M83" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1504462203382166627?viralityEntryPoint=1&amp;unique_share_id=EF5986AF-058B-4129-B2A6-973E7103962D&amp;slcid=66d165c7fb1b4623b2d61fbc7ad32e65&amp;s=76&amp;adults=1&amp;slug=PfGrvi7A&amp;source_impression_id=p3_1760961027_P3ffFFVDnBkN5HJi#_gl=1*1v7wizx*_gcl_aw*R0NMLjE3NTkzOTU5MDAuQ2p3S0NBand4ZmpHQmhBVUVpd0FLV1B3RHI1RjRqTXN1ZkN5N1pCYnNQQ3pSUlo4ZExYd1RFYW5ZTU80dWxFMlY2M3NRSGRJQlRsVXF4b0MwR0FRQXZEX0J3RQ..*_gcl_dc*R0NMLjE3NTkzOTU5MDAuQ2p3S0NBand4ZmpHQmhBVUVpd0FLV1B3RHI1RjRqTXN1ZkN5N1pCYnNQQ3pSUlo4ZExYd1RFYW5ZTU80dWxFMlY2M3NRSGRJQlRsVXF4b0MwR0FRQXZEX0J3RQ..*_gcl_au*MTk4NzkwMjc3Mi4xNzU5MTQ1NjUy*FPAU*MTU4NjI5OTU3NC4xNzU5MTQ1MzE0</v>
-      </c>
-      <c r="N83" t="str">
-        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
-      </c>
-      <c r="O83" t="str">
-        <v>Accommodation@calbrahomes.com</v>
-      </c>
-      <c r="P83" t="str">
-        <v>02045784820</v>
+        <v>https://www.airbnb.co.uk/rooms/600644958346284457?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=a8566da1-220b-4e6a-8919-5b3ecc90ebde&amp;source_impression_id=p3_1707324329_RZQTZjwM%2FyFvZC6T</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SW6 6NU</v>
+        <v>SW6 5QE</v>
       </c>
       <c r="B84" t="str">
-        <v>Inglethorpe St, London SW6 6NU, UK</v>
+        <v>Barclay Close, Cassidy Rd, London SW6 5QQ, UK</v>
       </c>
       <c r="C84">
         <v>4</v>
@@ -61087,7 +61087,7 @@
         <v>4</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F84" t="str">
         <v>off-site-chargeable</v>
@@ -61096,7 +61096,7 @@
         <v>chargeable</v>
       </c>
       <c r="H84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -61108,27 +61108,27 @@
         <v>0</v>
       </c>
       <c r="L84" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6900ae272e7dc87a87999dec</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/69147549be7e6aa6430527cd</v>
       </c>
       <c r="M84" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1043703968021137591?source_impression_id=p3_1761651623_P39RBu6Tjt6GKck_</v>
+        <v>https://www.airbnb.co.uk/rooms/1072946755416021325?source_impression_id=p3_1764151324_P3QVkH2jWSmElVqP</v>
       </c>
       <c r="N84" t="str">
-        <v>London base</v>
+        <v>Kay (Venn Management)</v>
       </c>
       <c r="O84" t="str">
-        <v>guest@londonbase.co</v>
+        <v>info@venmanagement.com</v>
       </c>
       <c r="P84" t="str">
-        <v>+4420 3189 1677</v>
+        <v>+447428980220</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SW6 6PH</v>
+        <v>SW6 5QQ</v>
       </c>
       <c r="B85" t="str">
-        <v>Harbord St, London SW6 6PH, UK</v>
+        <v>Cassidy Rd, London SW6 5QQ, UK</v>
       </c>
       <c r="C85">
         <v>4</v>
@@ -61137,7 +61137,7 @@
         <v>4</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" t="str">
         <v>off-site-chargeable</v>
@@ -61146,10 +61146,10 @@
         <v>chargeable</v>
       </c>
       <c r="H85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="b">
         <v>0</v>
@@ -61158,10 +61158,10 @@
         <v>0</v>
       </c>
       <c r="L85" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67337d2ac8526d02b94951c6</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6900a9342e7dc87a8799951b</v>
       </c>
       <c r="M85" t="str">
-        <v>https://www.airbnb.co.uk/rooms/971073232874583193?source_impression_id=p3_1731426909_P30hgRaZaShwo9jU&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
+        <v>https://www.airbnb.co.uk/rooms/1072946755416021325?adults=1&amp;check_in=2025-10-28&amp;check_out=2025-11-10&amp;children=5&amp;search_mode=regular_search&amp;infants=0&amp;pets=0&amp;source_impression_id=p3_1761647061_P3HjNMoMSugQ0mBC&amp;previous_page_section_name=1000&amp;federated_search_id=9ea658a4-3c21-4533-9c4d-f99b5bd5629b</v>
       </c>
       <c r="N85" t="str">
         <v>Airbnb Temporary</v>
@@ -61175,19 +61175,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SW6 6QP</v>
+        <v>SW6 6AR</v>
       </c>
       <c r="B86" t="str">
-        <v>Vera Rd, London SW6 6QP, UK</v>
+        <v>Crabtree Ln, London, UK</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F86" t="str">
         <v>off-site-chargeable</v>
@@ -61208,36 +61208,36 @@
         <v>0</v>
       </c>
       <c r="L86" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/689a0a6a150fed15c4e0dc25</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68f62a88c22a16f688e0406a</v>
       </c>
       <c r="M86" t="str">
-        <v>https://www.airbnb.co.uk/rooms/47213959?source_impression_id=p3_1754905791_P3elZ9UPa1plP8X3</v>
+        <v>https://www.airbnb.co.uk/rooms/1504462203382166627?viralityEntryPoint=1&amp;unique_share_id=EF5986AF-058B-4129-B2A6-973E7103962D&amp;slcid=66d165c7fb1b4623b2d61fbc7ad32e65&amp;s=76&amp;adults=1&amp;slug=PfGrvi7A&amp;source_impression_id=p3_1760961027_P3ffFFVDnBkN5HJi#_gl=1*1v7wizx*_gcl_aw*R0NMLjE3NTkzOTU5MDAuQ2p3S0NBand4ZmpHQmhBVUVpd0FLV1B3RHI1RjRqTXN1ZkN5N1pCYnNQQ3pSUlo4ZExYd1RFYW5ZTU80dWxFMlY2M3NRSGRJQlRsVXF4b0MwR0FRQXZEX0J3RQ..*_gcl_dc*R0NMLjE3NTkzOTU5MDAuQ2p3S0NBand4ZmpHQmhBVUVpd0FLV1B3RHI1RjRqTXN1ZkN5N1pCYnNQQ3pSUlo4ZExYd1RFYW5ZTU80dWxFMlY2M3NRSGRJQlRsVXF4b0MwR0FRQXZEX0J3RQ..*_gcl_au*MTk4NzkwMjc3Mi4xNzU5MTQ1NjUy*FPAU*MTU4NjI5OTU3NC4xNzU5MTQ1MzE0</v>
       </c>
       <c r="N86" t="str">
-        <v>Airbnb Temporary</v>
+        <v xml:space="preserve">Bradley Bennet - Calbra Homes </v>
       </c>
       <c r="O86" t="str">
-        <v>temp@airbnb.com</v>
+        <v>Accommodation@calbrahomes.com</v>
       </c>
       <c r="P86" t="str">
-        <v>00000000000</v>
+        <v>02045784820</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SW6 6TB</v>
+        <v>SW6 6NU</v>
       </c>
       <c r="B87" t="str">
-        <v>Fulham Palace Rd, London SW6 6TB, UK</v>
+        <v>Inglethorpe St, London SW6 6NU, UK</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D87">
+        <v>4</v>
+      </c>
+      <c r="E87">
         <v>3</v>
-      </c>
-      <c r="E87">
-        <v>1</v>
       </c>
       <c r="F87" t="str">
         <v>off-site-chargeable</v>
@@ -61246,10 +61246,10 @@
         <v>chargeable</v>
       </c>
       <c r="H87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
@@ -61258,30 +61258,30 @@
         <v>0</v>
       </c>
       <c r="L87" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/685526b463fbd51c0f5730ca</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6900ae272e7dc87a87999dec</v>
       </c>
       <c r="M87" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?viralityEntryPoint=1&amp;unique_share_id=831155F4-3E8B-4F5B-99B5-B85FA012CDF0&amp;slcid=2c9a58d13d294393adf98b429bad1477&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=A4rtpP1Q&amp;source_impression_id=p3_1750410709_P34EKQvWdwCAv1zY</v>
+        <v>https://www.airbnb.co.uk/rooms/1043703968021137591?source_impression_id=p3_1761651623_P39RBu6Tjt6GKck_</v>
       </c>
       <c r="N87" t="str">
-        <v>Shams</v>
+        <v>London base</v>
       </c>
       <c r="O87" t="str">
-        <v>info@findyourdwelling.com</v>
+        <v>guest@londonbase.co</v>
       </c>
       <c r="P87" t="str">
-        <v>020 8087 3161</v>
+        <v>+4420 3189 1677</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SW6 6TB</v>
+        <v>SW6 6PH</v>
       </c>
       <c r="B88" t="str">
-        <v>Fulham Palace Rd, London SW6 6TB, UK</v>
+        <v>Harbord St, London SW6 6PH, UK</v>
       </c>
       <c r="C88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88">
         <v>4</v>
@@ -61296,7 +61296,7 @@
         <v>chargeable</v>
       </c>
       <c r="H88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="b">
         <v>0</v>
@@ -61308,36 +61308,36 @@
         <v>0</v>
       </c>
       <c r="L88" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68551fb2f3cc17e4dacd24b6</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67337d2ac8526d02b94951c6</v>
       </c>
       <c r="M88" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1366216563172751118?viralityEntryPoint=1&amp;unique_share_id=556BD062-BF7C-41E1-A851-6C32E37FCD0C&amp;slcid=dc9bb1a712364a48bc98100458db6ad7&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=D5k1pgt8&amp;source_impression_id=p3_1750408921_P3dvLS9C2FNxRatw</v>
+        <v>https://www.airbnb.co.uk/rooms/971073232874583193?source_impression_id=p3_1731426909_P30hgRaZaShwo9jU&amp;modal=PHOTO_TOUR_SCROLLABLE</v>
       </c>
       <c r="N88" t="str">
-        <v>Shams</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O88" t="str">
-        <v>info@findyourdwelling.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P88" t="str">
-        <v>020 8087 3161</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SW6 6TB</v>
+        <v>SW6 6QP</v>
       </c>
       <c r="B89" t="str">
-        <v>353 Fulham Palace Rd, London SW6 6TB, UK</v>
+        <v>Vera Rd, London SW6 6QP, UK</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F89" t="str">
         <v>off-site-chargeable</v>
@@ -61349,7 +61349,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
@@ -61358,19 +61358,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/685ad138a64d265cf905ab30</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/689a0a6a150fed15c4e0dc25</v>
       </c>
       <c r="M89" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj&amp;source_impression_id=p3_1750782139_P3DWqvFlh4ekiIBJ</v>
+        <v>https://www.airbnb.co.uk/rooms/47213959?source_impression_id=p3_1754905791_P3elZ9UPa1plP8X3</v>
       </c>
       <c r="N89" t="str">
-        <v>Shams</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O89" t="str">
-        <v>info@findyourdwelling.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P89" t="str">
-        <v>020 8087 3161</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="90">
@@ -61378,13 +61378,13 @@
         <v>SW6 6TB</v>
       </c>
       <c r="B90" t="str">
-        <v>353 Fulham Palace Rd, London SW6 6TB, UK</v>
+        <v>Fulham Palace Rd, London SW6 6TB, UK</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -61408,10 +61408,10 @@
         <v>0</v>
       </c>
       <c r="L90" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/685ad139d1fc77c4876c63f6</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/685526b463fbd51c0f5730ca</v>
       </c>
       <c r="M90" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj&amp;source_impression_id=p3_1750782139_P3DWqvFlh4ekiIBJ</v>
+        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?viralityEntryPoint=1&amp;unique_share_id=831155F4-3E8B-4F5B-99B5-B85FA012CDF0&amp;slcid=2c9a58d13d294393adf98b429bad1477&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=A4rtpP1Q&amp;source_impression_id=p3_1750410709_P34EKQvWdwCAv1zY</v>
       </c>
       <c r="N90" t="str">
         <v>Shams</v>
@@ -61425,28 +61425,28 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SW6 7BX</v>
+        <v>SW6 6TB</v>
       </c>
       <c r="B91" t="str">
-        <v>Parkville Rd, London SW6 7BX, UK</v>
+        <v>Fulham Palace Rd, London SW6 6TB, UK</v>
       </c>
       <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91">
         <v>4</v>
       </c>
-      <c r="D91">
-        <v>5</v>
-      </c>
       <c r="E91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F91" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G91" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="b">
         <v>0</v>
@@ -61458,33 +61458,33 @@
         <v>0</v>
       </c>
       <c r="L91" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68d54b78c2535f08cb25db69</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68551fb2f3cc17e4dacd24b6</v>
       </c>
       <c r="M91" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1499099822600070432?source_impression_id=p3_1758807966_P3zaf67BtFxgUjVk</v>
+        <v>https://www.airbnb.co.uk/rooms/1366216563172751118?viralityEntryPoint=1&amp;unique_share_id=556BD062-BF7C-41E1-A851-6C32E37FCD0C&amp;slcid=dc9bb1a712364a48bc98100458db6ad7&amp;s=76&amp;feature=share&amp;adults=1&amp;channel=native&amp;slug=D5k1pgt8&amp;source_impression_id=p3_1750408921_P3dvLS9C2FNxRatw</v>
       </c>
       <c r="N91" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Shams</v>
       </c>
       <c r="O91" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@findyourdwelling.com</v>
       </c>
       <c r="P91" t="str">
-        <v>00000000000</v>
+        <v>020 8087 3161</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SW8 1AE</v>
+        <v>SW6 6TB</v>
       </c>
       <c r="B92" t="str">
-        <v>Beaufoy House, 1 Regents Bridge Gardens, London SW8 1JP, UK</v>
+        <v>353 Fulham Palace Rd, London SW6 6TB, UK</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -61499,7 +61499,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
@@ -61508,33 +61508,33 @@
         <v>0</v>
       </c>
       <c r="L92" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ee04a01043b950380eb2fc</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/685ad138a64d265cf905ab30</v>
       </c>
       <c r="M92" t="str">
-        <v>https://www.airbnb.co.uk/rooms/32695038?source_impression_id=p3_1760428843_P3mdse_sv0EsPht8&amp;check_in=2025-10-28&amp;guests=2&amp;adults=2&amp;check_out=2026-01-16</v>
+        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj&amp;source_impression_id=p3_1750782139_P3DWqvFlh4ekiIBJ</v>
       </c>
       <c r="N92" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Shams</v>
       </c>
       <c r="O92" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@findyourdwelling.com</v>
       </c>
       <c r="P92" t="str">
-        <v>00000000000</v>
+        <v>020 8087 3161</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SW8 1NB</v>
+        <v>SW6 6TB</v>
       </c>
       <c r="B93" t="str">
-        <v>Stoddart House, Meadow Rd, London SW8 1ND, UK</v>
+        <v>353 Fulham Palace Rd, London SW6 6TB, UK</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93">
         <v>1</v>
@@ -61549,7 +61549,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
@@ -61558,45 +61558,45 @@
         <v>0</v>
       </c>
       <c r="L93" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ee210f1e6542cc132ac9cc</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/685ad139d1fc77c4876c63f6</v>
       </c>
       <c r="M93" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1507829464694432386?source_impression_id=p3_1760436284_P3WVnq1rOmh-v0re</v>
+        <v>https://www.airbnb.co.uk/rooms/1371230501539256051?_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj&amp;source_impression_id=p3_1750782139_P3DWqvFlh4ekiIBJ</v>
       </c>
       <c r="N93" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Shams</v>
       </c>
       <c r="O93" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@findyourdwelling.com</v>
       </c>
       <c r="P93" t="str">
-        <v>00000000000</v>
+        <v>020 8087 3161</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SW8 2ED</v>
+        <v>SW6 7BX</v>
       </c>
       <c r="B94" t="str">
-        <v>Lansdowne Way, London, UK</v>
+        <v>Parkville Rd, London SW6 7BX, UK</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F94" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G94" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="b">
         <v>0</v>
@@ -61608,10 +61608,10 @@
         <v>0</v>
       </c>
       <c r="L94" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68ee1f001043b950380f06bf</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68d54b78c2535f08cb25db69</v>
       </c>
       <c r="M94" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1512292868036967810?source_impression_id=p3_1760435767_P3bry31toK2bC0qU</v>
+        <v>https://www.airbnb.co.uk/rooms/1499099822600070432?source_impression_id=p3_1758807966_P3zaf67BtFxgUjVk</v>
       </c>
       <c r="N94" t="str">
         <v>Airbnb Temporary</v>
@@ -61625,16 +61625,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SW8 2XA</v>
+        <v>SW8 1AE</v>
       </c>
       <c r="B95" t="str">
-        <v>Wilcox Rd, London SW8 2XA, UK</v>
+        <v>Beaufoy House, 1 Regents Bridge Gardens, London SW8 1JP, UK</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -61658,27 +61658,27 @@
         <v>0</v>
       </c>
       <c r="L95" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67659252631e063f5b9834bb</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ee04a01043b950380eb2fc</v>
       </c>
       <c r="M95" t="str">
-        <v>https://nq.hostify.club/listing/87523</v>
+        <v>https://www.airbnb.co.uk/rooms/32695038?source_impression_id=p3_1760428843_P3mdse_sv0EsPht8&amp;check_in=2025-10-28&amp;guests=2&amp;adults=2&amp;check_out=2026-01-16</v>
       </c>
       <c r="N95" t="str">
-        <v>Shloime</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O95" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P95" t="str">
-        <v>07867290839</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SW8 2XA</v>
+        <v>SW8 1NB</v>
       </c>
       <c r="B96" t="str">
-        <v>Wilcox Rd, London SW8 2XA, UK</v>
+        <v>Stoddart House, Meadow Rd, London SW8 1ND, UK</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -61708,27 +61708,27 @@
         <v>0</v>
       </c>
       <c r="L96" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67658f67631e063f5b98344f</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ee210f1e6542cc132ac9cc</v>
       </c>
       <c r="M96" t="str">
-        <v>https://nq.hostify.club/listing/144285</v>
+        <v>https://www.airbnb.co.uk/rooms/1507829464694432386?source_impression_id=p3_1760436284_P3WVnq1rOmh-v0re</v>
       </c>
       <c r="N96" t="str">
-        <v>Shloime</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O96" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P96" t="str">
-        <v>07867290839</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SW8 2XA</v>
+        <v>SW8 2ED</v>
       </c>
       <c r="B97" t="str">
-        <v>Wilcox Rd, London SW8 2XA, UK</v>
+        <v>Lansdowne Way, London, UK</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -61737,7 +61737,7 @@
         <v>2</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" t="str">
         <v>off-site-chargeable</v>
@@ -61758,36 +61758,36 @@
         <v>0</v>
       </c>
       <c r="L97" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67658b4aaafaba5175a9614b</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68ee1f001043b950380f06bf</v>
       </c>
       <c r="M97" t="str">
-        <v>https://nq.hostify.club/listing/144286</v>
+        <v>https://www.airbnb.co.uk/rooms/1512292868036967810?source_impression_id=p3_1760435767_P3bry31toK2bC0qU</v>
       </c>
       <c r="N97" t="str">
-        <v>Shloime</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O97" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P97" t="str">
-        <v>07867290839</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SW8 4XF</v>
+        <v>SW8 2XA</v>
       </c>
       <c r="B98" t="str">
-        <v>Deeley Rd, Nine Elms, London SW8 4XF, UK</v>
+        <v>Wilcox Rd, London SW8 2XA, UK</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" t="str">
         <v>off-site-chargeable</v>
@@ -61808,27 +61808,27 @@
         <v>0</v>
       </c>
       <c r="L98" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/285def14972d9284bf019172</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67658b4aaafaba5175a9614b</v>
       </c>
       <c r="M98" t="str">
-        <v>https://abnb.me/LIMHw5CTtGb</v>
+        <v>https://nq.hostify.club/listing/144286</v>
       </c>
       <c r="N98" t="str">
-        <v>Ayang</v>
+        <v>Shloime</v>
       </c>
       <c r="O98" t="str">
-        <v>hello@bookthatstay.com</v>
+        <v>shloime@hometohost.co.uk</v>
       </c>
       <c r="P98" t="str">
-        <v>07837424985</v>
+        <v>07867290839</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SW8 4XX</v>
+        <v>SW8 2XA</v>
       </c>
       <c r="B99" t="str">
-        <v>Thessaly Rd, Nine Elms, London SW8 4XX, UK</v>
+        <v>Wilcox Rd, London SW8 2XA, UK</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -61858,27 +61858,27 @@
         <v>0</v>
       </c>
       <c r="L99" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/687fa7d41ea8b1a0f73095a8</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67658f67631e063f5b98344f</v>
       </c>
       <c r="M99" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1433251646793494676?source_impression_id=p3_1753196080_P3zRtJexIYtWIN4E</v>
+        <v>https://nq.hostify.club/listing/144285</v>
       </c>
       <c r="N99" t="str">
-        <v>Toyin Ogunwomoju</v>
+        <v>Shloime</v>
       </c>
       <c r="O99" t="str">
-        <v>email@emaaaail.com</v>
+        <v>shloime@hometohost.co.uk</v>
       </c>
       <c r="P99" t="str">
-        <v>07835788872</v>
+        <v>07867290839</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sw18 5na</v>
+        <v>SW8 2XA</v>
       </c>
       <c r="B100" t="str">
-        <v>Pirbright Rd, London SW18 5NA, UK</v>
+        <v>Wilcox Rd, London SW8 2XA, UK</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -61908,36 +61908,36 @@
         <v>0</v>
       </c>
       <c r="L100" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67ebc6df633e1298a40ad537</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67659252631e063f5b9834bb</v>
       </c>
       <c r="M100" t="str">
-        <v>https://www.airbnb.co.uk/rooms/34944409?source_impression_id=p3_1743504960_P3qhXgZQW46E1oZt</v>
+        <v>https://nq.hostify.club/listing/87523</v>
       </c>
       <c r="N100" t="str">
-        <v>Mo</v>
+        <v>Shloime</v>
       </c>
       <c r="O100" t="str">
-        <v>info@milamanagement.co.uk</v>
+        <v>shloime@hometohost.co.uk</v>
       </c>
       <c r="P100" t="str">
-        <v>+447888003322</v>
+        <v>07867290839</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>TW1 1AX</v>
+        <v>SW8 4XF</v>
       </c>
       <c r="B101" t="str">
-        <v>Brewery Ln, Twickenham TW1, UK</v>
+        <v>Deeley Rd, Nine Elms, London SW8 4XF, UK</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" t="str">
         <v>off-site-chargeable</v>
@@ -61958,45 +61958,45 @@
         <v>0</v>
       </c>
       <c r="L101" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e531264742d568c76f4356</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/285def14972d9284bf019172</v>
       </c>
       <c r="M101" t="str">
-        <v>https://vantageapartments.com/apartments/twickenham-wharf-house/</v>
+        <v>https://abnb.me/LIMHw5CTtGb</v>
       </c>
       <c r="N101" t="str">
-        <v xml:space="preserve">Chris </v>
+        <v>Ayang</v>
       </c>
       <c r="O101" t="str">
-        <v>res@vantageapartments.com</v>
+        <v>hello@bookthatstay.com</v>
       </c>
       <c r="P101" t="str">
-        <v>07887954582</v>
+        <v>07837424985</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>TW1 1ET</v>
+        <v>SW8 4XX</v>
       </c>
       <c r="B102" t="str">
-        <v>Burnside Cl, Twickenham TW1 1ET, UK</v>
+        <v>Thessaly Rd, Nine Elms, London SW8 4XX, UK</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D102">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E102">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F102" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G102" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" t="b">
         <v>0</v>
@@ -62008,24 +62008,33 @@
         <v>0</v>
       </c>
       <c r="L102" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/67503f12fa4913aaece1d932</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/687fa7d41ea8b1a0f73095a8</v>
       </c>
       <c r="M102" t="str">
-        <v>https://www.airbnb.co.uk/rooms/14245764?source_impression_id=p3_1733311223_P3GMFtjyu9hp8_on</v>
+        <v>https://www.airbnb.co.uk/rooms/1433251646793494676?source_impression_id=p3_1753196080_P3zRtJexIYtWIN4E</v>
+      </c>
+      <c r="N102" t="str">
+        <v>Toyin Ogunwomoju</v>
+      </c>
+      <c r="O102" t="str">
+        <v>email@emaaaail.com</v>
+      </c>
+      <c r="P102" t="str">
+        <v>07835788872</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>TW1 2HN</v>
+        <v>Sw18 5na</v>
       </c>
       <c r="B103" t="str">
-        <v>27 Cambridge Rd, Twickenham TW1 2HN, UK</v>
+        <v>Pirbright Rd, London SW18 5NA, UK</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -62037,39 +62046,39 @@
         <v>chargeable</v>
       </c>
       <c r="H103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="b">
         <v>0</v>
       </c>
       <c r="J103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/690b296a6e4f26241d07138d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67ebc6df633e1298a40ad537</v>
       </c>
       <c r="M103" t="str">
-        <v>https://www.airbnb.co.uk/rooms/10328522?source_impression_id=p3_1762338948_P3m61HyGXUPit5Ld&amp;check_in=2026-01-23&amp;guests=3&amp;adults=3&amp;check_out=2026-03-23&amp;pets=1</v>
+        <v>https://www.airbnb.co.uk/rooms/34944409?source_impression_id=p3_1743504960_P3qhXgZQW46E1oZt</v>
       </c>
       <c r="N103" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Mo</v>
       </c>
       <c r="O103" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@milamanagement.co.uk</v>
       </c>
       <c r="P103" t="str">
-        <v>00000000000</v>
+        <v>+447888003322</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>TW1 3SX</v>
+        <v>TW1 1AX</v>
       </c>
       <c r="B104" t="str">
-        <v>London Rd, Twickenham TW1 3SX, UK</v>
+        <v>Brewery Ln, Twickenham TW1, UK</v>
       </c>
       <c r="C104">
         <v>2</v>
@@ -62090,7 +62099,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" t="b">
         <v>0</v>
@@ -62099,36 +62108,36 @@
         <v>0</v>
       </c>
       <c r="L104" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e53fe990b22e68a29caa77</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e531264742d568c76f4356</v>
       </c>
       <c r="M104" t="str">
-        <v>https://vantageapartments.com/apartments/twickenham-2-beds/</v>
+        <v>https://vantageapartments.com/apartments/twickenham-wharf-house/</v>
       </c>
       <c r="N104" t="str">
-        <v>Chris</v>
+        <v xml:space="preserve">Chris </v>
       </c>
       <c r="O104" t="str">
-        <v>info@finestay.co.uk</v>
+        <v>res@vantageapartments.com</v>
       </c>
       <c r="P104" t="str">
-        <v>+447514511518</v>
+        <v>07887954582</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>TW10 5DF</v>
+        <v>TW1 1ET</v>
       </c>
       <c r="B105" t="str">
-        <v>Sheen Ct Rd, Richmond TW10 5DF, UK</v>
+        <v>Burnside Cl, Twickenham TW1 1ET, UK</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E105">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F105" t="str">
         <v>on-site-free</v>
@@ -62137,7 +62146,7 @@
         <v>no</v>
       </c>
       <c r="H105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="b">
         <v>0</v>
@@ -62149,86 +62158,77 @@
         <v>0</v>
       </c>
       <c r="L105" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/683973c04c57ed8b6ad53947</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/67503f12fa4913aaece1d932</v>
       </c>
       <c r="M105" t="str">
-        <v>https://www.airbnb.co.uk/rooms/673889680829042157?source_impression_id=p3_1748595425_P3D00UuVeB-5YFVu</v>
-      </c>
-      <c r="N105" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-      <c r="O105" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="P105" t="str">
-        <v>00000000000</v>
+        <v>https://www.airbnb.co.uk/rooms/14245764?source_impression_id=p3_1733311223_P3GMFtjyu9hp8_on</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TW10 5LF</v>
+        <v>TW1 2HN</v>
       </c>
       <c r="B106" t="str">
-        <v>Dryden Court, Parkleys, Richmond TW10 5LJ, UK</v>
+        <v>27 Cambridge Rd, Twickenham TW1 2HN, UK</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106">
         <v>1</v>
       </c>
       <c r="F106" t="str">
-        <v>off-site-free</v>
+        <v>on-site-free</v>
       </c>
       <c r="G106" t="str">
         <v>chargeable</v>
       </c>
       <c r="H106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="b">
         <v>0</v>
       </c>
       <c r="J106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/673f14f4a41ba7207348675d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/690b296a6e4f26241d07138d</v>
       </c>
       <c r="M106" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1287693453607613837?adults=2&amp;children=1&amp;location=Twickenham%20TW2%205FN%2C%20UK&amp;search_mode=regular_search&amp;check_in=2024-11-25&amp;check_out=2024-12-23&amp;source_impression_id=p3_1732186595_P3eSRUQvTWhYcsu-&amp;previous_page_section_name=1001&amp;federated_search_id=016b6fdd-04c0-4251-a230-0722be645c90</v>
+        <v>https://www.airbnb.co.uk/rooms/10328522?source_impression_id=p3_1762338948_P3m61HyGXUPit5Ld&amp;check_in=2026-01-23&amp;guests=3&amp;adults=3&amp;check_out=2026-03-23&amp;pets=1</v>
       </c>
       <c r="N106" t="str">
-        <v>Fiona Teddington</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O106" t="str">
-        <v>fiona@headingtons.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P106" t="str">
-        <v>07769 696464</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>TW10 6NQ</v>
+        <v>TW1 3SX</v>
       </c>
       <c r="B107" t="str">
-        <v>Friars Stile Rd, Richmond TW10 6NQ, UK</v>
+        <v>London Rd, Twickenham TW1 3SX, UK</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F107" t="str">
         <v>off-site-chargeable</v>
@@ -62240,7 +62240,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" t="b">
         <v>0</v>
@@ -62249,36 +62249,36 @@
         <v>0</v>
       </c>
       <c r="L107" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/690b23376e4f26241d0700f0</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e53fe990b22e68a29caa77</v>
       </c>
       <c r="M107" t="str">
-        <v>https://www.airbnb.co.uk/rooms/6131981?source_impression_id=p3_1762337183_P3B65amILc_FLAcx&amp;check_in=2026-01-23&amp;guests=3&amp;adults=3&amp;check_out=2026-03-23&amp;pets=1</v>
+        <v>https://vantageapartments.com/apartments/twickenham-2-beds/</v>
       </c>
       <c r="N107" t="str">
-        <v>James Higges Malynn</v>
+        <v>Chris</v>
       </c>
       <c r="O107" t="str">
-        <v>jameshiggesmalynn@gmail.com</v>
+        <v>info@finestay.co.uk</v>
       </c>
       <c r="P107" t="str">
-        <v>07775864431</v>
+        <v>+447514511518</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>TW2 6AD</v>
+        <v>TW10 5DF</v>
       </c>
       <c r="B108" t="str">
-        <v>151 Ellerman Ave, Twickenham TW2 6AD, UK</v>
+        <v>Sheen Ct Rd, Richmond TW10 5DF, UK</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F108" t="str">
         <v>on-site-free</v>
@@ -62299,16 +62299,16 @@
         <v>0</v>
       </c>
       <c r="L108" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6890bc4d5076d27437bbe987</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/683973c04c57ed8b6ad53947</v>
       </c>
       <c r="M108" t="str">
-        <v>https://www.booking.com/hotel/gb/large-one-bedroom-flat-in-london-twickenham-with-free-parking.en-gb.html?aid=304142&amp;label=gen173nr-10CAsoUEI9bGFyZ2Utb25lLWJlZHJvb20tZmxhdC1pbi1sb25kb24tdHdpY2tlbmhhbS13aXRoLWZyZWUtcGFya2luZ0gJWARoaYgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAagCAbgCrfTCxAbAAgHSAiQxMDk3ZWQzOS01YjQ2LTQxZTQtYWMzNS04YjYyYWFiYjM5MTjYAgHgAgE&amp;sid=7c380fb8cafd8760226e8cee0417ae8a&amp;all_sr_blocks=1197316701_403932345_1_0_0_706331&amp;checkin=2025-08-17&amp;checkout=2025-08-24&amp;dist=0&amp;group_adults=1&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1197316701_403932345_1_0_0_706331&amp;hpos=1&amp;matching_block_id=1197316701_403932345_1_0_0_706331&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=1&amp;req_adults=1&amp;req_children=0&amp;room1=A&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=1197316701_403932345_1_0_0_706331_58441&amp;srepoch=1754315309&amp;srpvid=d42e97c4701d325dac390210bafaa6cd&amp;type=total&amp;ucfs=1&amp;</v>
+        <v>https://www.airbnb.co.uk/rooms/673889680829042157?source_impression_id=p3_1748595425_P3D00UuVeB-5YFVu</v>
       </c>
       <c r="N108" t="str">
-        <v>Booking.Com Temporary</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O108" t="str">
-        <v>fake@booking.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P108" t="str">
         <v>00000000000</v>
@@ -62316,25 +62316,25 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>TW2 6QW</v>
+        <v>TW10 5LF</v>
       </c>
       <c r="B109" t="str">
-        <v>1a May Rd, London, Twickenham TW2 6QW, UK</v>
+        <v>Dryden Court, Parkleys, Richmond TW10 5LJ, UK</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" t="str">
-        <v>off-site-chargeable</v>
+        <v>off-site-free</v>
       </c>
       <c r="G109" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
@@ -62349,86 +62349,86 @@
         <v>0</v>
       </c>
       <c r="L109" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e669cf5a715acf5518c7b5</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/673f14f4a41ba7207348675d</v>
       </c>
       <c r="M109" t="str">
-        <v>https://www.booking.com/hotel/gb/modern-stylish-townhouse.en-gb.html?aid=304142&amp;label=gen173rf-10CAQoggJCKnNlYXJjaF9lbG10cmVlK3JkLCt0ZWRkaW5ndG9uK3R3MTErOHN0LCt1a0gJWANoUIgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAaICE215aG9tZWlzeW91cnMuY28udWuoAgG4Ar32mMcGwAIB0gIkNTkxYzEwYzctNTViNy00ZWM1LWIyMzMtZmI5ZTFkMTI2YzZh2AIB4AIB&amp;sid=325a167012db26cb7644e17756f19220&amp;age=15&amp;age=15&amp;age=15&amp;all_sr_blocks=903932101_366522376_5_0_0&amp;checkin=2025-10-09&amp;checkout=2025-10-16&amp;dist=0&amp;group_adults=1&amp;group_children=3&amp;hapos=1&amp;highlighted_blocks=903932101_366522376_5_0_0&amp;hpos=1&amp;matching_block_id=903932101_366522376_5_0_0&amp;nflt=distance%3D3220&amp;no_rooms=1&amp;req_adults=1&amp;req_age=15&amp;req_age=15&amp;req_age=15&amp;req_children=3&amp;room1=A%2C15%2C15%2C15&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=903932101_366522376_5_0_0__214500&amp;srepoch=1759919013&amp;srpvid=b705490de835031e&amp;type=total&amp;ucfs=1&amp;#availability</v>
+        <v>https://www.airbnb.co.uk/rooms/1287693453607613837?adults=2&amp;children=1&amp;location=Twickenham%20TW2%205FN%2C%20UK&amp;search_mode=regular_search&amp;check_in=2024-11-25&amp;check_out=2024-12-23&amp;source_impression_id=p3_1732186595_P3eSRUQvTWhYcsu-&amp;previous_page_section_name=1001&amp;federated_search_id=016b6fdd-04c0-4251-a230-0722be645c90</v>
       </c>
       <c r="N109" t="str">
-        <v>Booking.Com Temporary</v>
+        <v>Fiona Teddington</v>
       </c>
       <c r="O109" t="str">
-        <v>fake@booking.com</v>
+        <v>fiona@headingtons.com</v>
       </c>
       <c r="P109" t="str">
-        <v>00000000000</v>
+        <v>07769 696464</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>TW2 7AJ</v>
+        <v>TW10 6AQ</v>
       </c>
       <c r="B110" t="str">
-        <v>Nelson Rd TW2 7AJ</v>
+        <v>The Vineyard, Richmond TW10 6AQ, UK</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E110">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F110" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G110" t="str">
         <v>chargeable</v>
       </c>
       <c r="H110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="b">
         <v>0</v>
       </c>
       <c r="J110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110" t="b">
         <v>0</v>
       </c>
       <c r="L110" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/59d73edef15abbc0bbd7b735</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6926cec592efe89da8626a6f</v>
       </c>
       <c r="M110" t="str">
-        <v>https://air.tl/LNCnb516</v>
+        <v>https://www.airbnb.co.uk/rooms/1004368986111863657?source_impression_id=p3_1764150780_P3etHTR_NBVnWszU</v>
       </c>
       <c r="N110" t="str">
-        <v>Daniella</v>
+        <v>Adrian</v>
       </c>
       <c r="O110" t="str">
-        <v>fake@regalstay.co.uk</v>
+        <v>lettings@smarterrent.co</v>
       </c>
       <c r="P110" t="str">
-        <v>07588733241</v>
+        <v>07725440611</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>TW9 1UP</v>
+        <v>TW10 6NQ</v>
       </c>
       <c r="B111" t="str">
-        <v>Sheen Park, Richmond TW9 1UP, UK</v>
+        <v>Friars Stile Rd, Richmond TW10 6NQ, UK</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F111" t="str">
         <v>off-site-chargeable</v>
@@ -62449,27 +62449,27 @@
         <v>0</v>
       </c>
       <c r="L111" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68499aafab93726599bbdc3a</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/690b23376e4f26241d0700f0</v>
       </c>
       <c r="M111" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1352162318526789141?adults=2&amp;check_in=2025-06-15&amp;check_out=2025-06-26&amp;location=TW9%204QQ&amp;search_mode=regular_search&amp;source_impression_id=p3_1748527649_P3gObTFTw4qoUYJu&amp;previous_page_section_name=1001&amp;federated_search_id=f6fcb773-7310-4092-a5b2-0b0400d495f7</v>
+        <v>https://www.airbnb.co.uk/rooms/6131981?source_impression_id=p3_1762337183_P3B65amILc_FLAcx&amp;check_in=2026-01-23&amp;guests=3&amp;adults=3&amp;check_out=2026-03-23&amp;pets=1</v>
       </c>
       <c r="N111" t="str">
-        <v>Airbnb Temporary</v>
+        <v>James Higges Malynn</v>
       </c>
       <c r="O111" t="str">
-        <v>temp@airbnb.com</v>
+        <v>jameshiggesmalynn@gmail.com</v>
       </c>
       <c r="P111" t="str">
-        <v>00000000000</v>
+        <v>07775864431</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>TW9 1YA</v>
+        <v>TW2 6AD</v>
       </c>
       <c r="B112" t="str">
-        <v>Manor Rd., Richmond TW9 1YA, UK</v>
+        <v>151 Ellerman Ave, Twickenham TW2 6AD, UK</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -62481,13 +62481,13 @@
         <v>1</v>
       </c>
       <c r="F112" t="str">
-        <v>off-site-free</v>
+        <v>on-site-free</v>
       </c>
       <c r="G112" t="str">
         <v>no</v>
       </c>
       <c r="H112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" t="b">
         <v>0</v>
@@ -62499,16 +62499,16 @@
         <v>0</v>
       </c>
       <c r="L112" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68a48edcb70315aefd180cc5</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6890bc4d5076d27437bbe987</v>
       </c>
       <c r="M112" t="str">
-        <v>https://www.airbnb.co.uk/rooms/48657532?adults=1&amp;check_in=2025-09-07&amp;check_out=2025-10-05&amp;search_mode=regular_search&amp;source_impression_id=p3_1755614553_P3ukIx0sYBmgXqRE&amp;previous_page_section_name=1000&amp;federated_search_id=f24e86bf-2b74-4122-b727-6745f41a15f1</v>
+        <v>https://www.booking.com/hotel/gb/large-one-bedroom-flat-in-london-twickenham-with-free-parking.en-gb.html?aid=304142&amp;label=gen173nr-10CAsoUEI9bGFyZ2Utb25lLWJlZHJvb20tZmxhdC1pbi1sb25kb24tdHdpY2tlbmhhbS13aXRoLWZyZWUtcGFya2luZ0gJWARoaYgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAagCAbgCrfTCxAbAAgHSAiQxMDk3ZWQzOS01YjQ2LTQxZTQtYWMzNS04YjYyYWFiYjM5MTjYAgHgAgE&amp;sid=7c380fb8cafd8760226e8cee0417ae8a&amp;all_sr_blocks=1197316701_403932345_1_0_0_706331&amp;checkin=2025-08-17&amp;checkout=2025-08-24&amp;dist=0&amp;group_adults=1&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1197316701_403932345_1_0_0_706331&amp;hpos=1&amp;matching_block_id=1197316701_403932345_1_0_0_706331&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=1&amp;req_adults=1&amp;req_children=0&amp;room1=A&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=1197316701_403932345_1_0_0_706331_58441&amp;srepoch=1754315309&amp;srpvid=d42e97c4701d325dac390210bafaa6cd&amp;type=total&amp;ucfs=1&amp;</v>
       </c>
       <c r="N112" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Booking.Com Temporary</v>
       </c>
       <c r="O112" t="str">
-        <v>temp@airbnb.com</v>
+        <v>fake@booking.com</v>
       </c>
       <c r="P112" t="str">
         <v>00000000000</v>
@@ -62516,25 +62516,25 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>TW9 1YJ</v>
+        <v>TW2 6QW</v>
       </c>
       <c r="B113" t="str">
-        <v>Sheen Rd, Richmond TW9 1YJ, UK</v>
+        <v>1a May Rd, London, Twickenham TW2 6QW, UK</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G113" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
@@ -62549,36 +62549,36 @@
         <v>0</v>
       </c>
       <c r="L113" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6893273aee11b286d6069d02</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e669cf5a715acf5518c7b5</v>
       </c>
       <c r="M113" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1477591205589843186?adults=1&amp;infants=1&amp;location=Melliss%20Avenue%2C%20Richmond%20TW9%204BF&amp;search_mode=regular_search&amp;source_impression_id=p3_1754411594_P3BbX2nMh-WG77LT&amp;previous_page_section_name=1001&amp;federated_search_id=69450dfd-662d-4ca9-8f69-ac92a539e93f&amp;guests=1</v>
+        <v>https://www.booking.com/hotel/gb/modern-stylish-townhouse.en-gb.html?aid=304142&amp;label=gen173rf-10CAQoggJCKnNlYXJjaF9lbG10cmVlK3JkLCt0ZWRkaW5ndG9uK3R3MTErOHN0LCt1a0gJWANoUIgBAZgBM7gBF8gBDNgBA-gBAfgBAYgCAaICE215aG9tZWlzeW91cnMuY28udWuoAgG4Ar32mMcGwAIB0gIkNTkxYzEwYzctNTViNy00ZWM1LWIyMzMtZmI5ZTFkMTI2YzZh2AIB4AIB&amp;sid=325a167012db26cb7644e17756f19220&amp;age=15&amp;age=15&amp;age=15&amp;all_sr_blocks=903932101_366522376_5_0_0&amp;checkin=2025-10-09&amp;checkout=2025-10-16&amp;dist=0&amp;group_adults=1&amp;group_children=3&amp;hapos=1&amp;highlighted_blocks=903932101_366522376_5_0_0&amp;hpos=1&amp;matching_block_id=903932101_366522376_5_0_0&amp;nflt=distance%3D3220&amp;no_rooms=1&amp;req_adults=1&amp;req_age=15&amp;req_age=15&amp;req_age=15&amp;req_children=3&amp;room1=A%2C15%2C15%2C15&amp;sb_price_type=total&amp;sr_order=distance_from_search&amp;sr_pri_blocks=903932101_366522376_5_0_0__214500&amp;srepoch=1759919013&amp;srpvid=b705490de835031e&amp;type=total&amp;ucfs=1&amp;#availability</v>
       </c>
       <c r="N113" t="str">
-        <v>Stress Free Homes</v>
+        <v>Booking.Com Temporary</v>
       </c>
       <c r="O113" t="str">
-        <v>enquiries@yourstressfreeproperties.com</v>
+        <v>fake@booking.com</v>
       </c>
       <c r="P113" t="str">
-        <v>020 3488 9972</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>TW9 2HN</v>
+        <v>TW2 7AJ</v>
       </c>
       <c r="B114" t="str">
-        <v>Stanmore Gardens, Richmond TW9 2HN, UK</v>
+        <v>Nelson Rd TW2 7AJ</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E114">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F114" t="str">
         <v>off-site-chargeable</v>
@@ -62587,48 +62587,48 @@
         <v>chargeable</v>
       </c>
       <c r="H114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" t="b">
         <v>0</v>
       </c>
       <c r="J114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/690c66323c528d855ec7b238</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/59d73edef15abbc0bbd7b735</v>
       </c>
       <c r="M114" t="str">
-        <v>https://www.airbnb.co.uk/rooms/643556548223968524?source_impression_id=p3_1762419895_P3NGJkno2kkUO9E_</v>
+        <v>https://air.tl/LNCnb516</v>
       </c>
       <c r="N114" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Daniella</v>
       </c>
       <c r="O114" t="str">
-        <v>temp@airbnb.com</v>
+        <v>fake@regalstay.co.uk</v>
       </c>
       <c r="P114" t="str">
-        <v>00000000000</v>
+        <v>07588733241</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>W12 7BT</v>
+        <v>TW9 1UP</v>
       </c>
       <c r="B115" t="str">
-        <v>Bloemfontein Rd, London W12 7BT, UK</v>
+        <v>Sheen Park, Richmond TW9 1UP, UK</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" t="str">
         <v>off-site-chargeable</v>
@@ -62649,10 +62649,10 @@
         <v>0</v>
       </c>
       <c r="L115" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68275e86976de26b249e7b25</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68499aafab93726599bbdc3a</v>
       </c>
       <c r="M115" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1369060821699399859?source_impression_id=p3_1747410227_P3EjSWJPblet4bzY</v>
+        <v>https://www.airbnb.co.uk/rooms/1352162318526789141?adults=2&amp;check_in=2025-06-15&amp;check_out=2025-06-26&amp;location=TW9%204QQ&amp;search_mode=regular_search&amp;source_impression_id=p3_1748527649_P3gObTFTw4qoUYJu&amp;previous_page_section_name=1001&amp;federated_search_id=f6fcb773-7310-4092-a5b2-0b0400d495f7</v>
       </c>
       <c r="N115" t="str">
         <v>Airbnb Temporary</v>
@@ -62666,10 +62666,10 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>W12 7DP</v>
+        <v>TW9 1YA</v>
       </c>
       <c r="B116" t="str">
-        <v>Wood Ln, London W12 7DP, UK</v>
+        <v>Manor Rd., Richmond TW9 1YA, UK</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -62681,13 +62681,13 @@
         <v>1</v>
       </c>
       <c r="F116" t="str">
-        <v>off-site-chargeable</v>
+        <v>off-site-free</v>
       </c>
       <c r="G116" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="b">
         <v>0</v>
@@ -62699,10 +62699,10 @@
         <v>0</v>
       </c>
       <c r="L116" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6808b4568f291c91ba324822</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68a48edcb70315aefd180cc5</v>
       </c>
       <c r="M116" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1262304556462702075?source_impression_id=p3_1745400881_P3248y-DWTiJCqcM</v>
+        <v>https://www.airbnb.co.uk/rooms/48657532?adults=1&amp;check_in=2025-09-07&amp;check_out=2025-10-05&amp;search_mode=regular_search&amp;source_impression_id=p3_1755614553_P3ukIx0sYBmgXqRE&amp;previous_page_section_name=1000&amp;federated_search_id=f24e86bf-2b74-4122-b727-6745f41a15f1</v>
       </c>
       <c r="N116" t="str">
         <v>Airbnb Temporary</v>
@@ -62716,13 +62716,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>W12 7EN</v>
+        <v>TW9 1YJ</v>
       </c>
       <c r="B117" t="str">
-        <v>Bakery House, 2A Loftus Rd, Greater, London W12 7EN, UK</v>
+        <v>Sheen Rd, Richmond TW9 1YJ, UK</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -62734,7 +62734,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G117" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
@@ -62749,83 +62749,83 @@
         <v>0</v>
       </c>
       <c r="L117" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68aeeca46ecc2a70681e8fb6</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6893273aee11b286d6069d02</v>
       </c>
       <c r="M117" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1427356510827612998?adults=3&amp;check_in=2025-08-10&amp;check_out=2025-08-15&amp;search_mode=regular_search&amp;source_impression_id=p3_1749545813_P3GO8TG-fJu7iQB0&amp;previous_page_section_name=1000&amp;federated_search_id=3376fb03-300d-4453-b532-0a265f06f74d&amp;_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj</v>
+        <v>https://www.airbnb.co.uk/rooms/1477591205589843186?adults=1&amp;infants=1&amp;location=Melliss%20Avenue%2C%20Richmond%20TW9%204BF&amp;search_mode=regular_search&amp;source_impression_id=p3_1754411594_P3BbX2nMh-WG77LT&amp;previous_page_section_name=1001&amp;federated_search_id=69450dfd-662d-4ca9-8f69-ac92a539e93f&amp;guests=1</v>
       </c>
       <c r="N117" t="str">
-        <v>Mark Hudson | Nestor Stay</v>
+        <v>Stress Free Homes</v>
       </c>
       <c r="O117" t="str">
-        <v>corporate@nestorstay.com</v>
+        <v>enquiries@yourstressfreeproperties.com</v>
       </c>
       <c r="P117" t="str">
-        <v>0203 695 1065</v>
+        <v>020 3488 9972</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>W12 7LZ</v>
+        <v>TW9 2HN</v>
       </c>
       <c r="B118" t="str">
-        <v>MacKenzie Cl, London W12 7LZ, UK</v>
+        <v>Stanmore Gardens, Richmond TW9 2HN, UK</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E118">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F118" t="str">
-        <v>off-site-chargeable</v>
+        <v>on-site-free</v>
       </c>
       <c r="G118" t="str">
         <v>chargeable</v>
       </c>
       <c r="H118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" t="b">
         <v>0</v>
       </c>
       <c r="J118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68271847e8098e7bbe61ae18</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/690c66323c528d855ec7b238</v>
       </c>
       <c r="M118" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1299926267625673607?source_impression_id=p3_1747390962_P3A7UrRiMm-pAV2r</v>
+        <v>https://www.airbnb.co.uk/rooms/643556548223968524?source_impression_id=p3_1762419895_P3NGJkno2kkUO9E_</v>
       </c>
       <c r="N118" t="str">
-        <v>Gerda &amp; Chris</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O118" t="str">
-        <v>hello@nournestapartments.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P118" t="str">
-        <v xml:space="preserve"> +44 208 064 0268</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>W12 7QZ</v>
+        <v>W12 7BT</v>
       </c>
       <c r="B119" t="str">
-        <v>36 Dunraven Road, Shepherd's Bush, London, W12 7QZ</v>
+        <v>Bloemfontein Rd, London W12 7BT, UK</v>
       </c>
       <c r="C119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119">
         <v>2</v>
@@ -62849,36 +62849,36 @@
         <v>0</v>
       </c>
       <c r="L119" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/66c831222034c569bc234fab</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68275e86976de26b249e7b25</v>
       </c>
       <c r="M119" t="str">
-        <v>https://www.airbnb.com/rooms/1154551953402165238?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=624645d7-d6f3-4145-999f-0a74538bf77f&amp;source_impression_id=p3_1715708177_pd0Y0%2FRJ0wWn1hXa</v>
+        <v>https://www.airbnb.co.uk/rooms/1369060821699399859?source_impression_id=p3_1747410227_P3EjSWJPblet4bzY</v>
       </c>
       <c r="N119" t="str">
-        <v>Dolly</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O119" t="str">
-        <v>info@citygateproperty.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P119" t="str">
-        <v>07958 571 307</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>W12 7SF</v>
+        <v>W12 7DP</v>
       </c>
       <c r="B120" t="str">
-        <v>Fountain Park Wy, London W12, UK</v>
+        <v>Wood Ln, London W12 7DP, UK</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" t="str">
         <v>off-site-chargeable</v>
@@ -62899,10 +62899,10 @@
         <v>0</v>
       </c>
       <c r="L120" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68bed9c329edaa5d143ebb98</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6808b4568f291c91ba324822</v>
       </c>
       <c r="M120" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1478234898769467858?source_impression_id=p3_1757337796_P3k3cbuyZDmInulR</v>
+        <v>https://www.airbnb.co.uk/rooms/1262304556462702075?source_impression_id=p3_1745400881_P3248y-DWTiJCqcM</v>
       </c>
       <c r="N120" t="str">
         <v>Airbnb Temporary</v>
@@ -62916,16 +62916,16 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>W12 8LQ</v>
+        <v>W12 7EN</v>
       </c>
       <c r="B121" t="str">
-        <v>2, 11 Richmond Way, London W12 8LQ, UK</v>
+        <v>Bakery House, 2A Loftus Rd, Greater, London W12 7EN, UK</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -62949,45 +62949,45 @@
         <v>0</v>
       </c>
       <c r="L121" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/684192d86e40fb463e0c7ea1</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68aeeca46ecc2a70681e8fb6</v>
       </c>
       <c r="M121" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1399201898792819142?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=aa839f79-dbd8-4fd0-868c-739405e0b33e&amp;source_impression_id=p3_1749127712_P3eR1pth3FE1L7T3</v>
+        <v>https://www.airbnb.co.uk/rooms/1427356510827612998?adults=3&amp;check_in=2025-08-10&amp;check_out=2025-08-15&amp;search_mode=regular_search&amp;source_impression_id=p3_1749545813_P3GO8TG-fJu7iQB0&amp;previous_page_section_name=1000&amp;federated_search_id=3376fb03-300d-4453-b532-0a265f06f74d&amp;_set_bev_on_new_domain=1733322640_EANjkzNTQxZTJmNj</v>
       </c>
       <c r="N121" t="str">
-        <v>Fernando</v>
+        <v>Mark Hudson | Nestor Stay</v>
       </c>
       <c r="O121" t="str">
-        <v>info@urbanview-rentals.co.uk</v>
+        <v>corporate@nestorstay.com</v>
       </c>
       <c r="P121" t="str">
-        <v>07946446163</v>
+        <v>0203 695 1065</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>W14 8AS</v>
+        <v>W12 7LZ</v>
       </c>
       <c r="B122" t="str">
-        <v>147A Holland Rd, London W14 8AS, UK</v>
+        <v>MacKenzie Cl, London W12 7LZ, UK</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E122">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F122" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G122" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" t="b">
         <v>0</v>
@@ -62999,27 +62999,36 @@
         <v>0</v>
       </c>
       <c r="L122" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6728b8cbd1ab2037750b678d</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68271847e8098e7bbe61ae18</v>
       </c>
       <c r="M122" t="str">
-        <v>https://www.booking.com/hotel/gb/luxury-designer-flat-holland-park.en-gb.html?aid=2276424&amp;label=msn-HEC27qPyOZmLPBxa2YE3Nw-80676810309425%3Atikwd-80676960770001%3Aloc-41471%3Aneo%3Amte%3Alp41471%3Adec%3Aqsapart%20hotels%20w14%20london&amp;sid=c56aa9f495ded14af2d4d054a903fa6d&amp;all_sr_blocks=143034801_130622008_6_0_0;checkin=2024-11-04;checkout=2024-11-25;dist=0;group_adults=2;group_children=0;hapos=1;highlighted_blocks=143034801_130622008_6_0_0;hpos=1;matching_block_id=143034801_130622008_6_0_0;nflt=price%3DGBP-min-max-1%3Bht_id%3D201%3Baccessible_room_facilities%3D131;no_rooms=2;req_adults=2;req_children=0;room1=A;room2=A;sb_price_type=total;sr_order=distance_from_search;sr_pri_blocks=143034801_130622008_6_0_0__598100;srepoch=1730721405;srpvid=13ca53d733e1142c;type=total;ucfs=1&amp;</v>
+        <v>https://www.airbnb.co.uk/rooms/1299926267625673607?source_impression_id=p3_1747390962_P3A7UrRiMm-pAV2r</v>
+      </c>
+      <c r="N122" t="str">
+        <v>Gerda &amp; Chris</v>
+      </c>
+      <c r="O122" t="str">
+        <v>hello@nournestapartments.com</v>
+      </c>
+      <c r="P122" t="str">
+        <v xml:space="preserve"> +44 208 064 0268</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>W14 8BA</v>
+        <v>W12 7QZ</v>
       </c>
       <c r="B123" t="str">
-        <v>Holland Rd, London W14 8BA, UK</v>
+        <v>36 Dunraven Road, Shepherd's Bush, London, W12 7QZ</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123">
         <v>3</v>
       </c>
       <c r="E123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" t="str">
         <v>off-site-chargeable</v>
@@ -63040,27 +63049,27 @@
         <v>0</v>
       </c>
       <c r="L123" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68e538654742d568c76f5319</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/66c831222034c569bc234fab</v>
       </c>
       <c r="M123" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1445520707647119008?viralityEntryPoint=1&amp;unique_share_id=DDB5C481-F3E7-4572-85B3-009A630913F4&amp;slcid=d978484b14934a44a2aa7208d3b8352b&amp;s=76&amp;adults=1&amp;slug=SGWujO2T&amp;source_impression_id=p3_1759851881_P3qGxUy-MB3E94D0</v>
+        <v>https://www.airbnb.com/rooms/1154551953402165238?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=624645d7-d6f3-4145-999f-0a74538bf77f&amp;source_impression_id=p3_1715708177_pd0Y0%2FRJ0wWn1hXa</v>
       </c>
       <c r="N123" t="str">
-        <v>Annie</v>
+        <v>Dolly</v>
       </c>
       <c r="O123" t="str">
-        <v>info@elev8stays.co.uk</v>
+        <v>info@citygateproperty.com</v>
       </c>
       <c r="P123" t="str">
-        <v>07940950065</v>
+        <v>07958 571 307</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">W14 8HP </v>
+        <v>W12 7SF</v>
       </c>
       <c r="B124" t="str">
-        <v>Holland Rd, London, UK</v>
+        <v>Fountain Park Wy, London W12, UK</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -63069,7 +63078,7 @@
         <v>2</v>
       </c>
       <c r="E124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" t="str">
         <v>off-site-chargeable</v>
@@ -63090,45 +63099,45 @@
         <v>0</v>
       </c>
       <c r="L124" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6762bce39705f8f6fd8d9054</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68bed9c329edaa5d143ebb98</v>
       </c>
       <c r="M124" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1281747887308361861?source_impression_id=p3_1734524064_P3yRQ2coR16ZqEqM</v>
+        <v>https://www.airbnb.co.uk/rooms/1478234898769467858?source_impression_id=p3_1757337796_P3k3cbuyZDmInulR</v>
       </c>
       <c r="N124" t="str">
-        <v>Hugh Nuemann</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O124" t="str">
-        <v>info@huemanhome.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P124" t="str">
-        <v>07812 036218</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>W14 8RS</v>
+        <v>W12 8LQ</v>
       </c>
       <c r="B125" t="str">
-        <v>Avonmore Rd, London W14 8RS, UK</v>
+        <v>2, 11 Richmond Way, London W12 8LQ, UK</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G125" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -63140,24 +63149,33 @@
         <v>0</v>
       </c>
       <c r="L125" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/670502cd6c4c8dd90f1e022c</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/684192d86e40fb463e0c7ea1</v>
       </c>
       <c r="M125" t="str">
-        <v>https://www.airbnb.co.uk/rooms/697860747839065994?source_impression_id=p3_1728380263_P3jxe6ldu5BvBmRf</v>
+        <v>https://www.airbnb.co.uk/rooms/1399201898792819142?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=aa839f79-dbd8-4fd0-868c-739405e0b33e&amp;source_impression_id=p3_1749127712_P3eR1pth3FE1L7T3</v>
+      </c>
+      <c r="N125" t="str">
+        <v>Fernando</v>
+      </c>
+      <c r="O125" t="str">
+        <v>info@urbanview-rentals.co.uk</v>
+      </c>
+      <c r="P125" t="str">
+        <v>07946446163</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>W14 9AD</v>
+        <v>W12 9PD</v>
       </c>
       <c r="B126" t="str">
-        <v>Edith Villas, London W14, UK</v>
+        <v>The Grange, Goldhawk Rd, London W12 9PD, UK</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -63181,10 +63199,10 @@
         <v>0</v>
       </c>
       <c r="L126" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/688c9e9dcd02201a20dec8ce</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/692031fa61fdbdc70f54aa74</v>
       </c>
       <c r="M126" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1421018748466196226?adults=1&amp;check_in=2025-08-18&amp;location=SW6%206AF&amp;search_mode=regular_search&amp;source_impression_id=p3_1754040229_P3gmT3e7jVNgGycf&amp;previous_page_section_name=1001&amp;federated_search_id=594e0e91-a148-448a-8f2b-0d25837a4931&amp;guests=1&amp;check_out=2025-09-01</v>
+        <v>https://www.airbnb.co.uk/rooms/843979084624842200?source_impression_id=p3_1763717152_P37Wgk2sD6gVKFr9&amp;check_in=2025-11-22&amp;guests=1&amp;adults=1&amp;check_out=2025-11-29</v>
       </c>
       <c r="N126" t="str">
         <v>Airbnb Temporary</v>
@@ -63198,28 +63216,28 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>W14 9EQ</v>
+        <v>W14 8AS</v>
       </c>
       <c r="B127" t="str">
-        <v>Palliser Rd, London W14, UK</v>
+        <v>147A Holland Rd, London W14 8AS, UK</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G127" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" t="b">
         <v>0</v>
@@ -63231,36 +63249,27 @@
         <v>0</v>
       </c>
       <c r="L127" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6733760fc8526d02b9494b9b</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6728b8cbd1ab2037750b678d</v>
       </c>
       <c r="M127" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1241856898090759613?source_impression_id=p3_1731425623_P31tbe-SFNfSoLlP</v>
-      </c>
-      <c r="N127" t="str">
-        <v>Rashid</v>
-      </c>
-      <c r="O127" t="str">
-        <v>q@propertyy.io</v>
-      </c>
-      <c r="P127" t="str">
-        <v>0000000000</v>
+        <v>https://www.booking.com/hotel/gb/luxury-designer-flat-holland-park.en-gb.html?aid=2276424&amp;label=msn-HEC27qPyOZmLPBxa2YE3Nw-80676810309425%3Atikwd-80676960770001%3Aloc-41471%3Aneo%3Amte%3Alp41471%3Adec%3Aqsapart%20hotels%20w14%20london&amp;sid=c56aa9f495ded14af2d4d054a903fa6d&amp;all_sr_blocks=143034801_130622008_6_0_0;checkin=2024-11-04;checkout=2024-11-25;dist=0;group_adults=2;group_children=0;hapos=1;highlighted_blocks=143034801_130622008_6_0_0;hpos=1;matching_block_id=143034801_130622008_6_0_0;nflt=price%3DGBP-min-max-1%3Bht_id%3D201%3Baccessible_room_facilities%3D131;no_rooms=2;req_adults=2;req_children=0;room1=A;room2=A;sb_price_type=total;sr_order=distance_from_search;sr_pri_blocks=143034801_130622008_6_0_0__598100;srepoch=1730721405;srpvid=13ca53d733e1142c;type=total;ucfs=1&amp;</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>W14 9NX</v>
+        <v>W14 8BA</v>
       </c>
       <c r="B128" t="str">
-        <v>212 North End Rd, London W14 9NX, UK</v>
+        <v>Holland Rd, London W14 8BA, UK</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E128">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F128" t="str">
         <v>off-site-chargeable</v>
@@ -63281,33 +63290,33 @@
         <v>0</v>
       </c>
       <c r="L128" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68713870be8ece05b88b745f</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68e538654742d568c76f5319</v>
       </c>
       <c r="M128" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1447993240658552749?adults=2&amp;check_in=2025-07-15&amp;check_out=2025-08-05&amp;children=2&amp;location=W14%200DY&amp;pets=1&amp;search_mode=regular_search&amp;source_impression_id=p3_1752249131_P3VbKqI2fz4MC43G&amp;previous_page_section_name=1001&amp;federated_search_id=f1f0314e-a10d-4f96-905a-f2ffcc26190b</v>
+        <v>https://www.airbnb.co.uk/rooms/1445520707647119008?viralityEntryPoint=1&amp;unique_share_id=DDB5C481-F3E7-4572-85B3-009A630913F4&amp;slcid=d978484b14934a44a2aa7208d3b8352b&amp;s=76&amp;adults=1&amp;slug=SGWujO2T&amp;source_impression_id=p3_1759851881_P3qGxUy-MB3E94D0</v>
       </c>
       <c r="N128" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Annie</v>
       </c>
       <c r="O128" t="str">
-        <v>temp@airbnb.com</v>
+        <v>info@elev8stays.co.uk</v>
       </c>
       <c r="P128" t="str">
-        <v>00000000000</v>
+        <v>07940950065</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>W14 9PA</v>
+        <v xml:space="preserve">W14 8HP </v>
       </c>
       <c r="B129" t="str">
-        <v>Bramber Rd, London W14 9PA, UK</v>
+        <v>Holland Rd, London, UK</v>
       </c>
       <c r="C129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -63316,10 +63325,10 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G129" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="b">
         <v>0</v>
@@ -63331,36 +63340,45 @@
         <v>0</v>
       </c>
       <c r="L129" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6703e70b225d9354290bd1ce</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6762bce39705f8f6fd8d9054</v>
       </c>
       <c r="M129" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1229169634762318402?source_impression_id=p3_1728308297_P3DdlK7LNWV8Wkr1</v>
+        <v>https://www.airbnb.co.uk/rooms/1281747887308361861?source_impression_id=p3_1734524064_P3yRQ2coR16ZqEqM</v>
+      </c>
+      <c r="N129" t="str">
+        <v>Hugh Nuemann</v>
+      </c>
+      <c r="O129" t="str">
+        <v>info@huemanhome.com</v>
+      </c>
+      <c r="P129" t="str">
+        <v>07812 036218</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>W14 9SR</v>
+        <v>W14 8RS</v>
       </c>
       <c r="B130" t="str">
-        <v>29 Perham Rd, London W14 9SR, UK</v>
+        <v>Avonmore Rd, London W14 8RS, UK</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G130" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="b">
         <v>0</v>
@@ -63372,27 +63390,18 @@
         <v>0</v>
       </c>
       <c r="L130" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b8516436569b00e6f88d5c</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/670502cd6c4c8dd90f1e022c</v>
       </c>
       <c r="M130" t="str">
-        <v>https://www.airbnb.co.uk/rooms/916062053365126516?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909399_P3aPPHZLh9R4sgCq</v>
-      </c>
-      <c r="N130" t="str">
-        <v>Waleed Khalid</v>
-      </c>
-      <c r="O130" t="str">
-        <v>fakewaleed@gmail.com</v>
-      </c>
-      <c r="P130" t="str">
-        <v>+44 7930 000039</v>
+        <v>https://www.airbnb.co.uk/rooms/697860747839065994?source_impression_id=p3_1728380263_P3jxe6ldu5BvBmRf</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>W14 9SR</v>
+        <v>W14 9AD</v>
       </c>
       <c r="B131" t="str">
-        <v>29 Perham Rd, London W14 9SR, UK</v>
+        <v>Edith Villas, London W14, UK</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -63422,33 +63431,33 @@
         <v>0</v>
       </c>
       <c r="L131" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b8532d36569b00e6f88f23</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/688c9e9dcd02201a20dec8ce</v>
       </c>
       <c r="M131" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1046492595924875175?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909999_P30xyAZGPUFJ-QQQ</v>
+        <v>https://www.airbnb.co.uk/rooms/1421018748466196226?adults=1&amp;check_in=2025-08-18&amp;location=SW6%206AF&amp;search_mode=regular_search&amp;source_impression_id=p3_1754040229_P3gmT3e7jVNgGycf&amp;previous_page_section_name=1001&amp;federated_search_id=594e0e91-a148-448a-8f2b-0d25837a4931&amp;guests=1&amp;check_out=2025-09-01</v>
       </c>
       <c r="N131" t="str">
-        <v>Waleed Khalid</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O131" t="str">
-        <v>fakewaleed@gmail.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P131" t="str">
-        <v>+44 7930 000039</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>W14 9SR</v>
+        <v>W14 9EQ</v>
       </c>
       <c r="B132" t="str">
-        <v>29 Perham Rd, London W14 9SR, UK</v>
+        <v>Palliser Rd, London W14, UK</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -63457,7 +63466,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G132" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H132" t="b">
         <v>0</v>
@@ -63472,42 +63481,42 @@
         <v>0</v>
       </c>
       <c r="L132" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b85250fead75d2c44e3756</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6733760fc8526d02b9494b9b</v>
       </c>
       <c r="M132" t="str">
-        <v>https://www.airbnb.co.uk/rooms/1014323013581423016?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909995_P3pKaGIDjb9Eqxi2</v>
+        <v>https://www.airbnb.co.uk/rooms/1241856898090759613?source_impression_id=p3_1731425623_P31tbe-SFNfSoLlP</v>
       </c>
       <c r="N132" t="str">
-        <v>Waleed Khalid</v>
+        <v>Rashid</v>
       </c>
       <c r="O132" t="str">
-        <v>fakewaleed@gmail.com</v>
+        <v>q@propertyy.io</v>
       </c>
       <c r="P132" t="str">
-        <v>+44 7930 000039</v>
+        <v>0000000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>W14 9SR</v>
+        <v>W14 9NX</v>
       </c>
       <c r="B133" t="str">
-        <v>29 Perham Rd, London W14 9SR, UK</v>
+        <v>212 North End Rd, London W14 9NX, UK</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F133" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G133" t="str">
-        <v>no</v>
+        <v>chargeable</v>
       </c>
       <c r="H133" t="b">
         <v>0</v>
@@ -63522,33 +63531,33 @@
         <v>0</v>
       </c>
       <c r="L133" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/68b852c8fead75d2c44e37a9</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68713870be8ece05b88b745f</v>
       </c>
       <c r="M133" t="str">
-        <v>https://www.airbnb.co.uk/rooms/779893715432977998?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909996_P320kjk6r2HDmdXw</v>
+        <v>https://www.airbnb.co.uk/rooms/1447993240658552749?adults=2&amp;check_in=2025-07-15&amp;check_out=2025-08-05&amp;children=2&amp;location=W14%200DY&amp;pets=1&amp;search_mode=regular_search&amp;source_impression_id=p3_1752249131_P3VbKqI2fz4MC43G&amp;previous_page_section_name=1001&amp;federated_search_id=f1f0314e-a10d-4f96-905a-f2ffcc26190b</v>
       </c>
       <c r="N133" t="str">
-        <v>Waleed Khalid</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O133" t="str">
-        <v>fakewaleed@gmail.com</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P133" t="str">
-        <v>+44 7930 000039</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>W6 0NW</v>
+        <v>W14 9PA</v>
       </c>
       <c r="B134" t="str">
-        <v>Verulam House, Hammersmith Grove, London W6 0NW, UK</v>
+        <v>Bramber Rd, London W14 9PA, UK</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -63560,7 +63569,7 @@
         <v>no</v>
       </c>
       <c r="H134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I134" t="b">
         <v>0</v>
@@ -63572,27 +63581,18 @@
         <v>0</v>
       </c>
       <c r="L134" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6797bd109b48e7bffd8e6e71</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6703e70b225d9354290bd1ce</v>
       </c>
       <c r="M134" t="str">
-        <v>https://www.airbnb.co.uk/rooms/846987931855578729?source_impression_id=p3_1737997474_P34IR7Y5umGSGePy</v>
-      </c>
-      <c r="N134" t="str">
-        <v>Airbnb Temporary</v>
-      </c>
-      <c r="O134" t="str">
-        <v>temp@airbnb.com</v>
-      </c>
-      <c r="P134" t="str">
-        <v>00000000000</v>
+        <v>https://www.airbnb.co.uk/rooms/1229169634762318402?source_impression_id=p3_1728308297_P3DdlK7LNWV8Wkr1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>W6 0RR</v>
+        <v>W14 9SR</v>
       </c>
       <c r="B135" t="str">
-        <v>308 King St, London W6 0RR, UK</v>
+        <v>29 Perham Rd, London W14 9SR, UK</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -63622,33 +63622,33 @@
         <v>0</v>
       </c>
       <c r="L135" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6797c3519b48e7bffd8e7610</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b8516436569b00e6f88d5c</v>
       </c>
       <c r="M135" t="str">
-        <v>https://www.booking.com/hotel/gb/cozy-1-bedroom-flat-greater-london.en-gb.html?aid=304142&amp;label=gen173rf-1FCAQoggJCKXNlYXJjaF9vYWtsYW5kcytncm92ZSwrbG9uZG9uK3cxMiswamQsK3VrSAlYA2hQiAEBmAEJuAEXyAEM2AEB6AEB-AEDiAIBogITbXlob21laXN5b3Vycy5jby51a6gCA7gC6ITfvAbAAgHSAiQ0MDQ3NmQ5NS01MzdlLTRkNGEtYmMyNy00NGM5OGFiYjQxMTLYAgXgAgE&amp;sid=52fce589b709a7c1281b11adf2d9f4bf&amp;all_sr_blocks=1300187401_402907111_2_41_0&amp;checkin=2025-01-28&amp;checkout=2025-02-25&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1300187401_402907111_2_41_0&amp;hpos=1&amp;matching_block_id=1300187401_402907111_2_41_0&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1300187401_402907111_2_41_0__356048&amp;srepoch=1737999019&amp;srpvid=5cb77af44b8709e9&amp;type=total&amp;ucfs=1&amp;</v>
+        <v>https://www.airbnb.co.uk/rooms/916062053365126516?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909399_P3aPPHZLh9R4sgCq</v>
       </c>
       <c r="N135" t="str">
-        <v>Booking.Com Temporary</v>
+        <v>Waleed Khalid</v>
       </c>
       <c r="O135" t="str">
-        <v>fake@booking.com</v>
+        <v>waleed.khalid2021@hotmail.com</v>
       </c>
       <c r="P135" t="str">
-        <v>00000000000</v>
+        <v>+44 7930 000039</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>W6 7HA</v>
+        <v>W14 9SR</v>
       </c>
       <c r="B136" t="str">
-        <v>Hammersmith Grove, London W6 7HA, UK</v>
+        <v>29 Perham Rd, London W14 9SR, UK</v>
       </c>
       <c r="C136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -63657,7 +63657,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G136" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H136" t="b">
         <v>0</v>
@@ -63672,33 +63672,33 @@
         <v>0</v>
       </c>
       <c r="L136" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6798be3e4222378e6f18a545</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b85250fead75d2c44e3756</v>
       </c>
       <c r="M136" t="str">
-        <v>https://www.airbnb.co.uk/rooms/846987931855578729?source_impression_id=p3_1738063351_P39Vma0mlvFkhxdD</v>
+        <v>https://www.airbnb.co.uk/rooms/1014323013581423016?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909995_P3pKaGIDjb9Eqxi2</v>
       </c>
       <c r="N136" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Waleed Khalid</v>
       </c>
       <c r="O136" t="str">
-        <v>temp@airbnb.com</v>
+        <v>waleed.khalid2021@hotmail.com</v>
       </c>
       <c r="P136" t="str">
-        <v>00000000000</v>
+        <v>+44 7930 000039</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>W6 7LY</v>
+        <v>W14 9SR</v>
       </c>
       <c r="B137" t="str">
-        <v>The Grampians, Shepherds Bush Rd, London W6 7LN, UK</v>
+        <v>29 Perham Rd, London W14 9SR, UK</v>
       </c>
       <c r="C137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -63707,7 +63707,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G137" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H137" t="b">
         <v>0</v>
@@ -63722,42 +63722,42 @@
         <v>0</v>
       </c>
       <c r="L137" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6797bf7c0f58a7d7cea7e892</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b852c8fead75d2c44e37a9</v>
       </c>
       <c r="M137" t="str">
-        <v>https://www.airbnb.co.uk/rooms/36418219?source_impression_id=p3_1737998044_P3i72K2eLJjQljBK</v>
+        <v>https://www.airbnb.co.uk/rooms/779893715432977998?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909996_P320kjk6r2HDmdXw</v>
       </c>
       <c r="N137" t="str">
-        <v>Airbnb Temporary</v>
+        <v>Waleed Khalid</v>
       </c>
       <c r="O137" t="str">
-        <v>temp@airbnb.com</v>
+        <v>waleed.khalid2021@hotmail.com</v>
       </c>
       <c r="P137" t="str">
-        <v>00000000000</v>
+        <v>+44 7930 000039</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>W6 9EZ</v>
+        <v>W14 9SR</v>
       </c>
       <c r="B138" t="str">
-        <v>Colwith Rd, London W6 9EZ, UK</v>
+        <v>29 Perham Rd, London W14 9SR, UK</v>
       </c>
       <c r="C138">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" t="str">
         <v>off-site-chargeable</v>
       </c>
       <c r="G138" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H138" t="b">
         <v>0</v>
@@ -63766,39 +63766,39 @@
         <v>0</v>
       </c>
       <c r="J138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" t="b">
         <v>0</v>
       </c>
       <c r="L138" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/682c609078091bb5b4b335db</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/68b8532d36569b00e6f88f23</v>
       </c>
       <c r="M138" t="str">
-        <v>https://nournestapartments.com/listing/refined-hammersmith-3-bedroom-with-rooftop/</v>
+        <v>https://www.airbnb.co.uk/rooms/1046492595924875175?viralityEntryPoint=1&amp;s=76&amp;source_impression_id=p3_1756909999_P30xyAZGPUFJ-QQQ</v>
       </c>
       <c r="N138" t="str">
-        <v>Gerda &amp; Chris</v>
+        <v>Waleed Khalid</v>
       </c>
       <c r="O138" t="str">
-        <v>hello@nournestapartments.com</v>
+        <v>waleed.khalid2021@hotmail.com</v>
       </c>
       <c r="P138" t="str">
-        <v xml:space="preserve"> +44 208 064 0268</v>
+        <v>+44 7930 000039</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>W6 9HA</v>
+        <v>W6 0NW</v>
       </c>
       <c r="B139" t="str">
-        <v>3 Rainville Rd, London W6 9HA, UK</v>
+        <v>Verulam House, Hammersmith Grove, London W6 0NW, UK</v>
       </c>
       <c r="C139">
         <v>2</v>
       </c>
       <c r="D139">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -63807,7 +63807,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G139" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H139" t="b">
         <v>0</v>
@@ -63822,33 +63822,33 @@
         <v>0</v>
       </c>
       <c r="L139" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6728d956d1ab2037750b823c</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6797bd109b48e7bffd8e6e71</v>
       </c>
       <c r="M139" t="str">
-        <v>https://www.airbnb.com/rooms/786221755699867670?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=3d016987-df10-4fae-8716-1c1edb9b9dfa</v>
+        <v>https://www.airbnb.co.uk/rooms/846987931855578729?source_impression_id=p3_1737997474_P34IR7Y5umGSGePy</v>
       </c>
       <c r="N139" t="str">
-        <v>Shloime</v>
+        <v>Airbnb Temporary</v>
       </c>
       <c r="O139" t="str">
-        <v>shloime@hometohost.co.uk</v>
+        <v>temp@airbnb.com</v>
       </c>
       <c r="P139" t="str">
-        <v>07867290839</v>
+        <v>00000000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>W6 9LF</v>
+        <v>W6 0RR</v>
       </c>
       <c r="B140" t="str">
-        <v>Holcombe St, London W6, UK</v>
+        <v>308 King St, London W6 0RR, UK</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -63857,7 +63857,7 @@
         <v>off-site-chargeable</v>
       </c>
       <c r="G140" t="str">
-        <v>chargeable</v>
+        <v>no</v>
       </c>
       <c r="H140" t="b">
         <v>0</v>
@@ -63872,10 +63872,10 @@
         <v>0</v>
       </c>
       <c r="L140" t="str">
-        <v>https://www.myhomeisyours.co.uk/public/property/6870e5e327c01b288f21fc21</v>
+        <v>https://www.myhomeisyours.co.uk/public/property/6797c3519b48e7bffd8e7610</v>
       </c>
       <c r="M140" t="str">
-        <v>https://www.booking.com/hotel/gb/hammersmith-gem-bright-flat-close-to-the-tube.en-gb.html?aid=304142&amp;label=gen173nr-1FCAsoUEItaGFtbWVyc21pdGgtZ2VtLWJyaWdodC1mbGF0LWNsb3NlLXRvLXRoZS10dWJlSAlYBGhQiAEBmAEJuAEXyAEM2AEB6AEB-AEGiAIBqAIDuALrw8PDBsACAdICJGRlMzkxMGYzLTI2ODMtNGQzZS04NDVjLThhODZhYzY5ODU5M9gCBeACAQ&amp;sid=7c380fb8cafd8760226e8cee0417ae8a&amp;all_sr_blocks=1410890301_412848739_4_0_0&amp;checkin=2025-07-14&amp;checkout=2025-08-11&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=3&amp;highlighted_blocks=1410890301_412848739_4_0_0&amp;hpos=3&amp;matching_block_id=1410890301_412848739_4_0_0&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1410890301_412848739_4_0_0__659700&amp;srepoch=1752228330&amp;srpvid=b7d5a0eaeb115dc254a20010ecf9f4a6&amp;type=total&amp;ucfs=1&amp;</v>
+        <v>https://www.booking.com/hotel/gb/cozy-1-bedroom-flat-greater-london.en-gb.html?aid=304142&amp;label=gen173rf-1FCAQoggJCKXNlYXJjaF9vYWtsYW5kcytncm92ZSwrbG9uZG9uK3cxMiswamQsK3VrSAlYA2hQiAEBmAEJuAEXyAEM2AEB6AEB-AEDiAIBogITbXlob21laXN5b3Vycy5jby51a6gCA7gC6ITfvAbAAgHSAiQ0MDQ3NmQ5NS01MzdlLTRkNGEtYmMyNy00NGM5OGFiYjQxMTLYAgXgAgE&amp;sid=52fce589b709a7c1281b11adf2d9f4bf&amp;all_sr_blocks=1300187401_402907111_2_41_0&amp;checkin=2025-01-28&amp;checkout=2025-02-25&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=1&amp;highlighted_blocks=1300187401_402907111_2_41_0&amp;hpos=1&amp;matching_block_id=1300187401_402907111_2_41_0&amp;nflt=accessible_room_facilities%3D131&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1300187401_402907111_2_41_0__356048&amp;srepoch=1737999019&amp;srpvid=5cb77af44b8709e9&amp;type=total&amp;ucfs=1&amp;</v>
       </c>
       <c r="N140" t="str">
         <v>Booking.Com Temporary</v>
@@ -63889,28 +63889,28 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>W6 9SP</v>
+        <v>W6 7HA</v>
       </c>
       <c r="B141" t="str">
-        <v>78 Rannoch Rd, London W6 9SP, UK</v>
+        <v>Hammersmith Grove, London W6 7HA, UK</v>
       </c>
       <c r="C141">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E141">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F141" t="str">
-        <v>on-site-free</v>
+        <v>off-site-chargeable</v>
       </c>
       <c r="G141" t="str">
         <v>chargeable</v>
       </c>
       <c r="H141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" t="b">
         <v>0</v>
@@ -63922,24 +63922,274 @@
         <v>0</v>
       </c>
       <c r="L141" t="str">
+        <v>https://www.myhomeisyours.co.uk/public/property/6798be3e4222378e6f18a545</v>
+      </c>
+      <c r="M141" t="str">
+        <v>https://www.airbnb.co.uk/rooms/846987931855578729?source_impression_id=p3_1738063351_P39Vma0mlvFkhxdD</v>
+      </c>
+      <c r="N141" t="str">
+        <v>Airbnb Temporary</v>
+      </c>
+      <c r="O141" t="str">
+        <v>temp@airbnb.com</v>
+      </c>
+      <c r="P141" t="str">
+        <v>00000000000</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>W6 7LY</v>
+      </c>
+      <c r="B142" t="str">
+        <v>The Grampians, Shepherds Bush Rd, London W6 7LN, UK</v>
+      </c>
+      <c r="C142">
+        <v>2</v>
+      </c>
+      <c r="D142">
+        <v>2</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142" t="str">
+        <v>off-site-chargeable</v>
+      </c>
+      <c r="G142" t="str">
+        <v>chargeable</v>
+      </c>
+      <c r="H142" t="b">
+        <v>0</v>
+      </c>
+      <c r="I142" t="b">
+        <v>0</v>
+      </c>
+      <c r="J142" t="b">
+        <v>0</v>
+      </c>
+      <c r="K142" t="b">
+        <v>0</v>
+      </c>
+      <c r="L142" t="str">
+        <v>https://www.myhomeisyours.co.uk/public/property/6797bf7c0f58a7d7cea7e892</v>
+      </c>
+      <c r="M142" t="str">
+        <v>https://www.airbnb.co.uk/rooms/36418219?source_impression_id=p3_1737998044_P3i72K2eLJjQljBK</v>
+      </c>
+      <c r="N142" t="str">
+        <v>Airbnb Temporary</v>
+      </c>
+      <c r="O142" t="str">
+        <v>temp@airbnb.com</v>
+      </c>
+      <c r="P142" t="str">
+        <v>00000000000</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>W6 9EZ</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Colwith Rd, London W6 9EZ, UK</v>
+      </c>
+      <c r="C143">
+        <v>3</v>
+      </c>
+      <c r="D143">
+        <v>3</v>
+      </c>
+      <c r="E143">
+        <v>2</v>
+      </c>
+      <c r="F143" t="str">
+        <v>off-site-chargeable</v>
+      </c>
+      <c r="G143" t="str">
+        <v>chargeable</v>
+      </c>
+      <c r="H143" t="b">
+        <v>0</v>
+      </c>
+      <c r="I143" t="b">
+        <v>0</v>
+      </c>
+      <c r="J143" t="b">
+        <v>1</v>
+      </c>
+      <c r="K143" t="b">
+        <v>0</v>
+      </c>
+      <c r="L143" t="str">
+        <v>https://www.myhomeisyours.co.uk/public/property/682c609078091bb5b4b335db</v>
+      </c>
+      <c r="M143" t="str">
+        <v>https://nournestapartments.com/listing/refined-hammersmith-3-bedroom-with-rooftop/</v>
+      </c>
+      <c r="N143" t="str">
+        <v>Gerda &amp; Chris</v>
+      </c>
+      <c r="O143" t="str">
+        <v>hello@nournestapartments.com</v>
+      </c>
+      <c r="P143" t="str">
+        <v xml:space="preserve"> +44 208 064 0268</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>W6 9HA</v>
+      </c>
+      <c r="B144" t="str">
+        <v>3 Rainville Rd, London W6 9HA, UK</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144">
+        <v>4</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="F144" t="str">
+        <v>off-site-chargeable</v>
+      </c>
+      <c r="G144" t="str">
+        <v>chargeable</v>
+      </c>
+      <c r="H144" t="b">
+        <v>0</v>
+      </c>
+      <c r="I144" t="b">
+        <v>0</v>
+      </c>
+      <c r="J144" t="b">
+        <v>0</v>
+      </c>
+      <c r="K144" t="b">
+        <v>0</v>
+      </c>
+      <c r="L144" t="str">
+        <v>https://www.myhomeisyours.co.uk/public/property/6728d956d1ab2037750b823c</v>
+      </c>
+      <c r="M144" t="str">
+        <v>https://www.airbnb.com/rooms/786221755699867670?guests=1&amp;adults=1&amp;s=67&amp;unique_share_id=3d016987-df10-4fae-8716-1c1edb9b9dfa</v>
+      </c>
+      <c r="N144" t="str">
+        <v>Shloime</v>
+      </c>
+      <c r="O144" t="str">
+        <v>shloime@hometohost.co.uk</v>
+      </c>
+      <c r="P144" t="str">
+        <v>07867290839</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>W6 9LF</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Holcombe St, London W6, UK</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145">
+        <v>2</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+      <c r="F145" t="str">
+        <v>off-site-chargeable</v>
+      </c>
+      <c r="G145" t="str">
+        <v>chargeable</v>
+      </c>
+      <c r="H145" t="b">
+        <v>0</v>
+      </c>
+      <c r="I145" t="b">
+        <v>0</v>
+      </c>
+      <c r="J145" t="b">
+        <v>0</v>
+      </c>
+      <c r="K145" t="b">
+        <v>0</v>
+      </c>
+      <c r="L145" t="str">
+        <v>https://www.myhomeisyours.co.uk/public/property/6870e5e327c01b288f21fc21</v>
+      </c>
+      <c r="M145" t="str">
+        <v>https://www.booking.com/hotel/gb/hammersmith-gem-bright-flat-close-to-the-tube.en-gb.html?aid=304142&amp;label=gen173nr-1FCAsoUEItaGFtbWVyc21pdGgtZ2VtLWJyaWdodC1mbGF0LWNsb3NlLXRvLXRoZS10dWJlSAlYBGhQiAEBmAEJuAEXyAEM2AEB6AEB-AEGiAIBqAIDuALrw8PDBsACAdICJGRlMzkxMGYzLTI2ODMtNGQzZS04NDVjLThhODZhYzY5ODU5M9gCBeACAQ&amp;sid=7c380fb8cafd8760226e8cee0417ae8a&amp;all_sr_blocks=1410890301_412848739_4_0_0&amp;checkin=2025-07-14&amp;checkout=2025-08-11&amp;dist=0&amp;group_adults=2&amp;group_children=0&amp;hapos=3&amp;highlighted_blocks=1410890301_412848739_4_0_0&amp;hpos=3&amp;matching_block_id=1410890301_412848739_4_0_0&amp;no_rooms=1&amp;req_adults=2&amp;req_children=0&amp;room1=A%2CA&amp;sb_price_type=total&amp;sr_order=popularity&amp;sr_pri_blocks=1410890301_412848739_4_0_0__659700&amp;srepoch=1752228330&amp;srpvid=b7d5a0eaeb115dc254a20010ecf9f4a6&amp;type=total&amp;ucfs=1&amp;</v>
+      </c>
+      <c r="N145" t="str">
+        <v>Booking.Com Temporary</v>
+      </c>
+      <c r="O145" t="str">
+        <v>fake@booking.com</v>
+      </c>
+      <c r="P145" t="str">
+        <v>00000000000</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>W6 9SP</v>
+      </c>
+      <c r="B146" t="str">
+        <v>78 Rannoch Rd, London W6 9SP, UK</v>
+      </c>
+      <c r="C146">
+        <v>5</v>
+      </c>
+      <c r="D146">
+        <v>5</v>
+      </c>
+      <c r="E146">
+        <v>4.5</v>
+      </c>
+      <c r="F146" t="str">
+        <v>on-site-free</v>
+      </c>
+      <c r="G146" t="str">
+        <v>chargeable</v>
+      </c>
+      <c r="H146" t="b">
+        <v>1</v>
+      </c>
+      <c r="I146" t="b">
+        <v>0</v>
+      </c>
+      <c r="J146" t="b">
+        <v>0</v>
+      </c>
+      <c r="K146" t="b">
+        <v>0</v>
+      </c>
+      <c r="L146" t="str">
         <v>https://www.myhomeisyours.co.uk/public/property/68dd223b699b101f6e5120d3</v>
       </c>
-      <c r="M141" t="str">
+      <c r="M146" t="str">
         <v>https://www.airbnb.co.uk/rooms/1221077715659269159?source_impression_id=p3_1759322347_P3thUDdzPZoe4FeP&amp;check_in=2025-10-06&amp;guests=1&amp;adults=1&amp;check_out=2025-10-13</v>
       </c>
-      <c r="N141" t="str">
+      <c r="N146" t="str">
         <v>Yoko Property Management</v>
       </c>
-      <c r="O141" t="str">
+      <c r="O146" t="str">
         <v>info@yokoproperty.co.uk</v>
       </c>
-      <c r="P141" t="str">
+      <c r="P146" t="str">
         <v>use whatsapp group / 0333 772 7478</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P141"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P146"/>
   </ignoredErrors>
 </worksheet>
 </file>